--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -9327,7 +9327,7 @@
         <v>47</v>
       </c>
       <c r="D504" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -9425,7 +9425,7 @@
         <v>134</v>
       </c>
       <c r="D511" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -9705,7 +9705,7 @@
         <v>286</v>
       </c>
       <c r="D531" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9957,7 +9957,7 @@
         <v>328</v>
       </c>
       <c r="D549" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9985,7 +9985,7 @@
         <v>330</v>
       </c>
       <c r="D551" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -10027,7 +10027,7 @@
         <v>338</v>
       </c>
       <c r="D554" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -10335,7 +10335,7 @@
         <v>441</v>
       </c>
       <c r="D576" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -10391,7 +10391,7 @@
         <v>445</v>
       </c>
       <c r="D580" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -10405,7 +10405,7 @@
         <v>446</v>
       </c>
       <c r="D581" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -10433,7 +10433,7 @@
         <v>447</v>
       </c>
       <c r="D583" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -10461,7 +10461,7 @@
         <v>449</v>
       </c>
       <c r="D585" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -62927,13 +62927,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97053B8B-B84D-4A85-96BF-7578E825D630}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6006856A-9378-4519-9EAB-32A108BA98E1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{739DBF45-4CA6-432C-BAB2-961E2F6B6EB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D80D66D2-6F1F-410E-9139-3967F52B3BB4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{552BD061-64CE-46C2-9DAA-32E2667BD71C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1181C9D4-4FC6-4273-BFF1-FE0122DB04D1}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -5686,7 +5686,7 @@
         <v>104</v>
       </c>
       <c r="D302" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5770,7 +5770,7 @@
         <v>125</v>
       </c>
       <c r="D308" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5854,7 +5854,7 @@
         <v>136</v>
       </c>
       <c r="D314" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5868,7 +5868,7 @@
         <v>139</v>
       </c>
       <c r="D315" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5910,7 +5910,7 @@
         <v>145</v>
       </c>
       <c r="D318" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5966,7 +5966,7 @@
         <v>154</v>
       </c>
       <c r="D322" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5980,7 +5980,7 @@
         <v>159</v>
       </c>
       <c r="D323" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6008,7 +6008,7 @@
         <v>162</v>
       </c>
       <c r="D325" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -6036,7 +6036,7 @@
         <v>168</v>
       </c>
       <c r="D327" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6218,7 +6218,7 @@
         <v>194</v>
       </c>
       <c r="D340" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6666,7 +6666,7 @@
         <v>299</v>
       </c>
       <c r="D372" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -33764,13 +33764,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE0CFC65-A868-43AD-8210-37C5F6EFBCE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53B96106-6FB1-4039-84A7-0A25F9292D1F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C859EBC7-31C6-4FE9-B676-71EE7E032E08}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B01FE9C3-8D3F-4ADF-AF8B-82776436C6B2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C395D57-84D4-40F7-9B53-47316288FDE5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16F14AE5-1C42-4D7F-94F5-0D2AE8475FF8}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -33764,13 +33764,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53B96106-6FB1-4039-84A7-0A25F9292D1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EABC2A8-EEA7-4F06-8F65-4AD332C8182E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B01FE9C3-8D3F-4ADF-AF8B-82776436C6B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E58779A9-1103-46FB-8604-9EE9EEFA3973}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16F14AE5-1C42-4D7F-94F5-0D2AE8475FF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D817C7A-D0E6-45B4-B07C-D76F1F692008}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -5364,7 +5364,7 @@
         <v>6</v>
       </c>
       <c r="D279" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5378,7 +5378,7 @@
         <v>7</v>
       </c>
       <c r="D280" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5420,7 +5420,7 @@
         <v>25</v>
       </c>
       <c r="D283" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5434,7 +5434,7 @@
         <v>28</v>
       </c>
       <c r="D284" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5476,7 +5476,7 @@
         <v>48</v>
       </c>
       <c r="D287" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5490,7 +5490,7 @@
         <v>49</v>
       </c>
       <c r="D288" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5504,7 +5504,7 @@
         <v>50</v>
       </c>
       <c r="D289" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5518,7 +5518,7 @@
         <v>51</v>
       </c>
       <c r="D290" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5532,7 +5532,7 @@
         <v>54</v>
       </c>
       <c r="D291" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5546,7 +5546,7 @@
         <v>55</v>
       </c>
       <c r="D292" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5560,7 +5560,7 @@
         <v>56</v>
       </c>
       <c r="D293" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5574,7 +5574,7 @@
         <v>72</v>
       </c>
       <c r="D294" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5588,7 +5588,7 @@
         <v>77</v>
       </c>
       <c r="D295" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5602,7 +5602,7 @@
         <v>85</v>
       </c>
       <c r="D296" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5616,7 +5616,7 @@
         <v>88</v>
       </c>
       <c r="D297" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5630,7 +5630,7 @@
         <v>92</v>
       </c>
       <c r="D298" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5644,7 +5644,7 @@
         <v>96</v>
       </c>
       <c r="D299" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5658,7 +5658,7 @@
         <v>102</v>
       </c>
       <c r="D300" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5686,7 +5686,7 @@
         <v>104</v>
       </c>
       <c r="D302" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5700,7 +5700,7 @@
         <v>107</v>
       </c>
       <c r="D303" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5742,7 +5742,7 @@
         <v>122</v>
       </c>
       <c r="D306" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5756,7 +5756,7 @@
         <v>123</v>
       </c>
       <c r="D307" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5770,7 +5770,7 @@
         <v>125</v>
       </c>
       <c r="D308" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5784,7 +5784,7 @@
         <v>126</v>
       </c>
       <c r="D309" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5826,7 +5826,7 @@
         <v>129</v>
       </c>
       <c r="D312" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5840,7 +5840,7 @@
         <v>135</v>
       </c>
       <c r="D313" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5854,7 +5854,7 @@
         <v>136</v>
       </c>
       <c r="D314" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5868,7 +5868,7 @@
         <v>139</v>
       </c>
       <c r="D315" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5910,7 +5910,7 @@
         <v>145</v>
       </c>
       <c r="D318" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5938,7 +5938,7 @@
         <v>148</v>
       </c>
       <c r="D320" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5952,7 +5952,7 @@
         <v>151</v>
       </c>
       <c r="D321" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5966,7 +5966,7 @@
         <v>154</v>
       </c>
       <c r="D322" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5980,7 +5980,7 @@
         <v>159</v>
       </c>
       <c r="D323" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6008,7 +6008,7 @@
         <v>162</v>
       </c>
       <c r="D325" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -6022,7 +6022,7 @@
         <v>166</v>
       </c>
       <c r="D326" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6078,7 +6078,7 @@
         <v>172</v>
       </c>
       <c r="D330" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6092,7 +6092,7 @@
         <v>173</v>
       </c>
       <c r="D331" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6120,7 +6120,7 @@
         <v>175</v>
       </c>
       <c r="D333" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6134,7 +6134,7 @@
         <v>177</v>
       </c>
       <c r="D334" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6148,7 +6148,7 @@
         <v>182</v>
       </c>
       <c r="D335" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6162,7 +6162,7 @@
         <v>183</v>
       </c>
       <c r="D336" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6176,7 +6176,7 @@
         <v>186</v>
       </c>
       <c r="D337" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6190,7 +6190,7 @@
         <v>189</v>
       </c>
       <c r="D338" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6204,7 +6204,7 @@
         <v>193</v>
       </c>
       <c r="D339" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6218,7 +6218,7 @@
         <v>194</v>
       </c>
       <c r="D340" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6260,7 +6260,7 @@
         <v>209</v>
       </c>
       <c r="D343" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6274,7 +6274,7 @@
         <v>226</v>
       </c>
       <c r="D344" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6288,7 +6288,7 @@
         <v>229</v>
       </c>
       <c r="D345" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6316,7 +6316,7 @@
         <v>235</v>
       </c>
       <c r="D347" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6330,7 +6330,7 @@
         <v>246</v>
       </c>
       <c r="D348" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6344,7 +6344,7 @@
         <v>259</v>
       </c>
       <c r="D349" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6372,7 +6372,7 @@
         <v>262</v>
       </c>
       <c r="D351" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6386,7 +6386,7 @@
         <v>263</v>
       </c>
       <c r="D352" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6400,7 +6400,7 @@
         <v>273</v>
       </c>
       <c r="D353" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6414,7 +6414,7 @@
         <v>276</v>
       </c>
       <c r="D354" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6428,7 +6428,7 @@
         <v>277</v>
       </c>
       <c r="D355" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6442,7 +6442,7 @@
         <v>285</v>
       </c>
       <c r="D356" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6470,7 +6470,7 @@
         <v>287</v>
       </c>
       <c r="D358" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6484,7 +6484,7 @@
         <v>288</v>
       </c>
       <c r="D359" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6498,7 +6498,7 @@
         <v>289</v>
       </c>
       <c r="D360" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6512,7 +6512,7 @@
         <v>290</v>
       </c>
       <c r="D361" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6526,7 +6526,7 @@
         <v>291</v>
       </c>
       <c r="D362" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6540,7 +6540,7 @@
         <v>150</v>
       </c>
       <c r="D363" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6554,7 +6554,7 @@
         <v>292</v>
       </c>
       <c r="D364" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6568,7 +6568,7 @@
         <v>293</v>
       </c>
       <c r="D365" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6582,7 +6582,7 @@
         <v>294</v>
       </c>
       <c r="D366" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6596,7 +6596,7 @@
         <v>130</v>
       </c>
       <c r="D367" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6610,7 +6610,7 @@
         <v>295</v>
       </c>
       <c r="D368" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6624,7 +6624,7 @@
         <v>296</v>
       </c>
       <c r="D369" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6680,7 +6680,7 @@
         <v>300</v>
       </c>
       <c r="D373" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6694,7 +6694,7 @@
         <v>301</v>
       </c>
       <c r="D374" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6708,7 +6708,7 @@
         <v>302</v>
       </c>
       <c r="D375" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6722,7 +6722,7 @@
         <v>303</v>
       </c>
       <c r="D376" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6736,7 +6736,7 @@
         <v>304</v>
       </c>
       <c r="D377" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6750,7 +6750,7 @@
         <v>305</v>
       </c>
       <c r="D378" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6764,7 +6764,7 @@
         <v>306</v>
       </c>
       <c r="D379" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6778,7 +6778,7 @@
         <v>307</v>
       </c>
       <c r="D380" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6792,7 +6792,7 @@
         <v>308</v>
       </c>
       <c r="D381" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6806,7 +6806,7 @@
         <v>309</v>
       </c>
       <c r="D382" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6820,7 +6820,7 @@
         <v>310</v>
       </c>
       <c r="D383" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6848,7 +6848,7 @@
         <v>312</v>
       </c>
       <c r="D385" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6862,7 +6862,7 @@
         <v>313</v>
       </c>
       <c r="D386" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6876,7 +6876,7 @@
         <v>314</v>
       </c>
       <c r="D387" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -6890,7 +6890,7 @@
         <v>315</v>
       </c>
       <c r="D388" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -6904,7 +6904,7 @@
         <v>316</v>
       </c>
       <c r="D389" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -6918,7 +6918,7 @@
         <v>317</v>
       </c>
       <c r="D390" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -6932,7 +6932,7 @@
         <v>318</v>
       </c>
       <c r="D391" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -6946,7 +6946,7 @@
         <v>319</v>
       </c>
       <c r="D392" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -6960,7 +6960,7 @@
         <v>320</v>
       </c>
       <c r="D393" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6974,7 +6974,7 @@
         <v>321</v>
       </c>
       <c r="D394" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6988,7 +6988,7 @@
         <v>322</v>
       </c>
       <c r="D395" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7002,7 +7002,7 @@
         <v>323</v>
       </c>
       <c r="D396" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7016,7 +7016,7 @@
         <v>324</v>
       </c>
       <c r="D397" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7030,7 +7030,7 @@
         <v>325</v>
       </c>
       <c r="D398" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7044,7 +7044,7 @@
         <v>326</v>
       </c>
       <c r="D399" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7058,7 +7058,7 @@
         <v>327</v>
       </c>
       <c r="D400" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7072,7 +7072,7 @@
         <v>328</v>
       </c>
       <c r="D401" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7086,7 +7086,7 @@
         <v>329</v>
       </c>
       <c r="D402" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7100,7 +7100,7 @@
         <v>330</v>
       </c>
       <c r="D403" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7128,7 +7128,7 @@
         <v>332</v>
       </c>
       <c r="D405" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7142,7 +7142,7 @@
         <v>333</v>
       </c>
       <c r="D406" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7156,7 +7156,7 @@
         <v>334</v>
       </c>
       <c r="D407" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7170,7 +7170,7 @@
         <v>335</v>
       </c>
       <c r="D408" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7184,7 +7184,7 @@
         <v>336</v>
       </c>
       <c r="D409" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7198,7 +7198,7 @@
         <v>337</v>
       </c>
       <c r="D410" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7226,7 +7226,7 @@
         <v>339</v>
       </c>
       <c r="D412" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -33764,13 +33764,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EABC2A8-EEA7-4F06-8F65-4AD332C8182E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB58F01-7E0D-43F3-9CD4-21F504940C2E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E58779A9-1103-46FB-8604-9EE9EEFA3973}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2C03D94-86AD-4025-992C-7C7F528A7A74}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D817C7A-D0E6-45B4-B07C-D76F1F692008}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0D37EE6-D292-42A5-8AB9-296F48436B89}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -33764,13 +33764,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB58F01-7E0D-43F3-9CD4-21F504940C2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87B07041-14C6-4BF3-BFF2-FFF6C03FFDE0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2C03D94-86AD-4025-992C-7C7F528A7A74}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29FB93F5-31ED-41BC-98C3-D3C26798F0AE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0D37EE6-D292-42A5-8AB9-296F48436B89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18A0FA12-5BDB-4376-A762-F5DE8AFDFDCF}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -5532,7 +5532,7 @@
         <v>54</v>
       </c>
       <c r="D291" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5574,7 +5574,7 @@
         <v>72</v>
       </c>
       <c r="D294" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5658,7 +5658,7 @@
         <v>102</v>
       </c>
       <c r="D300" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5700,7 +5700,7 @@
         <v>107</v>
       </c>
       <c r="D303" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5770,7 +5770,7 @@
         <v>125</v>
       </c>
       <c r="D308" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5840,7 +5840,7 @@
         <v>135</v>
       </c>
       <c r="D313" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5868,7 +5868,7 @@
         <v>139</v>
       </c>
       <c r="D315" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5938,7 +5938,7 @@
         <v>148</v>
       </c>
       <c r="D320" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5952,7 +5952,7 @@
         <v>151</v>
       </c>
       <c r="D321" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5980,7 +5980,7 @@
         <v>159</v>
       </c>
       <c r="D323" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6064,7 +6064,7 @@
         <v>171</v>
       </c>
       <c r="D329" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6106,7 +6106,7 @@
         <v>174</v>
       </c>
       <c r="D332" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6176,7 +6176,7 @@
         <v>186</v>
       </c>
       <c r="D337" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6484,7 +6484,7 @@
         <v>288</v>
       </c>
       <c r="D359" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6526,7 +6526,7 @@
         <v>291</v>
       </c>
       <c r="D362" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6582,7 +6582,7 @@
         <v>294</v>
       </c>
       <c r="D366" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -33764,13 +33764,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87B07041-14C6-4BF3-BFF2-FFF6C03FFDE0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA67A950-D38E-4B3D-AD66-A9D194AAF3E4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29FB93F5-31ED-41BC-98C3-D3C26798F0AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3071079B-505C-4255-A63B-D56C908774DC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18A0FA12-5BDB-4376-A762-F5DE8AFDFDCF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B9E172F-62A9-4969-BE0F-FF1CF03E717C}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -5392,7 +5392,7 @@
         <v>19</v>
       </c>
       <c r="D281" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5504,7 +5504,7 @@
         <v>50</v>
       </c>
       <c r="D289" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5742,7 +5742,7 @@
         <v>122</v>
       </c>
       <c r="D306" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5812,7 +5812,7 @@
         <v>128</v>
       </c>
       <c r="D311" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -6120,7 +6120,7 @@
         <v>175</v>
       </c>
       <c r="D333" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6204,7 +6204,7 @@
         <v>193</v>
       </c>
       <c r="D339" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6246,7 +6246,7 @@
         <v>208</v>
       </c>
       <c r="D342" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6260,7 +6260,7 @@
         <v>209</v>
       </c>
       <c r="D343" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6302,7 +6302,7 @@
         <v>230</v>
       </c>
       <c r="D346" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6358,7 +6358,7 @@
         <v>260</v>
       </c>
       <c r="D350" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6988,7 +6988,7 @@
         <v>322</v>
       </c>
       <c r="D395" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7002,7 +7002,7 @@
         <v>323</v>
       </c>
       <c r="D396" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7016,7 +7016,7 @@
         <v>324</v>
       </c>
       <c r="D397" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7030,7 +7030,7 @@
         <v>325</v>
       </c>
       <c r="D398" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7044,7 +7044,7 @@
         <v>326</v>
       </c>
       <c r="D399" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7058,7 +7058,7 @@
         <v>327</v>
       </c>
       <c r="D400" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7072,7 +7072,7 @@
         <v>328</v>
       </c>
       <c r="D401" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7086,7 +7086,7 @@
         <v>329</v>
       </c>
       <c r="D402" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7100,7 +7100,7 @@
         <v>330</v>
       </c>
       <c r="D403" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7128,7 +7128,7 @@
         <v>332</v>
       </c>
       <c r="D405" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7142,7 +7142,7 @@
         <v>333</v>
       </c>
       <c r="D406" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7156,7 +7156,7 @@
         <v>334</v>
       </c>
       <c r="D407" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7170,7 +7170,7 @@
         <v>335</v>
       </c>
       <c r="D408" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7184,7 +7184,7 @@
         <v>336</v>
       </c>
       <c r="D409" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7198,7 +7198,7 @@
         <v>337</v>
       </c>
       <c r="D410" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7226,7 +7226,7 @@
         <v>339</v>
       </c>
       <c r="D412" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -33764,13 +33764,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA67A950-D38E-4B3D-AD66-A9D194AAF3E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9866B1EF-3823-4132-A163-728D7CF78D88}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3071079B-505C-4255-A63B-D56C908774DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E61B77E1-6412-40E0-8E85-3919EFF8E9A7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B9E172F-62A9-4969-BE0F-FF1CF03E717C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{826A87F8-0FAC-4D76-A5E7-E84D7B1F8BC4}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4580" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4826" uniqueCount="363">
   <si>
     <t>Month</t>
   </si>
@@ -1091,6 +1091,9 @@
   </si>
   <si>
     <t>May-25</t>
+  </si>
+  <si>
+    <t>May-26</t>
   </si>
   <si>
     <t>Nov-25</t>
@@ -1161,8 +1164,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:D2289" totalsRowShown="0">
-  <autoFilter ref="A1:D2289"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:D2412" totalsRowShown="0">
+  <autoFilter ref="A1:D2412"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Month" dataDxfId="0"/>
     <tableColumn id="2" name="EID" dataDxfId="1"/>
@@ -1458,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2289"/>
+  <dimension ref="A1:D2412"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5364,7 +5367,7 @@
         <v>6</v>
       </c>
       <c r="D279" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5448,7 +5451,7 @@
         <v>29</v>
       </c>
       <c r="D285" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5462,7 +5465,7 @@
         <v>283</v>
       </c>
       <c r="D286" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5476,7 +5479,7 @@
         <v>48</v>
       </c>
       <c r="D287" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5490,7 +5493,7 @@
         <v>49</v>
       </c>
       <c r="D288" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5504,7 +5507,7 @@
         <v>50</v>
       </c>
       <c r="D289" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5728,7 +5731,7 @@
         <v>284</v>
       </c>
       <c r="D305" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -6106,7 +6109,7 @@
         <v>174</v>
       </c>
       <c r="D332" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6134,7 +6137,7 @@
         <v>177</v>
       </c>
       <c r="D334" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6190,7 +6193,7 @@
         <v>189</v>
       </c>
       <c r="D338" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6442,7 +6445,7 @@
         <v>285</v>
       </c>
       <c r="D356" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6456,7 +6459,7 @@
         <v>286</v>
       </c>
       <c r="D357" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6526,7 +6529,7 @@
         <v>291</v>
       </c>
       <c r="D362" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6554,7 +6557,7 @@
         <v>292</v>
       </c>
       <c r="D364" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6568,7 +6571,7 @@
         <v>293</v>
       </c>
       <c r="D365" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6596,7 +6599,7 @@
         <v>130</v>
       </c>
       <c r="D367" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6610,7 +6613,7 @@
         <v>295</v>
       </c>
       <c r="D368" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6680,7 +6683,7 @@
         <v>300</v>
       </c>
       <c r="D373" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -7058,7 +7061,7 @@
         <v>327</v>
       </c>
       <c r="D400" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7142,7 +7145,7 @@
         <v>333</v>
       </c>
       <c r="D406" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7184,7 +7187,7 @@
         <v>336</v>
       </c>
       <c r="D409" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -27022,7 +27025,7 @@
         <v>6</v>
       </c>
       <c r="D1826" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1827" spans="1:4">
@@ -27036,7 +27039,7 @@
         <v>7</v>
       </c>
       <c r="D1827" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1828" spans="1:4">
@@ -27044,13 +27047,13 @@
         <v>359</v>
       </c>
       <c r="B1828" s="2">
-        <v>102211179</v>
+        <v>102369579</v>
       </c>
       <c r="C1828" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D1828" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1829" spans="1:4">
@@ -27058,13 +27061,13 @@
         <v>359</v>
       </c>
       <c r="B1829" s="2">
-        <v>102219144</v>
+        <v>102370804</v>
       </c>
       <c r="C1829" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D1829" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1830" spans="1:4">
@@ -27072,13 +27075,13 @@
         <v>359</v>
       </c>
       <c r="B1830" s="2">
-        <v>102326882</v>
+        <v>102371964</v>
       </c>
       <c r="C1830" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D1830" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1831" spans="1:4">
@@ -27086,13 +27089,13 @@
         <v>359</v>
       </c>
       <c r="B1831" s="2">
-        <v>102343359</v>
+        <v>102456984</v>
       </c>
       <c r="C1831" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D1831" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1832" spans="1:4">
@@ -27100,13 +27103,13 @@
         <v>359</v>
       </c>
       <c r="B1832" s="2">
-        <v>102369579</v>
+        <v>102456993</v>
       </c>
       <c r="C1832" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D1832" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1833" spans="1:4">
@@ -27114,13 +27117,13 @@
         <v>359</v>
       </c>
       <c r="B1833" s="2">
-        <v>102370804</v>
+        <v>102458990</v>
       </c>
       <c r="C1833" s="1" t="s">
-        <v>22</v>
+        <v>283</v>
       </c>
       <c r="D1833" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1834" spans="1:4">
@@ -27128,13 +27131,13 @@
         <v>359</v>
       </c>
       <c r="B1834" s="2">
-        <v>102371964</v>
+        <v>102477293</v>
       </c>
       <c r="C1834" s="1" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D1834" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1835" spans="1:4">
@@ -27142,13 +27145,13 @@
         <v>359</v>
       </c>
       <c r="B1835" s="2">
-        <v>102456914</v>
+        <v>102477371</v>
       </c>
       <c r="C1835" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D1835" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1836" spans="1:4">
@@ -27156,13 +27159,13 @@
         <v>359</v>
       </c>
       <c r="B1836" s="2">
-        <v>102456984</v>
+        <v>102477422</v>
       </c>
       <c r="C1836" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D1836" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1837" spans="1:4">
@@ -27170,13 +27173,13 @@
         <v>359</v>
       </c>
       <c r="B1837" s="2">
-        <v>102456993</v>
+        <v>102477510</v>
       </c>
       <c r="C1837" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1837" s="2">
         <v>29</v>
-      </c>
-      <c r="D1837" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="1838" spans="1:4">
@@ -27184,13 +27187,13 @@
         <v>359</v>
       </c>
       <c r="B1838" s="2">
-        <v>102457937</v>
+        <v>102478278</v>
       </c>
       <c r="C1838" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D1838" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1839" spans="1:4">
@@ -27198,13 +27201,13 @@
         <v>359</v>
       </c>
       <c r="B1839" s="2">
-        <v>102458550</v>
+        <v>102482237</v>
       </c>
       <c r="C1839" s="1" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D1839" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1840" spans="1:4">
@@ -27212,13 +27215,13 @@
         <v>359</v>
       </c>
       <c r="B1840" s="2">
-        <v>102464498</v>
+        <v>102484482</v>
       </c>
       <c r="C1840" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D1840" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1841" spans="1:4">
@@ -27226,13 +27229,13 @@
         <v>359</v>
       </c>
       <c r="B1841" s="2">
-        <v>102477288</v>
+        <v>102509109</v>
       </c>
       <c r="C1841" s="1" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="D1841" s="2">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1842" spans="1:4">
@@ -27240,13 +27243,13 @@
         <v>359</v>
       </c>
       <c r="B1842" s="2">
-        <v>102477293</v>
+        <v>102517346</v>
       </c>
       <c r="C1842" s="1" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="D1842" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1843" spans="1:4">
@@ -27254,13 +27257,13 @@
         <v>359</v>
       </c>
       <c r="B1843" s="2">
-        <v>102477371</v>
+        <v>102830253</v>
       </c>
       <c r="C1843" s="1" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D1843" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1844" spans="1:4">
@@ -27268,13 +27271,13 @@
         <v>359</v>
       </c>
       <c r="B1844" s="2">
-        <v>102477422</v>
+        <v>102830316</v>
       </c>
       <c r="C1844" s="1" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="D1844" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1845" spans="1:4">
@@ -27282,13 +27285,13 @@
         <v>359</v>
       </c>
       <c r="B1845" s="2">
-        <v>102477510</v>
+        <v>102831065</v>
       </c>
       <c r="C1845" s="1" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="D1845" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1846" spans="1:4">
@@ -27296,13 +27299,13 @@
         <v>359</v>
       </c>
       <c r="B1846" s="2">
-        <v>102478278</v>
+        <v>102843519</v>
       </c>
       <c r="C1846" s="1" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="D1846" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1847" spans="1:4">
@@ -27310,13 +27313,13 @@
         <v>359</v>
       </c>
       <c r="B1847" s="2">
-        <v>102482237</v>
+        <v>102855952</v>
       </c>
       <c r="C1847" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="D1847" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1848" spans="1:4">
@@ -27324,13 +27327,13 @@
         <v>359</v>
       </c>
       <c r="B1848" s="2">
-        <v>102484482</v>
+        <v>102864715</v>
       </c>
       <c r="C1848" s="1" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="D1848" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1849" spans="1:4">
@@ -27338,13 +27341,13 @@
         <v>359</v>
       </c>
       <c r="B1849" s="2">
-        <v>102502720</v>
+        <v>102871040</v>
       </c>
       <c r="C1849" s="1" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="D1849" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1850" spans="1:4">
@@ -27352,13 +27355,13 @@
         <v>359</v>
       </c>
       <c r="B1850" s="2">
-        <v>102502737</v>
+        <v>102884064</v>
       </c>
       <c r="C1850" s="1" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="D1850" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1851" spans="1:4">
@@ -27366,13 +27369,13 @@
         <v>359</v>
       </c>
       <c r="B1851" s="2">
-        <v>102502871</v>
+        <v>102884675</v>
       </c>
       <c r="C1851" s="1" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="D1851" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1852" spans="1:4">
@@ -27380,13 +27383,13 @@
         <v>359</v>
       </c>
       <c r="B1852" s="2">
-        <v>102503478</v>
+        <v>103002947</v>
       </c>
       <c r="C1852" s="1" t="s">
-        <v>68</v>
+        <v>284</v>
       </c>
       <c r="D1852" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1853" spans="1:4">
@@ -27394,13 +27397,13 @@
         <v>359</v>
       </c>
       <c r="B1853" s="2">
-        <v>102507584</v>
+        <v>103060430</v>
       </c>
       <c r="C1853" s="1" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="D1853" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1854" spans="1:4">
@@ -27408,13 +27411,13 @@
         <v>359</v>
       </c>
       <c r="B1854" s="2">
-        <v>102509109</v>
+        <v>103060435</v>
       </c>
       <c r="C1854" s="1" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="D1854" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1855" spans="1:4">
@@ -27422,13 +27425,13 @@
         <v>359</v>
       </c>
       <c r="B1855" s="2">
-        <v>102511945</v>
+        <v>103060453</v>
       </c>
       <c r="C1855" s="1" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="D1855" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1856" spans="1:4">
@@ -27436,13 +27439,13 @@
         <v>359</v>
       </c>
       <c r="B1856" s="2">
-        <v>102517333</v>
+        <v>103060459</v>
       </c>
       <c r="C1856" s="1" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="D1856" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1857" spans="1:4">
@@ -27450,13 +27453,13 @@
         <v>359</v>
       </c>
       <c r="B1857" s="2">
-        <v>102517346</v>
+        <v>103060467</v>
       </c>
       <c r="C1857" s="1" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D1857" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1858" spans="1:4">
@@ -27464,13 +27467,13 @@
         <v>359</v>
       </c>
       <c r="B1858" s="2">
-        <v>102821757</v>
+        <v>103060471</v>
       </c>
       <c r="C1858" s="1" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="D1858" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1859" spans="1:4">
@@ -27478,13 +27481,13 @@
         <v>359</v>
       </c>
       <c r="B1859" s="2">
-        <v>102830253</v>
+        <v>103082112</v>
       </c>
       <c r="C1859" s="1" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="D1859" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1860" spans="1:4">
@@ -27492,13 +27495,13 @@
         <v>359</v>
       </c>
       <c r="B1860" s="2">
-        <v>102830316</v>
+        <v>103082113</v>
       </c>
       <c r="C1860" s="1" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="D1860" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1861" spans="1:4">
@@ -27506,13 +27509,13 @@
         <v>359</v>
       </c>
       <c r="B1861" s="2">
-        <v>102831065</v>
+        <v>103082121</v>
       </c>
       <c r="C1861" s="1" t="s">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="D1861" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1862" spans="1:4">
@@ -27520,13 +27523,13 @@
         <v>359</v>
       </c>
       <c r="B1862" s="2">
-        <v>102843519</v>
+        <v>103085298</v>
       </c>
       <c r="C1862" s="1" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="D1862" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1863" spans="1:4">
@@ -27534,13 +27537,13 @@
         <v>359</v>
       </c>
       <c r="B1863" s="2">
-        <v>102855952</v>
+        <v>103092092</v>
       </c>
       <c r="C1863" s="1" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="D1863" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1864" spans="1:4">
@@ -27548,13 +27551,13 @@
         <v>359</v>
       </c>
       <c r="B1864" s="2">
-        <v>102864715</v>
+        <v>103092310</v>
       </c>
       <c r="C1864" s="1" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="D1864" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1865" spans="1:4">
@@ -27562,13 +27565,13 @@
         <v>359</v>
       </c>
       <c r="B1865" s="2">
-        <v>102871040</v>
+        <v>103101206</v>
       </c>
       <c r="C1865" s="1" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="D1865" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1866" spans="1:4">
@@ -27576,13 +27579,13 @@
         <v>359</v>
       </c>
       <c r="B1866" s="2">
-        <v>102879799</v>
+        <v>103103198</v>
       </c>
       <c r="C1866" s="1" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="D1866" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1867" spans="1:4">
@@ -27590,13 +27593,13 @@
         <v>359</v>
       </c>
       <c r="B1867" s="2">
-        <v>102884064</v>
+        <v>103103213</v>
       </c>
       <c r="C1867" s="1" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="D1867" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1868" spans="1:4">
@@ -27604,13 +27607,13 @@
         <v>359</v>
       </c>
       <c r="B1868" s="2">
-        <v>102884675</v>
+        <v>103105143</v>
       </c>
       <c r="C1868" s="1" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D1868" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1869" spans="1:4">
@@ -27618,13 +27621,13 @@
         <v>359</v>
       </c>
       <c r="B1869" s="2">
-        <v>102908267</v>
+        <v>103109089</v>
       </c>
       <c r="C1869" s="1" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="D1869" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1870" spans="1:4">
@@ -27632,13 +27635,13 @@
         <v>359</v>
       </c>
       <c r="B1870" s="2">
-        <v>103028093</v>
+        <v>103109136</v>
       </c>
       <c r="C1870" s="1" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="D1870" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1871" spans="1:4">
@@ -27646,13 +27649,13 @@
         <v>359</v>
       </c>
       <c r="B1871" s="2">
-        <v>103060430</v>
+        <v>103109151</v>
       </c>
       <c r="C1871" s="1" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="D1871" s="2">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1872" spans="1:4">
@@ -27660,13 +27663,13 @@
         <v>359</v>
       </c>
       <c r="B1872" s="2">
-        <v>103060435</v>
+        <v>103109336</v>
       </c>
       <c r="C1872" s="1" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="D1872" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1873" spans="1:4">
@@ -27674,13 +27677,13 @@
         <v>359</v>
       </c>
       <c r="B1873" s="2">
-        <v>103060453</v>
+        <v>103109339</v>
       </c>
       <c r="C1873" s="1" t="s">
-        <v>125</v>
+        <v>173</v>
       </c>
       <c r="D1873" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1874" spans="1:4">
@@ -27688,13 +27691,13 @@
         <v>359</v>
       </c>
       <c r="B1874" s="2">
-        <v>103060459</v>
+        <v>103109343</v>
       </c>
       <c r="C1874" s="1" t="s">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="D1874" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1875" spans="1:4">
@@ -27702,13 +27705,13 @@
         <v>359</v>
       </c>
       <c r="B1875" s="2">
-        <v>103060462</v>
+        <v>103109357</v>
       </c>
       <c r="C1875" s="1" t="s">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="D1875" s="2">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1876" spans="1:4">
@@ -27716,13 +27719,13 @@
         <v>359</v>
       </c>
       <c r="B1876" s="2">
-        <v>103060467</v>
+        <v>103110013</v>
       </c>
       <c r="C1876" s="1" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="D1876" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1877" spans="1:4">
@@ -27730,13 +27733,13 @@
         <v>359</v>
       </c>
       <c r="B1877" s="2">
-        <v>103060471</v>
+        <v>103111956</v>
       </c>
       <c r="C1877" s="1" t="s">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="D1877" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1878" spans="1:4">
@@ -27744,13 +27747,13 @@
         <v>359</v>
       </c>
       <c r="B1878" s="2">
-        <v>103082092</v>
+        <v>103113926</v>
       </c>
       <c r="C1878" s="1" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
       <c r="D1878" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1879" spans="1:4">
@@ -27758,13 +27761,13 @@
         <v>359</v>
       </c>
       <c r="B1879" s="2">
-        <v>103082095</v>
+        <v>103116487</v>
       </c>
       <c r="C1879" s="1" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="D1879" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1880" spans="1:4">
@@ -27772,13 +27775,13 @@
         <v>359</v>
       </c>
       <c r="B1880" s="2">
-        <v>103082112</v>
+        <v>103117188</v>
       </c>
       <c r="C1880" s="1" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="D1880" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1881" spans="1:4">
@@ -27786,13 +27789,13 @@
         <v>359</v>
       </c>
       <c r="B1881" s="2">
-        <v>103082113</v>
+        <v>103121097</v>
       </c>
       <c r="C1881" s="1" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="D1881" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1882" spans="1:4">
@@ -27800,13 +27803,13 @@
         <v>359</v>
       </c>
       <c r="B1882" s="2">
-        <v>103082118</v>
+        <v>103121098</v>
       </c>
       <c r="C1882" s="1" t="s">
-        <v>137</v>
+        <v>194</v>
       </c>
       <c r="D1882" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1883" spans="1:4">
@@ -27814,13 +27817,13 @@
         <v>359</v>
       </c>
       <c r="B1883" s="2">
-        <v>103082121</v>
+        <v>103125208</v>
       </c>
       <c r="C1883" s="1" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="D1883" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1884" spans="1:4">
@@ -27828,13 +27831,13 @@
         <v>359</v>
       </c>
       <c r="B1884" s="2">
-        <v>103082161</v>
+        <v>103125228</v>
       </c>
       <c r="C1884" s="1" t="s">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="D1884" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1885" spans="1:4">
@@ -27842,13 +27845,13 @@
         <v>359</v>
       </c>
       <c r="B1885" s="2">
-        <v>103082166</v>
+        <v>103125229</v>
       </c>
       <c r="C1885" s="1" t="s">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="D1885" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1886" spans="1:4">
@@ -27856,13 +27859,13 @@
         <v>359</v>
       </c>
       <c r="B1886" s="2">
-        <v>103082385</v>
+        <v>103130519</v>
       </c>
       <c r="C1886" s="1" t="s">
-        <v>144</v>
+        <v>226</v>
       </c>
       <c r="D1886" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1887" spans="1:4">
@@ -27870,13 +27873,13 @@
         <v>359</v>
       </c>
       <c r="B1887" s="2">
-        <v>103085298</v>
+        <v>103132423</v>
       </c>
       <c r="C1887" s="1" t="s">
-        <v>145</v>
+        <v>229</v>
       </c>
       <c r="D1887" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1888" spans="1:4">
@@ -27884,13 +27887,13 @@
         <v>359</v>
       </c>
       <c r="B1888" s="2">
-        <v>103088009</v>
+        <v>103132424</v>
       </c>
       <c r="C1888" s="1" t="s">
-        <v>146</v>
+        <v>230</v>
       </c>
       <c r="D1888" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1889" spans="1:4">
@@ -27898,13 +27901,13 @@
         <v>359</v>
       </c>
       <c r="B1889" s="2">
-        <v>103092092</v>
+        <v>103133036</v>
       </c>
       <c r="C1889" s="1" t="s">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="D1889" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1890" spans="1:4">
@@ -27912,13 +27915,13 @@
         <v>359</v>
       </c>
       <c r="B1890" s="2">
-        <v>103092310</v>
+        <v>103139871</v>
       </c>
       <c r="C1890" s="1" t="s">
-        <v>151</v>
+        <v>246</v>
       </c>
       <c r="D1890" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1891" spans="1:4">
@@ -27926,13 +27929,13 @@
         <v>359</v>
       </c>
       <c r="B1891" s="2">
-        <v>103092316</v>
+        <v>103169795</v>
       </c>
       <c r="C1891" s="1" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="D1891" s="2">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1892" spans="1:4">
@@ -27940,13 +27943,13 @@
         <v>359</v>
       </c>
       <c r="B1892" s="2">
-        <v>103101206</v>
+        <v>103169797</v>
       </c>
       <c r="C1892" s="1" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="D1892" s="2">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1893" spans="1:4">
@@ -27954,13 +27957,13 @@
         <v>359</v>
       </c>
       <c r="B1893" s="2">
-        <v>103103196</v>
+        <v>103169814</v>
       </c>
       <c r="C1893" s="1" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="D1893" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1894" spans="1:4">
@@ -27968,13 +27971,13 @@
         <v>359</v>
       </c>
       <c r="B1894" s="2">
-        <v>103103198</v>
+        <v>103169816</v>
       </c>
       <c r="C1894" s="1" t="s">
-        <v>159</v>
+        <v>263</v>
       </c>
       <c r="D1894" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1895" spans="1:4">
@@ -27982,13 +27985,13 @@
         <v>359</v>
       </c>
       <c r="B1895" s="2">
-        <v>103103213</v>
+        <v>103171103</v>
       </c>
       <c r="C1895" s="1" t="s">
-        <v>160</v>
+        <v>273</v>
       </c>
       <c r="D1895" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1896" spans="1:4">
@@ -27996,13 +27999,13 @@
         <v>359</v>
       </c>
       <c r="B1896" s="2">
-        <v>103105143</v>
+        <v>103173195</v>
       </c>
       <c r="C1896" s="1" t="s">
-        <v>162</v>
+        <v>276</v>
       </c>
       <c r="D1896" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1897" spans="1:4">
@@ -28010,13 +28013,13 @@
         <v>359</v>
       </c>
       <c r="B1897" s="2">
-        <v>103109089</v>
+        <v>103173197</v>
       </c>
       <c r="C1897" s="1" t="s">
-        <v>166</v>
+        <v>277</v>
       </c>
       <c r="D1897" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1898" spans="1:4">
@@ -28024,13 +28027,13 @@
         <v>359</v>
       </c>
       <c r="B1898" s="2">
-        <v>103109090</v>
+        <v>103177016</v>
       </c>
       <c r="C1898" s="1" t="s">
-        <v>167</v>
+        <v>285</v>
       </c>
       <c r="D1898" s="2">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1899" spans="1:4">
@@ -28038,13 +28041,13 @@
         <v>359</v>
       </c>
       <c r="B1899" s="2">
-        <v>103109091</v>
+        <v>103293732</v>
       </c>
       <c r="C1899" s="1" t="s">
-        <v>168</v>
+        <v>286</v>
       </c>
       <c r="D1899" s="2">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1900" spans="1:4">
@@ -28052,13 +28055,13 @@
         <v>359</v>
       </c>
       <c r="B1900" s="2">
-        <v>103109136</v>
+        <v>103293737</v>
       </c>
       <c r="C1900" s="1" t="s">
-        <v>170</v>
+        <v>287</v>
       </c>
       <c r="D1900" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1901" spans="1:4">
@@ -28066,13 +28069,13 @@
         <v>359</v>
       </c>
       <c r="B1901" s="2">
-        <v>103109151</v>
+        <v>103293751</v>
       </c>
       <c r="C1901" s="1" t="s">
-        <v>171</v>
+        <v>288</v>
       </c>
       <c r="D1901" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1902" spans="1:4">
@@ -28080,13 +28083,13 @@
         <v>359</v>
       </c>
       <c r="B1902" s="2">
-        <v>103109336</v>
+        <v>103293756</v>
       </c>
       <c r="C1902" s="1" t="s">
-        <v>172</v>
+        <v>289</v>
       </c>
       <c r="D1902" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1903" spans="1:4">
@@ -28094,13 +28097,13 @@
         <v>359</v>
       </c>
       <c r="B1903" s="2">
-        <v>103109339</v>
+        <v>103293766</v>
       </c>
       <c r="C1903" s="1" t="s">
-        <v>173</v>
+        <v>290</v>
       </c>
       <c r="D1903" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1904" spans="1:4">
@@ -28108,13 +28111,13 @@
         <v>359</v>
       </c>
       <c r="B1904" s="2">
-        <v>103109343</v>
+        <v>103293773</v>
       </c>
       <c r="C1904" s="1" t="s">
-        <v>174</v>
+        <v>291</v>
       </c>
       <c r="D1904" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1905" spans="1:4">
@@ -28122,13 +28125,13 @@
         <v>359</v>
       </c>
       <c r="B1905" s="2">
-        <v>103109357</v>
+        <v>103294755</v>
       </c>
       <c r="C1905" s="1" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="D1905" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1906" spans="1:4">
@@ -28136,13 +28139,13 @@
         <v>359</v>
       </c>
       <c r="B1906" s="2">
-        <v>103110013</v>
+        <v>103296160</v>
       </c>
       <c r="C1906" s="1" t="s">
-        <v>177</v>
+        <v>292</v>
       </c>
       <c r="D1906" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1907" spans="1:4">
@@ -28150,13 +28153,13 @@
         <v>359</v>
       </c>
       <c r="B1907" s="2">
-        <v>103111713</v>
+        <v>103297566</v>
       </c>
       <c r="C1907" s="1" t="s">
-        <v>180</v>
+        <v>293</v>
       </c>
       <c r="D1907" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1908" spans="1:4">
@@ -28164,13 +28167,13 @@
         <v>359</v>
       </c>
       <c r="B1908" s="2">
-        <v>103111956</v>
+        <v>103300418</v>
       </c>
       <c r="C1908" s="1" t="s">
-        <v>182</v>
+        <v>294</v>
       </c>
       <c r="D1908" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1909" spans="1:4">
@@ -28178,13 +28181,13 @@
         <v>359</v>
       </c>
       <c r="B1909" s="2">
-        <v>103113926</v>
+        <v>103304866</v>
       </c>
       <c r="C1909" s="1" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="D1909" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1910" spans="1:4">
@@ -28192,13 +28195,13 @@
         <v>359</v>
       </c>
       <c r="B1910" s="2">
-        <v>103115341</v>
+        <v>103304875</v>
       </c>
       <c r="C1910" s="1" t="s">
-        <v>184</v>
+        <v>295</v>
       </c>
       <c r="D1910" s="2">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1911" spans="1:4">
@@ -28206,13 +28209,13 @@
         <v>359</v>
       </c>
       <c r="B1911" s="2">
-        <v>103116487</v>
+        <v>103305150</v>
       </c>
       <c r="C1911" s="1" t="s">
-        <v>186</v>
+        <v>296</v>
       </c>
       <c r="D1911" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1912" spans="1:4">
@@ -28220,13 +28223,13 @@
         <v>359</v>
       </c>
       <c r="B1912" s="2">
-        <v>103116496</v>
+        <v>103548803</v>
       </c>
       <c r="C1912" s="1" t="s">
-        <v>187</v>
+        <v>300</v>
       </c>
       <c r="D1912" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1913" spans="1:4">
@@ -28234,13 +28237,13 @@
         <v>359</v>
       </c>
       <c r="B1913" s="2">
-        <v>103117188</v>
+        <v>103548811</v>
       </c>
       <c r="C1913" s="1" t="s">
-        <v>189</v>
+        <v>301</v>
       </c>
       <c r="D1913" s="2">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1914" spans="1:4">
@@ -28248,13 +28251,13 @@
         <v>359</v>
       </c>
       <c r="B1914" s="2">
-        <v>103121097</v>
+        <v>103548829</v>
       </c>
       <c r="C1914" s="1" t="s">
-        <v>193</v>
+        <v>302</v>
       </c>
       <c r="D1914" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1915" spans="1:4">
@@ -28262,13 +28265,13 @@
         <v>359</v>
       </c>
       <c r="B1915" s="2">
-        <v>103121098</v>
+        <v>103548830</v>
       </c>
       <c r="C1915" s="1" t="s">
-        <v>194</v>
+        <v>303</v>
       </c>
       <c r="D1915" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1916" spans="1:4">
@@ -28276,13 +28279,13 @@
         <v>359</v>
       </c>
       <c r="B1916" s="2">
-        <v>103125208</v>
+        <v>103548832</v>
       </c>
       <c r="C1916" s="1" t="s">
-        <v>206</v>
+        <v>304</v>
       </c>
       <c r="D1916" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1917" spans="1:4">
@@ -28290,13 +28293,13 @@
         <v>359</v>
       </c>
       <c r="B1917" s="2">
-        <v>103125228</v>
+        <v>103548833</v>
       </c>
       <c r="C1917" s="1" t="s">
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="D1917" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1918" spans="1:4">
@@ -28304,13 +28307,13 @@
         <v>359</v>
       </c>
       <c r="B1918" s="2">
-        <v>103125229</v>
+        <v>103548834</v>
       </c>
       <c r="C1918" s="1" t="s">
-        <v>209</v>
+        <v>306</v>
       </c>
       <c r="D1918" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1919" spans="1:4">
@@ -28318,13 +28321,13 @@
         <v>359</v>
       </c>
       <c r="B1919" s="2">
-        <v>103127936</v>
+        <v>103548839</v>
       </c>
       <c r="C1919" s="1" t="s">
-        <v>211</v>
+        <v>307</v>
       </c>
       <c r="D1919" s="2">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1920" spans="1:4">
@@ -28332,13 +28335,13 @@
         <v>359</v>
       </c>
       <c r="B1920" s="2">
-        <v>103130519</v>
+        <v>103548841</v>
       </c>
       <c r="C1920" s="1" t="s">
-        <v>226</v>
+        <v>308</v>
       </c>
       <c r="D1920" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1921" spans="1:4">
@@ -28346,13 +28349,13 @@
         <v>359</v>
       </c>
       <c r="B1921" s="2">
-        <v>103132423</v>
+        <v>103548843</v>
       </c>
       <c r="C1921" s="1" t="s">
-        <v>229</v>
+        <v>309</v>
       </c>
       <c r="D1921" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1922" spans="1:4">
@@ -28360,13 +28363,13 @@
         <v>359</v>
       </c>
       <c r="B1922" s="2">
-        <v>103132424</v>
+        <v>103548848</v>
       </c>
       <c r="C1922" s="1" t="s">
-        <v>230</v>
+        <v>310</v>
       </c>
       <c r="D1922" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1923" spans="1:4">
@@ -28374,13 +28377,13 @@
         <v>359</v>
       </c>
       <c r="B1923" s="2">
-        <v>103133036</v>
+        <v>103548851</v>
       </c>
       <c r="C1923" s="1" t="s">
-        <v>235</v>
+        <v>312</v>
       </c>
       <c r="D1923" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1924" spans="1:4">
@@ -28388,13 +28391,13 @@
         <v>359</v>
       </c>
       <c r="B1924" s="2">
-        <v>103136107</v>
+        <v>103548859</v>
       </c>
       <c r="C1924" s="1" t="s">
-        <v>242</v>
+        <v>313</v>
       </c>
       <c r="D1924" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1925" spans="1:4">
@@ -28402,13 +28405,13 @@
         <v>359</v>
       </c>
       <c r="B1925" s="2">
-        <v>103139871</v>
+        <v>103548862</v>
       </c>
       <c r="C1925" s="1" t="s">
-        <v>246</v>
+        <v>314</v>
       </c>
       <c r="D1925" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1926" spans="1:4">
@@ -28416,13 +28419,13 @@
         <v>359</v>
       </c>
       <c r="B1926" s="2">
-        <v>103145144</v>
+        <v>103548863</v>
       </c>
       <c r="C1926" s="1" t="s">
-        <v>252</v>
+        <v>315</v>
       </c>
       <c r="D1926" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1927" spans="1:4">
@@ -28430,13 +28433,13 @@
         <v>359</v>
       </c>
       <c r="B1927" s="2">
-        <v>103169793</v>
+        <v>103548864</v>
       </c>
       <c r="C1927" s="1" t="s">
-        <v>258</v>
+        <v>316</v>
       </c>
       <c r="D1927" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1928" spans="1:4">
@@ -28444,13 +28447,13 @@
         <v>359</v>
       </c>
       <c r="B1928" s="2">
-        <v>103169795</v>
+        <v>103550259</v>
       </c>
       <c r="C1928" s="1" t="s">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="D1928" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1929" spans="1:4">
@@ -28458,13 +28461,13 @@
         <v>359</v>
       </c>
       <c r="B1929" s="2">
-        <v>103169797</v>
+        <v>103550260</v>
       </c>
       <c r="C1929" s="1" t="s">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c r="D1929" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1930" spans="1:4">
@@ -28472,13 +28475,13 @@
         <v>359</v>
       </c>
       <c r="B1930" s="2">
-        <v>103169814</v>
+        <v>103550261</v>
       </c>
       <c r="C1930" s="1" t="s">
-        <v>262</v>
+        <v>319</v>
       </c>
       <c r="D1930" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1931" spans="1:4">
@@ -28486,13 +28489,13 @@
         <v>359</v>
       </c>
       <c r="B1931" s="2">
-        <v>103169816</v>
+        <v>103550262</v>
       </c>
       <c r="C1931" s="1" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="D1931" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1932" spans="1:4">
@@ -28500,13 +28503,13 @@
         <v>359</v>
       </c>
       <c r="B1932" s="2">
-        <v>103171103</v>
+        <v>103550263</v>
       </c>
       <c r="C1932" s="1" t="s">
-        <v>273</v>
+        <v>321</v>
       </c>
       <c r="D1932" s="2">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1933" spans="1:4">
@@ -28514,13 +28517,13 @@
         <v>359</v>
       </c>
       <c r="B1933" s="2">
-        <v>103173195</v>
+        <v>103559008</v>
       </c>
       <c r="C1933" s="1" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="D1933" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1934" spans="1:4">
@@ -28528,13 +28531,13 @@
         <v>359</v>
       </c>
       <c r="B1934" s="2">
-        <v>103173197</v>
+        <v>103559011</v>
       </c>
       <c r="C1934" s="1" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="D1934" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1935" spans="1:4">
@@ -28542,13 +28545,13 @@
         <v>359</v>
       </c>
       <c r="B1935" s="2">
-        <v>103283831</v>
+        <v>103559012</v>
       </c>
       <c r="C1935" s="1" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="D1935" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1936" spans="1:4">
@@ -28556,13 +28559,13 @@
         <v>359</v>
       </c>
       <c r="B1936" s="2">
-        <v>103293732</v>
+        <v>103559014</v>
       </c>
       <c r="C1936" s="1" t="s">
-        <v>286</v>
+        <v>325</v>
       </c>
       <c r="D1936" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1937" spans="1:4">
@@ -28570,13 +28573,13 @@
         <v>359</v>
       </c>
       <c r="B1937" s="2">
-        <v>103293737</v>
+        <v>103559271</v>
       </c>
       <c r="C1937" s="1" t="s">
-        <v>287</v>
+        <v>326</v>
       </c>
       <c r="D1937" s="2">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1938" spans="1:4">
@@ -28584,13 +28587,13 @@
         <v>359</v>
       </c>
       <c r="B1938" s="2">
-        <v>103293745</v>
+        <v>103559274</v>
       </c>
       <c r="C1938" s="1" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="D1938" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1939" spans="1:4">
@@ -28598,13 +28601,13 @@
         <v>359</v>
       </c>
       <c r="B1939" s="2">
-        <v>103293751</v>
+        <v>103559275</v>
       </c>
       <c r="C1939" s="1" t="s">
-        <v>288</v>
+        <v>328</v>
       </c>
       <c r="D1939" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1940" spans="1:4">
@@ -28612,13 +28615,13 @@
         <v>359</v>
       </c>
       <c r="B1940" s="2">
-        <v>103293756</v>
+        <v>103559276</v>
       </c>
       <c r="C1940" s="1" t="s">
-        <v>289</v>
+        <v>329</v>
       </c>
       <c r="D1940" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1941" spans="1:4">
@@ -28626,13 +28629,13 @@
         <v>359</v>
       </c>
       <c r="B1941" s="2">
-        <v>103293766</v>
+        <v>103559278</v>
       </c>
       <c r="C1941" s="1" t="s">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="D1941" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1942" spans="1:4">
@@ -28640,13 +28643,13 @@
         <v>359</v>
       </c>
       <c r="B1942" s="2">
-        <v>103293773</v>
+        <v>103559293</v>
       </c>
       <c r="C1942" s="1" t="s">
-        <v>291</v>
+        <v>332</v>
       </c>
       <c r="D1942" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1943" spans="1:4">
@@ -28654,13 +28657,13 @@
         <v>359</v>
       </c>
       <c r="B1943" s="2">
-        <v>103294755</v>
+        <v>103559300</v>
       </c>
       <c r="C1943" s="1" t="s">
-        <v>150</v>
+        <v>333</v>
       </c>
       <c r="D1943" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1944" spans="1:4">
@@ -28668,13 +28671,13 @@
         <v>359</v>
       </c>
       <c r="B1944" s="2">
-        <v>103296160</v>
+        <v>103559310</v>
       </c>
       <c r="C1944" s="1" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="D1944" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1945" spans="1:4">
@@ -28682,13 +28685,13 @@
         <v>359</v>
       </c>
       <c r="B1945" s="2">
-        <v>103296167</v>
+        <v>103559312</v>
       </c>
       <c r="C1945" s="1" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D1945" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1946" spans="1:4">
@@ -28696,13 +28699,13 @@
         <v>359</v>
       </c>
       <c r="B1946" s="2">
-        <v>103297566</v>
+        <v>103560295</v>
       </c>
       <c r="C1946" s="1" t="s">
-        <v>293</v>
+        <v>336</v>
       </c>
       <c r="D1946" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1947" spans="1:4">
@@ -28710,13 +28713,13 @@
         <v>359</v>
       </c>
       <c r="B1947" s="2">
-        <v>103300418</v>
+        <v>103560298</v>
       </c>
       <c r="C1947" s="1" t="s">
-        <v>294</v>
+        <v>337</v>
       </c>
       <c r="D1947" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1948" spans="1:4">
@@ -28724,125 +28727,125 @@
         <v>359</v>
       </c>
       <c r="B1948" s="2">
-        <v>103304841</v>
+        <v>103560998</v>
       </c>
       <c r="C1948" s="1" t="s">
-        <v>290</v>
+        <v>339</v>
       </c>
       <c r="D1948" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1949" spans="1:4">
       <c r="A1949" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1949" s="2">
-        <v>103304846</v>
+        <v>102029874</v>
       </c>
       <c r="C1949" s="1" t="s">
-        <v>348</v>
+        <v>6</v>
       </c>
       <c r="D1949" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1950" spans="1:4">
       <c r="A1950" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1950" s="2">
-        <v>103304863</v>
+        <v>102173363</v>
       </c>
       <c r="C1950" s="1" t="s">
-        <v>349</v>
+        <v>7</v>
       </c>
       <c r="D1950" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1951" spans="1:4">
       <c r="A1951" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1951" s="2">
-        <v>103304866</v>
+        <v>102211179</v>
       </c>
       <c r="C1951" s="1" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="D1951" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1952" spans="1:4">
       <c r="A1952" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1952" s="2">
-        <v>103304875</v>
+        <v>102219144</v>
       </c>
       <c r="C1952" s="1" t="s">
-        <v>295</v>
+        <v>12</v>
       </c>
       <c r="D1952" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1953" spans="1:4">
       <c r="A1953" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1953" s="2">
-        <v>103305150</v>
+        <v>102326882</v>
       </c>
       <c r="C1953" s="1" t="s">
-        <v>296</v>
+        <v>16</v>
       </c>
       <c r="D1953" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1954" spans="1:4">
       <c r="A1954" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1954" s="2">
-        <v>103305154</v>
+        <v>102343359</v>
       </c>
       <c r="C1954" s="1" t="s">
-        <v>297</v>
+        <v>17</v>
       </c>
       <c r="D1954" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1955" spans="1:4">
       <c r="A1955" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1955" s="2">
-        <v>103305160</v>
+        <v>102369579</v>
       </c>
       <c r="C1955" s="1" t="s">
-        <v>298</v>
+        <v>19</v>
       </c>
       <c r="D1955" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1956" spans="1:4">
       <c r="A1956" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1956" s="2">
-        <v>103305165</v>
+        <v>102370804</v>
       </c>
       <c r="C1956" s="1" t="s">
-        <v>299</v>
+        <v>22</v>
       </c>
       <c r="D1956" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1957" spans="1:4">
@@ -28850,13 +28853,13 @@
         <v>360</v>
       </c>
       <c r="B1957" s="2">
-        <v>102029874</v>
+        <v>102371964</v>
       </c>
       <c r="C1957" s="1" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D1957" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1958" spans="1:4">
@@ -28864,10 +28867,10 @@
         <v>360</v>
       </c>
       <c r="B1958" s="2">
-        <v>102173363</v>
+        <v>102456914</v>
       </c>
       <c r="C1958" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D1958" s="2">
         <v>22</v>
@@ -28878,13 +28881,13 @@
         <v>360</v>
       </c>
       <c r="B1959" s="2">
-        <v>102211179</v>
+        <v>102456984</v>
       </c>
       <c r="C1959" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D1959" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1960" spans="1:4">
@@ -28892,13 +28895,13 @@
         <v>360</v>
       </c>
       <c r="B1960" s="2">
-        <v>102219144</v>
+        <v>102456993</v>
       </c>
       <c r="C1960" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D1960" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1961" spans="1:4">
@@ -28906,10 +28909,10 @@
         <v>360</v>
       </c>
       <c r="B1961" s="2">
-        <v>102326882</v>
+        <v>102457937</v>
       </c>
       <c r="C1961" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D1961" s="2">
         <v>19</v>
@@ -28920,13 +28923,13 @@
         <v>360</v>
       </c>
       <c r="B1962" s="2">
-        <v>102343359</v>
+        <v>102458550</v>
       </c>
       <c r="C1962" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1962" s="2">
         <v>17</v>
-      </c>
-      <c r="D1962" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="1963" spans="1:4">
@@ -28934,13 +28937,13 @@
         <v>360</v>
       </c>
       <c r="B1963" s="2">
-        <v>102369579</v>
+        <v>102464498</v>
       </c>
       <c r="C1963" s="1" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D1963" s="2">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1964" spans="1:4">
@@ -28948,13 +28951,13 @@
         <v>360</v>
       </c>
       <c r="B1964" s="2">
-        <v>102370804</v>
+        <v>102477288</v>
       </c>
       <c r="C1964" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D1964" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1965" spans="1:4">
@@ -28962,13 +28965,13 @@
         <v>360</v>
       </c>
       <c r="B1965" s="2">
-        <v>102371964</v>
+        <v>102477293</v>
       </c>
       <c r="C1965" s="1" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D1965" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1966" spans="1:4">
@@ -28976,13 +28979,13 @@
         <v>360</v>
       </c>
       <c r="B1966" s="2">
-        <v>102456914</v>
+        <v>102477371</v>
       </c>
       <c r="C1966" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D1966" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1967" spans="1:4">
@@ -28990,13 +28993,13 @@
         <v>360</v>
       </c>
       <c r="B1967" s="2">
-        <v>102456984</v>
+        <v>102477422</v>
       </c>
       <c r="C1967" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D1967" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1968" spans="1:4">
@@ -29004,13 +29007,13 @@
         <v>360</v>
       </c>
       <c r="B1968" s="2">
-        <v>102456993</v>
+        <v>102477510</v>
       </c>
       <c r="C1968" s="1" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D1968" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1969" spans="1:4">
@@ -29018,10 +29021,10 @@
         <v>360</v>
       </c>
       <c r="B1969" s="2">
-        <v>102457937</v>
+        <v>102478278</v>
       </c>
       <c r="C1969" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D1969" s="2">
         <v>20</v>
@@ -29032,13 +29035,13 @@
         <v>360</v>
       </c>
       <c r="B1970" s="2">
-        <v>102458550</v>
+        <v>102482237</v>
       </c>
       <c r="C1970" s="1" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D1970" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1971" spans="1:4">
@@ -29046,13 +29049,13 @@
         <v>360</v>
       </c>
       <c r="B1971" s="2">
-        <v>102464498</v>
+        <v>102484482</v>
       </c>
       <c r="C1971" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D1971" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1972" spans="1:4">
@@ -29060,10 +29063,10 @@
         <v>360</v>
       </c>
       <c r="B1972" s="2">
-        <v>102477288</v>
+        <v>102502720</v>
       </c>
       <c r="C1972" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D1972" s="2">
         <v>21</v>
@@ -29074,10 +29077,10 @@
         <v>360</v>
       </c>
       <c r="B1973" s="2">
-        <v>102477293</v>
+        <v>102502737</v>
       </c>
       <c r="C1973" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D1973" s="2">
         <v>21</v>
@@ -29088,13 +29091,13 @@
         <v>360</v>
       </c>
       <c r="B1974" s="2">
-        <v>102477371</v>
+        <v>102502871</v>
       </c>
       <c r="C1974" s="1" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D1974" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1975" spans="1:4">
@@ -29102,13 +29105,13 @@
         <v>360</v>
       </c>
       <c r="B1975" s="2">
-        <v>102477422</v>
+        <v>102503478</v>
       </c>
       <c r="C1975" s="1" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D1975" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1976" spans="1:4">
@@ -29116,10 +29119,10 @@
         <v>360</v>
       </c>
       <c r="B1976" s="2">
-        <v>102477510</v>
+        <v>102507584</v>
       </c>
       <c r="C1976" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="D1976" s="2">
         <v>21</v>
@@ -29130,10 +29133,10 @@
         <v>360</v>
       </c>
       <c r="B1977" s="2">
-        <v>102478278</v>
+        <v>102509109</v>
       </c>
       <c r="C1977" s="1" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D1977" s="2">
         <v>19</v>
@@ -29144,13 +29147,13 @@
         <v>360</v>
       </c>
       <c r="B1978" s="2">
-        <v>102482237</v>
+        <v>102511945</v>
       </c>
       <c r="C1978" s="1" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D1978" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1979" spans="1:4">
@@ -29158,10 +29161,10 @@
         <v>360</v>
       </c>
       <c r="B1979" s="2">
-        <v>102484482</v>
+        <v>102517333</v>
       </c>
       <c r="C1979" s="1" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D1979" s="2">
         <v>20</v>
@@ -29172,13 +29175,13 @@
         <v>360</v>
       </c>
       <c r="B1980" s="2">
-        <v>102502720</v>
+        <v>102517346</v>
       </c>
       <c r="C1980" s="1" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D1980" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1981" spans="1:4">
@@ -29186,10 +29189,10 @@
         <v>360</v>
       </c>
       <c r="B1981" s="2">
-        <v>102502737</v>
+        <v>102821757</v>
       </c>
       <c r="C1981" s="1" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D1981" s="2">
         <v>22</v>
@@ -29200,10 +29203,10 @@
         <v>360</v>
       </c>
       <c r="B1982" s="2">
-        <v>102502871</v>
+        <v>102830253</v>
       </c>
       <c r="C1982" s="1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="D1982" s="2">
         <v>22</v>
@@ -29214,13 +29217,13 @@
         <v>360</v>
       </c>
       <c r="B1983" s="2">
-        <v>102503478</v>
+        <v>102830316</v>
       </c>
       <c r="C1983" s="1" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D1983" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1984" spans="1:4">
@@ -29228,13 +29231,13 @@
         <v>360</v>
       </c>
       <c r="B1984" s="2">
-        <v>102507584</v>
+        <v>102831065</v>
       </c>
       <c r="C1984" s="1" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="D1984" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1985" spans="1:4">
@@ -29242,13 +29245,13 @@
         <v>360</v>
       </c>
       <c r="B1985" s="2">
-        <v>102509109</v>
+        <v>102843519</v>
       </c>
       <c r="C1985" s="1" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D1985" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1986" spans="1:4">
@@ -29256,13 +29259,13 @@
         <v>360</v>
       </c>
       <c r="B1986" s="2">
-        <v>102511945</v>
+        <v>102855952</v>
       </c>
       <c r="C1986" s="1" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="D1986" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1987" spans="1:4">
@@ -29270,13 +29273,13 @@
         <v>360</v>
       </c>
       <c r="B1987" s="2">
-        <v>102517330</v>
+        <v>102864715</v>
       </c>
       <c r="C1987" s="1" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="D1987" s="2">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1988" spans="1:4">
@@ -29284,13 +29287,13 @@
         <v>360</v>
       </c>
       <c r="B1988" s="2">
-        <v>102517333</v>
+        <v>102871040</v>
       </c>
       <c r="C1988" s="1" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="D1988" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1989" spans="1:4">
@@ -29298,13 +29301,13 @@
         <v>360</v>
       </c>
       <c r="B1989" s="2">
-        <v>102517346</v>
+        <v>102879799</v>
       </c>
       <c r="C1989" s="1" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="D1989" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1990" spans="1:4">
@@ -29312,13 +29315,13 @@
         <v>360</v>
       </c>
       <c r="B1990" s="2">
-        <v>102821757</v>
+        <v>102884064</v>
       </c>
       <c r="C1990" s="1" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="D1990" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1991" spans="1:4">
@@ -29326,13 +29329,13 @@
         <v>360</v>
       </c>
       <c r="B1991" s="2">
-        <v>102821761</v>
+        <v>102884675</v>
       </c>
       <c r="C1991" s="1" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="D1991" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1992" spans="1:4">
@@ -29340,13 +29343,13 @@
         <v>360</v>
       </c>
       <c r="B1992" s="2">
-        <v>102830253</v>
+        <v>102908267</v>
       </c>
       <c r="C1992" s="1" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="D1992" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1993" spans="1:4">
@@ -29354,13 +29357,13 @@
         <v>360</v>
       </c>
       <c r="B1993" s="2">
-        <v>102830316</v>
+        <v>103028093</v>
       </c>
       <c r="C1993" s="1" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="D1993" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1994" spans="1:4">
@@ -29368,13 +29371,13 @@
         <v>360</v>
       </c>
       <c r="B1994" s="2">
-        <v>102831065</v>
+        <v>103060430</v>
       </c>
       <c r="C1994" s="1" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D1994" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1995" spans="1:4">
@@ -29382,10 +29385,10 @@
         <v>360</v>
       </c>
       <c r="B1995" s="2">
-        <v>102837399</v>
+        <v>103060435</v>
       </c>
       <c r="C1995" s="1" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="D1995" s="2">
         <v>20</v>
@@ -29396,13 +29399,13 @@
         <v>360</v>
       </c>
       <c r="B1996" s="2">
-        <v>102843519</v>
+        <v>103060453</v>
       </c>
       <c r="C1996" s="1" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="D1996" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1997" spans="1:4">
@@ -29410,10 +29413,10 @@
         <v>360</v>
       </c>
       <c r="B1997" s="2">
-        <v>102855952</v>
+        <v>103060459</v>
       </c>
       <c r="C1997" s="1" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="D1997" s="2">
         <v>19</v>
@@ -29424,13 +29427,13 @@
         <v>360</v>
       </c>
       <c r="B1998" s="2">
-        <v>102864715</v>
+        <v>103060462</v>
       </c>
       <c r="C1998" s="1" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="D1998" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1999" spans="1:4">
@@ -29438,13 +29441,13 @@
         <v>360</v>
       </c>
       <c r="B1999" s="2">
-        <v>102871040</v>
+        <v>103060467</v>
       </c>
       <c r="C1999" s="1" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="D1999" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2000" spans="1:4">
@@ -29452,13 +29455,13 @@
         <v>360</v>
       </c>
       <c r="B2000" s="2">
-        <v>102879799</v>
+        <v>103060471</v>
       </c>
       <c r="C2000" s="1" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D2000" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2001" spans="1:4">
@@ -29466,10 +29469,10 @@
         <v>360</v>
       </c>
       <c r="B2001" s="2">
-        <v>102884064</v>
+        <v>103082092</v>
       </c>
       <c r="C2001" s="1" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="D2001" s="2">
         <v>20</v>
@@ -29480,13 +29483,13 @@
         <v>360</v>
       </c>
       <c r="B2002" s="2">
-        <v>102884675</v>
+        <v>103082095</v>
       </c>
       <c r="C2002" s="1" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="D2002" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2003" spans="1:4">
@@ -29494,13 +29497,13 @@
         <v>360</v>
       </c>
       <c r="B2003" s="2">
-        <v>102908267</v>
+        <v>103082112</v>
       </c>
       <c r="C2003" s="1" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="D2003" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2004" spans="1:4">
@@ -29508,13 +29511,13 @@
         <v>360</v>
       </c>
       <c r="B2004" s="2">
-        <v>103028093</v>
+        <v>103082113</v>
       </c>
       <c r="C2004" s="1" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D2004" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2005" spans="1:4">
@@ -29522,13 +29525,13 @@
         <v>360</v>
       </c>
       <c r="B2005" s="2">
-        <v>103060430</v>
+        <v>103082118</v>
       </c>
       <c r="C2005" s="1" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="D2005" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2006" spans="1:4">
@@ -29536,13 +29539,13 @@
         <v>360</v>
       </c>
       <c r="B2006" s="2">
-        <v>103060435</v>
+        <v>103082121</v>
       </c>
       <c r="C2006" s="1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="D2006" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2007" spans="1:4">
@@ -29550,13 +29553,13 @@
         <v>360</v>
       </c>
       <c r="B2007" s="2">
-        <v>103060453</v>
+        <v>103082161</v>
       </c>
       <c r="C2007" s="1" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D2007" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2008" spans="1:4">
@@ -29564,10 +29567,10 @@
         <v>360</v>
       </c>
       <c r="B2008" s="2">
-        <v>103060459</v>
+        <v>103082166</v>
       </c>
       <c r="C2008" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="D2008" s="2">
         <v>22</v>
@@ -29578,13 +29581,13 @@
         <v>360</v>
       </c>
       <c r="B2009" s="2">
-        <v>103060462</v>
+        <v>103082385</v>
       </c>
       <c r="C2009" s="1" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D2009" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2010" spans="1:4">
@@ -29592,13 +29595,13 @@
         <v>360</v>
       </c>
       <c r="B2010" s="2">
-        <v>103060467</v>
+        <v>103085298</v>
       </c>
       <c r="C2010" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D2010" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2011" spans="1:4">
@@ -29606,10 +29609,10 @@
         <v>360</v>
       </c>
       <c r="B2011" s="2">
-        <v>103060471</v>
+        <v>103088009</v>
       </c>
       <c r="C2011" s="1" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="D2011" s="2">
         <v>20</v>
@@ -29620,10 +29623,10 @@
         <v>360</v>
       </c>
       <c r="B2012" s="2">
-        <v>103082092</v>
+        <v>103092092</v>
       </c>
       <c r="C2012" s="1" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D2012" s="2">
         <v>20</v>
@@ -29634,13 +29637,13 @@
         <v>360</v>
       </c>
       <c r="B2013" s="2">
-        <v>103082095</v>
+        <v>103092310</v>
       </c>
       <c r="C2013" s="1" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="D2013" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2014" spans="1:4">
@@ -29648,13 +29651,13 @@
         <v>360</v>
       </c>
       <c r="B2014" s="2">
-        <v>103082112</v>
+        <v>103092316</v>
       </c>
       <c r="C2014" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="D2014" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2015" spans="1:4">
@@ -29662,13 +29665,13 @@
         <v>360</v>
       </c>
       <c r="B2015" s="2">
-        <v>103082113</v>
+        <v>103101206</v>
       </c>
       <c r="C2015" s="1" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="D2015" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2016" spans="1:4">
@@ -29676,10 +29679,10 @@
         <v>360</v>
       </c>
       <c r="B2016" s="2">
-        <v>103082118</v>
+        <v>103103196</v>
       </c>
       <c r="C2016" s="1" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="D2016" s="2">
         <v>13</v>
@@ -29690,13 +29693,13 @@
         <v>360</v>
       </c>
       <c r="B2017" s="2">
-        <v>103082119</v>
+        <v>103103198</v>
       </c>
       <c r="C2017" s="1" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="D2017" s="2">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2018" spans="1:4">
@@ -29704,13 +29707,13 @@
         <v>360</v>
       </c>
       <c r="B2018" s="2">
-        <v>103082121</v>
+        <v>103103213</v>
       </c>
       <c r="C2018" s="1" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="D2018" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2019" spans="1:4">
@@ -29718,13 +29721,13 @@
         <v>360</v>
       </c>
       <c r="B2019" s="2">
-        <v>103082161</v>
+        <v>103105143</v>
       </c>
       <c r="C2019" s="1" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="D2019" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2020" spans="1:4">
@@ -29732,10 +29735,10 @@
         <v>360</v>
       </c>
       <c r="B2020" s="2">
-        <v>103082166</v>
+        <v>103109089</v>
       </c>
       <c r="C2020" s="1" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="D2020" s="2">
         <v>20</v>
@@ -29746,13 +29749,13 @@
         <v>360</v>
       </c>
       <c r="B2021" s="2">
-        <v>103082385</v>
+        <v>103109090</v>
       </c>
       <c r="C2021" s="1" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="D2021" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2022" spans="1:4">
@@ -29760,13 +29763,13 @@
         <v>360</v>
       </c>
       <c r="B2022" s="2">
-        <v>103085298</v>
+        <v>103109091</v>
       </c>
       <c r="C2022" s="1" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="D2022" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2023" spans="1:4">
@@ -29774,13 +29777,13 @@
         <v>360</v>
       </c>
       <c r="B2023" s="2">
-        <v>103088009</v>
+        <v>103109136</v>
       </c>
       <c r="C2023" s="1" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="D2023" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2024" spans="1:4">
@@ -29788,13 +29791,13 @@
         <v>360</v>
       </c>
       <c r="B2024" s="2">
-        <v>103092092</v>
+        <v>103109151</v>
       </c>
       <c r="C2024" s="1" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="D2024" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2025" spans="1:4">
@@ -29802,13 +29805,13 @@
         <v>360</v>
       </c>
       <c r="B2025" s="2">
-        <v>103092141</v>
+        <v>103109336</v>
       </c>
       <c r="C2025" s="1" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D2025" s="2">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2026" spans="1:4">
@@ -29816,13 +29819,13 @@
         <v>360</v>
       </c>
       <c r="B2026" s="2">
-        <v>103092310</v>
+        <v>103109339</v>
       </c>
       <c r="C2026" s="1" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="D2026" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2027" spans="1:4">
@@ -29830,13 +29833,13 @@
         <v>360</v>
       </c>
       <c r="B2027" s="2">
-        <v>103092316</v>
+        <v>103109343</v>
       </c>
       <c r="C2027" s="1" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="D2027" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2028" spans="1:4">
@@ -29844,13 +29847,13 @@
         <v>360</v>
       </c>
       <c r="B2028" s="2">
-        <v>103101206</v>
+        <v>103109357</v>
       </c>
       <c r="C2028" s="1" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="D2028" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2029" spans="1:4">
@@ -29858,13 +29861,13 @@
         <v>360</v>
       </c>
       <c r="B2029" s="2">
-        <v>103101215</v>
+        <v>103110013</v>
       </c>
       <c r="C2029" s="1" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="D2029" s="2">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2030" spans="1:4">
@@ -29872,13 +29875,13 @@
         <v>360</v>
       </c>
       <c r="B2030" s="2">
-        <v>103101217</v>
+        <v>103111713</v>
       </c>
       <c r="C2030" s="1" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="D2030" s="2">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2031" spans="1:4">
@@ -29886,10 +29889,10 @@
         <v>360</v>
       </c>
       <c r="B2031" s="2">
-        <v>103103196</v>
+        <v>103111956</v>
       </c>
       <c r="C2031" s="1" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="D2031" s="2">
         <v>19</v>
@@ -29900,13 +29903,13 @@
         <v>360</v>
       </c>
       <c r="B2032" s="2">
-        <v>103103198</v>
+        <v>103113926</v>
       </c>
       <c r="C2032" s="1" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="D2032" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2033" spans="1:4">
@@ -29914,13 +29917,13 @@
         <v>360</v>
       </c>
       <c r="B2033" s="2">
-        <v>103103213</v>
+        <v>103115341</v>
       </c>
       <c r="C2033" s="1" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="D2033" s="2">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2034" spans="1:4">
@@ -29928,10 +29931,10 @@
         <v>360</v>
       </c>
       <c r="B2034" s="2">
-        <v>103105143</v>
+        <v>103116487</v>
       </c>
       <c r="C2034" s="1" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="D2034" s="2">
         <v>20</v>
@@ -29942,13 +29945,13 @@
         <v>360</v>
       </c>
       <c r="B2035" s="2">
-        <v>103109089</v>
+        <v>103116496</v>
       </c>
       <c r="C2035" s="1" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="D2035" s="2">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2036" spans="1:4">
@@ -29956,10 +29959,10 @@
         <v>360</v>
       </c>
       <c r="B2036" s="2">
-        <v>103109090</v>
+        <v>103117188</v>
       </c>
       <c r="C2036" s="1" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="D2036" s="2">
         <v>17</v>
@@ -29970,13 +29973,13 @@
         <v>360</v>
       </c>
       <c r="B2037" s="2">
-        <v>103109091</v>
+        <v>103121097</v>
       </c>
       <c r="C2037" s="1" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="D2037" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2038" spans="1:4">
@@ -29984,13 +29987,13 @@
         <v>360</v>
       </c>
       <c r="B2038" s="2">
-        <v>103109136</v>
+        <v>103121098</v>
       </c>
       <c r="C2038" s="1" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="D2038" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2039" spans="1:4">
@@ -29998,13 +30001,13 @@
         <v>360</v>
       </c>
       <c r="B2039" s="2">
-        <v>103109151</v>
+        <v>103125208</v>
       </c>
       <c r="C2039" s="1" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="D2039" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2040" spans="1:4">
@@ -30012,13 +30015,13 @@
         <v>360</v>
       </c>
       <c r="B2040" s="2">
-        <v>103109336</v>
+        <v>103125228</v>
       </c>
       <c r="C2040" s="1" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="D2040" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2041" spans="1:4">
@@ -30026,10 +30029,10 @@
         <v>360</v>
       </c>
       <c r="B2041" s="2">
-        <v>103109339</v>
+        <v>103125229</v>
       </c>
       <c r="C2041" s="1" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="D2041" s="2">
         <v>20</v>
@@ -30040,13 +30043,13 @@
         <v>360</v>
       </c>
       <c r="B2042" s="2">
-        <v>103109343</v>
+        <v>103127936</v>
       </c>
       <c r="C2042" s="1" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="D2042" s="2">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2043" spans="1:4">
@@ -30054,13 +30057,13 @@
         <v>360</v>
       </c>
       <c r="B2043" s="2">
-        <v>103109357</v>
+        <v>103130519</v>
       </c>
       <c r="C2043" s="1" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="D2043" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2044" spans="1:4">
@@ -30068,13 +30071,13 @@
         <v>360</v>
       </c>
       <c r="B2044" s="2">
-        <v>103110013</v>
+        <v>103132423</v>
       </c>
       <c r="C2044" s="1" t="s">
-        <v>177</v>
+        <v>229</v>
       </c>
       <c r="D2044" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2045" spans="1:4">
@@ -30082,13 +30085,13 @@
         <v>360</v>
       </c>
       <c r="B2045" s="2">
-        <v>103110453</v>
+        <v>103132424</v>
       </c>
       <c r="C2045" s="1" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="D2045" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2046" spans="1:4">
@@ -30096,13 +30099,13 @@
         <v>360</v>
       </c>
       <c r="B2046" s="2">
-        <v>103111713</v>
+        <v>103133036</v>
       </c>
       <c r="C2046" s="1" t="s">
-        <v>180</v>
+        <v>235</v>
       </c>
       <c r="D2046" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2047" spans="1:4">
@@ -30110,13 +30113,13 @@
         <v>360</v>
       </c>
       <c r="B2047" s="2">
-        <v>103111920</v>
+        <v>103136107</v>
       </c>
       <c r="C2047" s="1" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="D2047" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2048" spans="1:4">
@@ -30124,13 +30127,13 @@
         <v>360</v>
       </c>
       <c r="B2048" s="2">
-        <v>103111956</v>
+        <v>103139871</v>
       </c>
       <c r="C2048" s="1" t="s">
-        <v>182</v>
+        <v>246</v>
       </c>
       <c r="D2048" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2049" spans="1:4">
@@ -30138,13 +30141,13 @@
         <v>360</v>
       </c>
       <c r="B2049" s="2">
-        <v>103113926</v>
+        <v>103145144</v>
       </c>
       <c r="C2049" s="1" t="s">
-        <v>183</v>
+        <v>252</v>
       </c>
       <c r="D2049" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2050" spans="1:4">
@@ -30152,10 +30155,10 @@
         <v>360</v>
       </c>
       <c r="B2050" s="2">
-        <v>103115341</v>
+        <v>103169793</v>
       </c>
       <c r="C2050" s="1" t="s">
-        <v>184</v>
+        <v>258</v>
       </c>
       <c r="D2050" s="2">
         <v>20</v>
@@ -30166,13 +30169,13 @@
         <v>360</v>
       </c>
       <c r="B2051" s="2">
-        <v>103116487</v>
+        <v>103169795</v>
       </c>
       <c r="C2051" s="1" t="s">
-        <v>186</v>
+        <v>259</v>
       </c>
       <c r="D2051" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2052" spans="1:4">
@@ -30180,13 +30183,13 @@
         <v>360</v>
       </c>
       <c r="B2052" s="2">
-        <v>103116496</v>
+        <v>103169797</v>
       </c>
       <c r="C2052" s="1" t="s">
-        <v>187</v>
+        <v>260</v>
       </c>
       <c r="D2052" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2053" spans="1:4">
@@ -30194,10 +30197,10 @@
         <v>360</v>
       </c>
       <c r="B2053" s="2">
-        <v>103117188</v>
+        <v>103169814</v>
       </c>
       <c r="C2053" s="1" t="s">
-        <v>189</v>
+        <v>262</v>
       </c>
       <c r="D2053" s="2">
         <v>19</v>
@@ -30208,13 +30211,13 @@
         <v>360</v>
       </c>
       <c r="B2054" s="2">
-        <v>103121097</v>
+        <v>103169816</v>
       </c>
       <c r="C2054" s="1" t="s">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c r="D2054" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2055" spans="1:4">
@@ -30222,13 +30225,13 @@
         <v>360</v>
       </c>
       <c r="B2055" s="2">
-        <v>103121098</v>
+        <v>103171103</v>
       </c>
       <c r="C2055" s="1" t="s">
-        <v>194</v>
+        <v>273</v>
       </c>
       <c r="D2055" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2056" spans="1:4">
@@ -30236,13 +30239,13 @@
         <v>360</v>
       </c>
       <c r="B2056" s="2">
-        <v>103125208</v>
+        <v>103173195</v>
       </c>
       <c r="C2056" s="1" t="s">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="D2056" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2057" spans="1:4">
@@ -30250,13 +30253,13 @@
         <v>360</v>
       </c>
       <c r="B2057" s="2">
-        <v>103125228</v>
+        <v>103173197</v>
       </c>
       <c r="C2057" s="1" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="D2057" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2058" spans="1:4">
@@ -30264,13 +30267,13 @@
         <v>360</v>
       </c>
       <c r="B2058" s="2">
-        <v>103125229</v>
+        <v>103283831</v>
       </c>
       <c r="C2058" s="1" t="s">
-        <v>209</v>
+        <v>341</v>
       </c>
       <c r="D2058" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2059" spans="1:4">
@@ -30278,13 +30281,13 @@
         <v>360</v>
       </c>
       <c r="B2059" s="2">
-        <v>103127936</v>
+        <v>103293732</v>
       </c>
       <c r="C2059" s="1" t="s">
-        <v>211</v>
+        <v>286</v>
       </c>
       <c r="D2059" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2060" spans="1:4">
@@ -30292,13 +30295,13 @@
         <v>360</v>
       </c>
       <c r="B2060" s="2">
-        <v>103130519</v>
+        <v>103293737</v>
       </c>
       <c r="C2060" s="1" t="s">
-        <v>226</v>
+        <v>287</v>
       </c>
       <c r="D2060" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2061" spans="1:4">
@@ -30306,10 +30309,10 @@
         <v>360</v>
       </c>
       <c r="B2061" s="2">
-        <v>103132423</v>
+        <v>103293745</v>
       </c>
       <c r="C2061" s="1" t="s">
-        <v>229</v>
+        <v>342</v>
       </c>
       <c r="D2061" s="2">
         <v>22</v>
@@ -30320,13 +30323,13 @@
         <v>360</v>
       </c>
       <c r="B2062" s="2">
-        <v>103132424</v>
+        <v>103293751</v>
       </c>
       <c r="C2062" s="1" t="s">
-        <v>230</v>
+        <v>288</v>
       </c>
       <c r="D2062" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2063" spans="1:4">
@@ -30334,13 +30337,13 @@
         <v>360</v>
       </c>
       <c r="B2063" s="2">
-        <v>103133036</v>
+        <v>103293756</v>
       </c>
       <c r="C2063" s="1" t="s">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="D2063" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2064" spans="1:4">
@@ -30348,13 +30351,13 @@
         <v>360</v>
       </c>
       <c r="B2064" s="2">
-        <v>103136107</v>
+        <v>103293766</v>
       </c>
       <c r="C2064" s="1" t="s">
-        <v>242</v>
+        <v>290</v>
       </c>
       <c r="D2064" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2065" spans="1:4">
@@ -30362,10 +30365,10 @@
         <v>360</v>
       </c>
       <c r="B2065" s="2">
-        <v>103139871</v>
+        <v>103293773</v>
       </c>
       <c r="C2065" s="1" t="s">
-        <v>246</v>
+        <v>291</v>
       </c>
       <c r="D2065" s="2">
         <v>20</v>
@@ -30376,13 +30379,13 @@
         <v>360</v>
       </c>
       <c r="B2066" s="2">
-        <v>103145144</v>
+        <v>103294755</v>
       </c>
       <c r="C2066" s="1" t="s">
-        <v>252</v>
+        <v>150</v>
       </c>
       <c r="D2066" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2067" spans="1:4">
@@ -30390,10 +30393,10 @@
         <v>360</v>
       </c>
       <c r="B2067" s="2">
-        <v>103169793</v>
+        <v>103296160</v>
       </c>
       <c r="C2067" s="1" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="D2067" s="2">
         <v>18</v>
@@ -30404,13 +30407,13 @@
         <v>360</v>
       </c>
       <c r="B2068" s="2">
-        <v>103169795</v>
+        <v>103296167</v>
       </c>
       <c r="C2068" s="1" t="s">
-        <v>259</v>
+        <v>345</v>
       </c>
       <c r="D2068" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2069" spans="1:4">
@@ -30418,10 +30421,10 @@
         <v>360</v>
       </c>
       <c r="B2069" s="2">
-        <v>103169797</v>
+        <v>103297566</v>
       </c>
       <c r="C2069" s="1" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="D2069" s="2">
         <v>18</v>
@@ -30432,13 +30435,13 @@
         <v>360</v>
       </c>
       <c r="B2070" s="2">
-        <v>103169814</v>
+        <v>103300418</v>
       </c>
       <c r="C2070" s="1" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="D2070" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2071" spans="1:4">
@@ -30446,13 +30449,13 @@
         <v>360</v>
       </c>
       <c r="B2071" s="2">
-        <v>103169816</v>
+        <v>103304841</v>
       </c>
       <c r="C2071" s="1" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="D2071" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2072" spans="1:4">
@@ -30460,13 +30463,13 @@
         <v>360</v>
       </c>
       <c r="B2072" s="2">
-        <v>103171084</v>
+        <v>103304846</v>
       </c>
       <c r="C2072" s="1" t="s">
-        <v>272</v>
+        <v>348</v>
       </c>
       <c r="D2072" s="2">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2073" spans="1:4">
@@ -30474,13 +30477,13 @@
         <v>360</v>
       </c>
       <c r="B2073" s="2">
-        <v>103171103</v>
+        <v>103304863</v>
       </c>
       <c r="C2073" s="1" t="s">
-        <v>273</v>
+        <v>349</v>
       </c>
       <c r="D2073" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2074" spans="1:4">
@@ -30488,13 +30491,13 @@
         <v>360</v>
       </c>
       <c r="B2074" s="2">
-        <v>103173195</v>
+        <v>103304866</v>
       </c>
       <c r="C2074" s="1" t="s">
-        <v>276</v>
+        <v>130</v>
       </c>
       <c r="D2074" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2075" spans="1:4">
@@ -30502,13 +30505,13 @@
         <v>360</v>
       </c>
       <c r="B2075" s="2">
-        <v>103173197</v>
+        <v>103304875</v>
       </c>
       <c r="C2075" s="1" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="D2075" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2076" spans="1:4">
@@ -30516,13 +30519,13 @@
         <v>360</v>
       </c>
       <c r="B2076" s="2">
-        <v>103283831</v>
+        <v>103305150</v>
       </c>
       <c r="C2076" s="1" t="s">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="D2076" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2077" spans="1:4">
@@ -30530,13 +30533,13 @@
         <v>360</v>
       </c>
       <c r="B2077" s="2">
-        <v>103293732</v>
+        <v>103305154</v>
       </c>
       <c r="C2077" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="D2077" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2078" spans="1:4">
@@ -30544,13 +30547,13 @@
         <v>360</v>
       </c>
       <c r="B2078" s="2">
-        <v>103293737</v>
+        <v>103305160</v>
       </c>
       <c r="C2078" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="D2078" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2079" spans="1:4">
@@ -30558,80 +30561,80 @@
         <v>360</v>
       </c>
       <c r="B2079" s="2">
-        <v>103293745</v>
+        <v>103305165</v>
       </c>
       <c r="C2079" s="1" t="s">
-        <v>342</v>
+        <v>299</v>
       </c>
       <c r="D2079" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2080" spans="1:4">
       <c r="A2080" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2080" s="2">
-        <v>103293751</v>
+        <v>102029874</v>
       </c>
       <c r="C2080" s="1" t="s">
-        <v>288</v>
+        <v>6</v>
       </c>
       <c r="D2080" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2081" spans="1:4">
       <c r="A2081" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2081" s="2">
-        <v>103293756</v>
+        <v>102173363</v>
       </c>
       <c r="C2081" s="1" t="s">
-        <v>289</v>
+        <v>7</v>
       </c>
       <c r="D2081" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2082" spans="1:4">
       <c r="A2082" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2082" s="2">
-        <v>103293766</v>
+        <v>102211179</v>
       </c>
       <c r="C2082" s="1" t="s">
-        <v>290</v>
+        <v>10</v>
       </c>
       <c r="D2082" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2083" spans="1:4">
       <c r="A2083" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2083" s="2">
-        <v>103293773</v>
+        <v>102219144</v>
       </c>
       <c r="C2083" s="1" t="s">
-        <v>291</v>
+        <v>12</v>
       </c>
       <c r="D2083" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2084" spans="1:4">
       <c r="A2084" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2084" s="2">
-        <v>103294755</v>
+        <v>102326882</v>
       </c>
       <c r="C2084" s="1" t="s">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="D2084" s="2">
         <v>19</v>
@@ -30639,111 +30642,111 @@
     </row>
     <row r="2085" spans="1:4">
       <c r="A2085" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2085" s="2">
-        <v>103296160</v>
+        <v>102343359</v>
       </c>
       <c r="C2085" s="1" t="s">
-        <v>292</v>
+        <v>17</v>
       </c>
       <c r="D2085" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2086" spans="1:4">
       <c r="A2086" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2086" s="2">
-        <v>103296167</v>
+        <v>102369579</v>
       </c>
       <c r="C2086" s="1" t="s">
-        <v>345</v>
+        <v>19</v>
       </c>
       <c r="D2086" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2087" spans="1:4">
       <c r="A2087" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2087" s="2">
-        <v>103297566</v>
+        <v>102370804</v>
       </c>
       <c r="C2087" s="1" t="s">
-        <v>293</v>
+        <v>22</v>
       </c>
       <c r="D2087" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2088" spans="1:4">
       <c r="A2088" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2088" s="2">
-        <v>103300418</v>
+        <v>102371964</v>
       </c>
       <c r="C2088" s="1" t="s">
-        <v>294</v>
+        <v>25</v>
       </c>
       <c r="D2088" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2089" spans="1:4">
       <c r="A2089" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2089" s="2">
-        <v>103304841</v>
+        <v>102456914</v>
       </c>
       <c r="C2089" s="1" t="s">
-        <v>290</v>
+        <v>27</v>
       </c>
       <c r="D2089" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2090" spans="1:4">
       <c r="A2090" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2090" s="2">
-        <v>103304846</v>
+        <v>102456984</v>
       </c>
       <c r="C2090" s="1" t="s">
-        <v>348</v>
+        <v>28</v>
       </c>
       <c r="D2090" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2091" spans="1:4">
       <c r="A2091" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2091" s="2">
-        <v>103304863</v>
+        <v>102456993</v>
       </c>
       <c r="C2091" s="1" t="s">
-        <v>349</v>
+        <v>29</v>
       </c>
       <c r="D2091" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2092" spans="1:4">
       <c r="A2092" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2092" s="2">
-        <v>103304866</v>
+        <v>102457937</v>
       </c>
       <c r="C2092" s="1" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="D2092" s="2">
         <v>20</v>
@@ -30751,86 +30754,86 @@
     </row>
     <row r="2093" spans="1:4">
       <c r="A2093" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2093" s="2">
-        <v>103304868</v>
+        <v>102458550</v>
       </c>
       <c r="C2093" s="1" t="s">
-        <v>350</v>
+        <v>35</v>
       </c>
       <c r="D2093" s="2">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2094" spans="1:4">
       <c r="A2094" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2094" s="2">
-        <v>103304875</v>
+        <v>102464498</v>
       </c>
       <c r="C2094" s="1" t="s">
-        <v>295</v>
+        <v>36</v>
       </c>
       <c r="D2094" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2095" spans="1:4">
       <c r="A2095" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2095" s="2">
-        <v>103305150</v>
+        <v>102477288</v>
       </c>
       <c r="C2095" s="1" t="s">
-        <v>296</v>
+        <v>46</v>
       </c>
       <c r="D2095" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2096" spans="1:4">
       <c r="A2096" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2096" s="2">
-        <v>103305154</v>
+        <v>102477293</v>
       </c>
       <c r="C2096" s="1" t="s">
-        <v>297</v>
+        <v>48</v>
       </c>
       <c r="D2096" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2097" spans="1:4">
       <c r="A2097" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2097" s="2">
-        <v>103305160</v>
+        <v>102477371</v>
       </c>
       <c r="C2097" s="1" t="s">
-        <v>298</v>
+        <v>49</v>
       </c>
       <c r="D2097" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2098" spans="1:4">
       <c r="A2098" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B2098" s="2">
-        <v>103305165</v>
+        <v>102477422</v>
       </c>
       <c r="C2098" s="1" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
       <c r="D2098" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2099" spans="1:4">
@@ -30838,10 +30841,10 @@
         <v>361</v>
       </c>
       <c r="B2099" s="2">
-        <v>102029874</v>
+        <v>102477510</v>
       </c>
       <c r="C2099" s="1" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="D2099" s="2">
         <v>21</v>
@@ -30852,13 +30855,13 @@
         <v>361</v>
       </c>
       <c r="B2100" s="2">
-        <v>102173363</v>
+        <v>102478278</v>
       </c>
       <c r="C2100" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="D2100" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2101" spans="1:4">
@@ -30866,13 +30869,13 @@
         <v>361</v>
       </c>
       <c r="B2101" s="2">
-        <v>102211179</v>
+        <v>102482237</v>
       </c>
       <c r="C2101" s="1" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="D2101" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2102" spans="1:4">
@@ -30880,13 +30883,13 @@
         <v>361</v>
       </c>
       <c r="B2102" s="2">
-        <v>102219144</v>
+        <v>102484482</v>
       </c>
       <c r="C2102" s="1" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="D2102" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2103" spans="1:4">
@@ -30894,10 +30897,10 @@
         <v>361</v>
       </c>
       <c r="B2103" s="2">
-        <v>102326882</v>
+        <v>102502720</v>
       </c>
       <c r="C2103" s="1" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D2103" s="2">
         <v>21</v>
@@ -30908,13 +30911,13 @@
         <v>361</v>
       </c>
       <c r="B2104" s="2">
-        <v>102343359</v>
+        <v>102502737</v>
       </c>
       <c r="C2104" s="1" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D2104" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2105" spans="1:4">
@@ -30922,13 +30925,13 @@
         <v>361</v>
       </c>
       <c r="B2105" s="2">
-        <v>102351853</v>
+        <v>102502871</v>
       </c>
       <c r="C2105" s="1" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="D2105" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2106" spans="1:4">
@@ -30936,13 +30939,13 @@
         <v>361</v>
       </c>
       <c r="B2106" s="2">
-        <v>102369579</v>
+        <v>102503478</v>
       </c>
       <c r="C2106" s="1" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="D2106" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2107" spans="1:4">
@@ -30950,13 +30953,13 @@
         <v>361</v>
       </c>
       <c r="B2107" s="2">
-        <v>102370804</v>
+        <v>102507584</v>
       </c>
       <c r="C2107" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2107" s="2">
         <v>22</v>
-      </c>
-      <c r="D2107" s="2">
-        <v>24</v>
       </c>
     </row>
     <row r="2108" spans="1:4">
@@ -30964,13 +30967,13 @@
         <v>361</v>
       </c>
       <c r="B2108" s="2">
-        <v>102371964</v>
+        <v>102509109</v>
       </c>
       <c r="C2108" s="1" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="D2108" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2109" spans="1:4">
@@ -30978,13 +30981,13 @@
         <v>361</v>
       </c>
       <c r="B2109" s="2">
-        <v>102456914</v>
+        <v>102511945</v>
       </c>
       <c r="C2109" s="1" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D2109" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2110" spans="1:4">
@@ -30992,13 +30995,13 @@
         <v>361</v>
       </c>
       <c r="B2110" s="2">
-        <v>102456984</v>
+        <v>102517330</v>
       </c>
       <c r="C2110" s="1" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="D2110" s="2">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2111" spans="1:4">
@@ -31006,13 +31009,13 @@
         <v>361</v>
       </c>
       <c r="B2111" s="2">
-        <v>102456993</v>
+        <v>102517333</v>
       </c>
       <c r="C2111" s="1" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="D2111" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2112" spans="1:4">
@@ -31020,13 +31023,13 @@
         <v>361</v>
       </c>
       <c r="B2112" s="2">
-        <v>102457124</v>
+        <v>102517346</v>
       </c>
       <c r="C2112" s="1" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D2112" s="2">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2113" spans="1:4">
@@ -31034,13 +31037,13 @@
         <v>361</v>
       </c>
       <c r="B2113" s="2">
-        <v>102457937</v>
+        <v>102821757</v>
       </c>
       <c r="C2113" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="D2113" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2114" spans="1:4">
@@ -31048,13 +31051,13 @@
         <v>361</v>
       </c>
       <c r="B2114" s="2">
-        <v>102458550</v>
+        <v>102821761</v>
       </c>
       <c r="C2114" s="1" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="D2114" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2115" spans="1:4">
@@ -31062,13 +31065,13 @@
         <v>361</v>
       </c>
       <c r="B2115" s="2">
-        <v>102464498</v>
+        <v>102830253</v>
       </c>
       <c r="C2115" s="1" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="D2115" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2116" spans="1:4">
@@ -31076,13 +31079,13 @@
         <v>361</v>
       </c>
       <c r="B2116" s="2">
-        <v>102466917</v>
+        <v>102830316</v>
       </c>
       <c r="C2116" s="1" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D2116" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2117" spans="1:4">
@@ -31090,13 +31093,13 @@
         <v>361</v>
       </c>
       <c r="B2117" s="2">
-        <v>102477288</v>
+        <v>102831065</v>
       </c>
       <c r="C2117" s="1" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="D2117" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2118" spans="1:4">
@@ -31104,13 +31107,13 @@
         <v>361</v>
       </c>
       <c r="B2118" s="2">
-        <v>102477293</v>
+        <v>102837399</v>
       </c>
       <c r="C2118" s="1" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="D2118" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2119" spans="1:4">
@@ -31118,13 +31121,13 @@
         <v>361</v>
       </c>
       <c r="B2119" s="2">
-        <v>102477371</v>
+        <v>102843519</v>
       </c>
       <c r="C2119" s="1" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="D2119" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2120" spans="1:4">
@@ -31132,13 +31135,13 @@
         <v>361</v>
       </c>
       <c r="B2120" s="2">
-        <v>102477422</v>
+        <v>102855952</v>
       </c>
       <c r="C2120" s="1" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="D2120" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2121" spans="1:4">
@@ -31146,13 +31149,13 @@
         <v>361</v>
       </c>
       <c r="B2121" s="2">
-        <v>102477510</v>
+        <v>102864715</v>
       </c>
       <c r="C2121" s="1" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="D2121" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2122" spans="1:4">
@@ -31160,13 +31163,13 @@
         <v>361</v>
       </c>
       <c r="B2122" s="2">
-        <v>102478278</v>
+        <v>102871040</v>
       </c>
       <c r="C2122" s="1" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="D2122" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2123" spans="1:4">
@@ -31174,13 +31177,13 @@
         <v>361</v>
       </c>
       <c r="B2123" s="2">
-        <v>102482237</v>
+        <v>102879799</v>
       </c>
       <c r="C2123" s="1" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="D2123" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2124" spans="1:4">
@@ -31188,13 +31191,13 @@
         <v>361</v>
       </c>
       <c r="B2124" s="2">
-        <v>102484482</v>
+        <v>102884064</v>
       </c>
       <c r="C2124" s="1" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="D2124" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2125" spans="1:4">
@@ -31202,10 +31205,10 @@
         <v>361</v>
       </c>
       <c r="B2125" s="2">
-        <v>102502720</v>
+        <v>102884675</v>
       </c>
       <c r="C2125" s="1" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="D2125" s="2">
         <v>22</v>
@@ -31216,13 +31219,13 @@
         <v>361</v>
       </c>
       <c r="B2126" s="2">
-        <v>102502737</v>
+        <v>102908267</v>
       </c>
       <c r="C2126" s="1" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="D2126" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2127" spans="1:4">
@@ -31230,10 +31233,10 @@
         <v>361</v>
       </c>
       <c r="B2127" s="2">
-        <v>102502871</v>
+        <v>103028093</v>
       </c>
       <c r="C2127" s="1" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="D2127" s="2">
         <v>22</v>
@@ -31244,10 +31247,10 @@
         <v>361</v>
       </c>
       <c r="B2128" s="2">
-        <v>102503478</v>
+        <v>103060430</v>
       </c>
       <c r="C2128" s="1" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="D2128" s="2">
         <v>21</v>
@@ -31258,13 +31261,13 @@
         <v>361</v>
       </c>
       <c r="B2129" s="2">
-        <v>102507584</v>
+        <v>103060435</v>
       </c>
       <c r="C2129" s="1" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="D2129" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2130" spans="1:4">
@@ -31272,13 +31275,13 @@
         <v>361</v>
       </c>
       <c r="B2130" s="2">
-        <v>102509109</v>
+        <v>103060453</v>
       </c>
       <c r="C2130" s="1" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="D2130" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2131" spans="1:4">
@@ -31286,13 +31289,13 @@
         <v>361</v>
       </c>
       <c r="B2131" s="2">
-        <v>102511945</v>
+        <v>103060459</v>
       </c>
       <c r="C2131" s="1" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="D2131" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2132" spans="1:4">
@@ -31300,13 +31303,13 @@
         <v>361</v>
       </c>
       <c r="B2132" s="2">
-        <v>102517330</v>
+        <v>103060462</v>
       </c>
       <c r="C2132" s="1" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="D2132" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2133" spans="1:4">
@@ -31314,13 +31317,13 @@
         <v>361</v>
       </c>
       <c r="B2133" s="2">
-        <v>102517333</v>
+        <v>103060467</v>
       </c>
       <c r="C2133" s="1" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="D2133" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2134" spans="1:4">
@@ -31328,10 +31331,10 @@
         <v>361</v>
       </c>
       <c r="B2134" s="2">
-        <v>102517346</v>
+        <v>103060471</v>
       </c>
       <c r="C2134" s="1" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D2134" s="2">
         <v>20</v>
@@ -31342,13 +31345,13 @@
         <v>361</v>
       </c>
       <c r="B2135" s="2">
-        <v>102821757</v>
+        <v>103082092</v>
       </c>
       <c r="C2135" s="1" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="D2135" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2136" spans="1:4">
@@ -31356,13 +31359,13 @@
         <v>361</v>
       </c>
       <c r="B2136" s="2">
-        <v>102821761</v>
+        <v>103082095</v>
       </c>
       <c r="C2136" s="1" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="D2136" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2137" spans="1:4">
@@ -31370,10 +31373,10 @@
         <v>361</v>
       </c>
       <c r="B2137" s="2">
-        <v>102830253</v>
+        <v>103082112</v>
       </c>
       <c r="C2137" s="1" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="D2137" s="2">
         <v>22</v>
@@ -31384,13 +31387,13 @@
         <v>361</v>
       </c>
       <c r="B2138" s="2">
-        <v>102830316</v>
+        <v>103082113</v>
       </c>
       <c r="C2138" s="1" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="D2138" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2139" spans="1:4">
@@ -31398,13 +31401,13 @@
         <v>361</v>
       </c>
       <c r="B2139" s="2">
-        <v>102831065</v>
+        <v>103082118</v>
       </c>
       <c r="C2139" s="1" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="D2139" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2140" spans="1:4">
@@ -31412,13 +31415,13 @@
         <v>361</v>
       </c>
       <c r="B2140" s="2">
-        <v>102837399</v>
+        <v>103082119</v>
       </c>
       <c r="C2140" s="1" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="D2140" s="2">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2141" spans="1:4">
@@ -31426,13 +31429,13 @@
         <v>361</v>
       </c>
       <c r="B2141" s="2">
-        <v>102843519</v>
+        <v>103082121</v>
       </c>
       <c r="C2141" s="1" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="D2141" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2142" spans="1:4">
@@ -31440,13 +31443,13 @@
         <v>361</v>
       </c>
       <c r="B2142" s="2">
-        <v>102850964</v>
+        <v>103082161</v>
       </c>
       <c r="C2142" s="1" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="D2142" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2143" spans="1:4">
@@ -31454,10 +31457,10 @@
         <v>361</v>
       </c>
       <c r="B2143" s="2">
-        <v>102855952</v>
+        <v>103082166</v>
       </c>
       <c r="C2143" s="1" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="D2143" s="2">
         <v>20</v>
@@ -31468,10 +31471,10 @@
         <v>361</v>
       </c>
       <c r="B2144" s="2">
-        <v>102864715</v>
+        <v>103082385</v>
       </c>
       <c r="C2144" s="1" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="D2144" s="2">
         <v>19</v>
@@ -31482,13 +31485,13 @@
         <v>361</v>
       </c>
       <c r="B2145" s="2">
-        <v>102871040</v>
+        <v>103085298</v>
       </c>
       <c r="C2145" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="D2145" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2146" spans="1:4">
@@ -31496,13 +31499,13 @@
         <v>361</v>
       </c>
       <c r="B2146" s="2">
-        <v>102879799</v>
+        <v>103088009</v>
       </c>
       <c r="C2146" s="1" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="D2146" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2147" spans="1:4">
@@ -31510,13 +31513,13 @@
         <v>361</v>
       </c>
       <c r="B2147" s="2">
-        <v>102884064</v>
+        <v>103092092</v>
       </c>
       <c r="C2147" s="1" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="D2147" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2148" spans="1:4">
@@ -31524,13 +31527,13 @@
         <v>361</v>
       </c>
       <c r="B2148" s="2">
-        <v>102884675</v>
+        <v>103092141</v>
       </c>
       <c r="C2148" s="1" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="D2148" s="2">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2149" spans="1:4">
@@ -31538,13 +31541,13 @@
         <v>361</v>
       </c>
       <c r="B2149" s="2">
-        <v>102908267</v>
+        <v>103092310</v>
       </c>
       <c r="C2149" s="1" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="D2149" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2150" spans="1:4">
@@ -31552,13 +31555,13 @@
         <v>361</v>
       </c>
       <c r="B2150" s="2">
-        <v>103001864</v>
+        <v>103092316</v>
       </c>
       <c r="C2150" s="1" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="D2150" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2151" spans="1:4">
@@ -31566,13 +31569,13 @@
         <v>361</v>
       </c>
       <c r="B2151" s="2">
-        <v>103028093</v>
+        <v>103101206</v>
       </c>
       <c r="C2151" s="1" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="D2151" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2152" spans="1:4">
@@ -31580,13 +31583,13 @@
         <v>361</v>
       </c>
       <c r="B2152" s="2">
-        <v>103060430</v>
+        <v>103101215</v>
       </c>
       <c r="C2152" s="1" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="D2152" s="2">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2153" spans="1:4">
@@ -31594,13 +31597,13 @@
         <v>361</v>
       </c>
       <c r="B2153" s="2">
-        <v>103060435</v>
+        <v>103101217</v>
       </c>
       <c r="C2153" s="1" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="D2153" s="2">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2154" spans="1:4">
@@ -31608,10 +31611,10 @@
         <v>361</v>
       </c>
       <c r="B2154" s="2">
-        <v>103060453</v>
+        <v>103103196</v>
       </c>
       <c r="C2154" s="1" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="D2154" s="2">
         <v>19</v>
@@ -31622,13 +31625,13 @@
         <v>361</v>
       </c>
       <c r="B2155" s="2">
-        <v>103060459</v>
+        <v>103103198</v>
       </c>
       <c r="C2155" s="1" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="D2155" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2156" spans="1:4">
@@ -31636,13 +31639,13 @@
         <v>361</v>
       </c>
       <c r="B2156" s="2">
-        <v>103060462</v>
+        <v>103103213</v>
       </c>
       <c r="C2156" s="1" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="D2156" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2157" spans="1:4">
@@ -31650,10 +31653,10 @@
         <v>361</v>
       </c>
       <c r="B2157" s="2">
-        <v>103060467</v>
+        <v>103105143</v>
       </c>
       <c r="C2157" s="1" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="D2157" s="2">
         <v>20</v>
@@ -31664,10 +31667,10 @@
         <v>361</v>
       </c>
       <c r="B2158" s="2">
-        <v>103060471</v>
+        <v>103109089</v>
       </c>
       <c r="C2158" s="1" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="D2158" s="2">
         <v>22</v>
@@ -31678,13 +31681,13 @@
         <v>361</v>
       </c>
       <c r="B2159" s="2">
-        <v>103082092</v>
+        <v>103109090</v>
       </c>
       <c r="C2159" s="1" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="D2159" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2160" spans="1:4">
@@ -31692,13 +31695,13 @@
         <v>361</v>
       </c>
       <c r="B2160" s="2">
-        <v>103082095</v>
+        <v>103109091</v>
       </c>
       <c r="C2160" s="1" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="D2160" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2161" spans="1:4">
@@ -31706,13 +31709,13 @@
         <v>361</v>
       </c>
       <c r="B2161" s="2">
-        <v>103082112</v>
+        <v>103109136</v>
       </c>
       <c r="C2161" s="1" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="D2161" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2162" spans="1:4">
@@ -31720,13 +31723,13 @@
         <v>361</v>
       </c>
       <c r="B2162" s="2">
-        <v>103082113</v>
+        <v>103109151</v>
       </c>
       <c r="C2162" s="1" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="D2162" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2163" spans="1:4">
@@ -31734,13 +31737,13 @@
         <v>361</v>
       </c>
       <c r="B2163" s="2">
-        <v>103082118</v>
+        <v>103109336</v>
       </c>
       <c r="C2163" s="1" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="D2163" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2164" spans="1:4">
@@ -31748,13 +31751,13 @@
         <v>361</v>
       </c>
       <c r="B2164" s="2">
-        <v>103082119</v>
+        <v>103109339</v>
       </c>
       <c r="C2164" s="1" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="D2164" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2165" spans="1:4">
@@ -31762,13 +31765,13 @@
         <v>361</v>
       </c>
       <c r="B2165" s="2">
-        <v>103082121</v>
+        <v>103109343</v>
       </c>
       <c r="C2165" s="1" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="D2165" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2166" spans="1:4">
@@ -31776,13 +31779,13 @@
         <v>361</v>
       </c>
       <c r="B2166" s="2">
-        <v>103082160</v>
+        <v>103109357</v>
       </c>
       <c r="C2166" s="1" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="D2166" s="2">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2167" spans="1:4">
@@ -31790,13 +31793,13 @@
         <v>361</v>
       </c>
       <c r="B2167" s="2">
-        <v>103082161</v>
+        <v>103110013</v>
       </c>
       <c r="C2167" s="1" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="D2167" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2168" spans="1:4">
@@ -31804,13 +31807,13 @@
         <v>361</v>
       </c>
       <c r="B2168" s="2">
-        <v>103082166</v>
+        <v>103110453</v>
       </c>
       <c r="C2168" s="1" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="D2168" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2169" spans="1:4">
@@ -31818,13 +31821,13 @@
         <v>361</v>
       </c>
       <c r="B2169" s="2">
-        <v>103082385</v>
+        <v>103111713</v>
       </c>
       <c r="C2169" s="1" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="D2169" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2170" spans="1:4">
@@ -31832,13 +31835,13 @@
         <v>361</v>
       </c>
       <c r="B2170" s="2">
-        <v>103085298</v>
+        <v>103111920</v>
       </c>
       <c r="C2170" s="1" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="D2170" s="2">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2171" spans="1:4">
@@ -31846,13 +31849,13 @@
         <v>361</v>
       </c>
       <c r="B2171" s="2">
-        <v>103088009</v>
+        <v>103111956</v>
       </c>
       <c r="C2171" s="1" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="D2171" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2172" spans="1:4">
@@ -31860,10 +31863,10 @@
         <v>361</v>
       </c>
       <c r="B2172" s="2">
-        <v>103092092</v>
+        <v>103113926</v>
       </c>
       <c r="C2172" s="1" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="D2172" s="2">
         <v>21</v>
@@ -31874,13 +31877,13 @@
         <v>361</v>
       </c>
       <c r="B2173" s="2">
-        <v>103092141</v>
+        <v>103115341</v>
       </c>
       <c r="C2173" s="1" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="D2173" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2174" spans="1:4">
@@ -31888,13 +31891,13 @@
         <v>361</v>
       </c>
       <c r="B2174" s="2">
-        <v>103092310</v>
+        <v>103116487</v>
       </c>
       <c r="C2174" s="1" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="D2174" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2175" spans="1:4">
@@ -31902,10 +31905,10 @@
         <v>361</v>
       </c>
       <c r="B2175" s="2">
-        <v>103092316</v>
+        <v>103116496</v>
       </c>
       <c r="C2175" s="1" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="D2175" s="2">
         <v>17</v>
@@ -31916,13 +31919,13 @@
         <v>361</v>
       </c>
       <c r="B2176" s="2">
-        <v>103101197</v>
+        <v>103117188</v>
       </c>
       <c r="C2176" s="1" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="D2176" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2177" spans="1:4">
@@ -31930,10 +31933,10 @@
         <v>361</v>
       </c>
       <c r="B2177" s="2">
-        <v>103101206</v>
+        <v>103121097</v>
       </c>
       <c r="C2177" s="1" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="D2177" s="2">
         <v>18</v>
@@ -31944,10 +31947,10 @@
         <v>361</v>
       </c>
       <c r="B2178" s="2">
-        <v>103101215</v>
+        <v>103121098</v>
       </c>
       <c r="C2178" s="1" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="D2178" s="2">
         <v>21</v>
@@ -31958,13 +31961,13 @@
         <v>361</v>
       </c>
       <c r="B2179" s="2">
-        <v>103101217</v>
+        <v>103125208</v>
       </c>
       <c r="C2179" s="1" t="s">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="D2179" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2180" spans="1:4">
@@ -31972,13 +31975,13 @@
         <v>361</v>
       </c>
       <c r="B2180" s="2">
-        <v>103103196</v>
+        <v>103125228</v>
       </c>
       <c r="C2180" s="1" t="s">
-        <v>158</v>
+        <v>208</v>
       </c>
       <c r="D2180" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2181" spans="1:4">
@@ -31986,13 +31989,13 @@
         <v>361</v>
       </c>
       <c r="B2181" s="2">
-        <v>103103198</v>
+        <v>103125229</v>
       </c>
       <c r="C2181" s="1" t="s">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="D2181" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2182" spans="1:4">
@@ -32000,13 +32003,13 @@
         <v>361</v>
       </c>
       <c r="B2182" s="2">
-        <v>103103213</v>
+        <v>103127936</v>
       </c>
       <c r="C2182" s="1" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="D2182" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2183" spans="1:4">
@@ -32014,13 +32017,13 @@
         <v>361</v>
       </c>
       <c r="B2183" s="2">
-        <v>103105143</v>
+        <v>103130519</v>
       </c>
       <c r="C2183" s="1" t="s">
-        <v>162</v>
+        <v>226</v>
       </c>
       <c r="D2183" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2184" spans="1:4">
@@ -32028,13 +32031,13 @@
         <v>361</v>
       </c>
       <c r="B2184" s="2">
-        <v>103109089</v>
+        <v>103132423</v>
       </c>
       <c r="C2184" s="1" t="s">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="D2184" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2185" spans="1:4">
@@ -32042,13 +32045,13 @@
         <v>361</v>
       </c>
       <c r="B2185" s="2">
-        <v>103109090</v>
+        <v>103132424</v>
       </c>
       <c r="C2185" s="1" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="D2185" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2186" spans="1:4">
@@ -32056,13 +32059,13 @@
         <v>361</v>
       </c>
       <c r="B2186" s="2">
-        <v>103109091</v>
+        <v>103133036</v>
       </c>
       <c r="C2186" s="1" t="s">
-        <v>168</v>
+        <v>235</v>
       </c>
       <c r="D2186" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2187" spans="1:4">
@@ -32070,13 +32073,13 @@
         <v>361</v>
       </c>
       <c r="B2187" s="2">
-        <v>103109136</v>
+        <v>103136107</v>
       </c>
       <c r="C2187" s="1" t="s">
-        <v>170</v>
+        <v>242</v>
       </c>
       <c r="D2187" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2188" spans="1:4">
@@ -32084,13 +32087,13 @@
         <v>361</v>
       </c>
       <c r="B2188" s="2">
-        <v>103109151</v>
+        <v>103139871</v>
       </c>
       <c r="C2188" s="1" t="s">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="D2188" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2189" spans="1:4">
@@ -32098,13 +32101,13 @@
         <v>361</v>
       </c>
       <c r="B2189" s="2">
-        <v>103109336</v>
+        <v>103145144</v>
       </c>
       <c r="C2189" s="1" t="s">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="D2189" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2190" spans="1:4">
@@ -32112,13 +32115,13 @@
         <v>361</v>
       </c>
       <c r="B2190" s="2">
-        <v>103109339</v>
+        <v>103169793</v>
       </c>
       <c r="C2190" s="1" t="s">
-        <v>173</v>
+        <v>258</v>
       </c>
       <c r="D2190" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2191" spans="1:4">
@@ -32126,13 +32129,13 @@
         <v>361</v>
       </c>
       <c r="B2191" s="2">
-        <v>103109343</v>
+        <v>103169795</v>
       </c>
       <c r="C2191" s="1" t="s">
-        <v>174</v>
+        <v>259</v>
       </c>
       <c r="D2191" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2192" spans="1:4">
@@ -32140,13 +32143,13 @@
         <v>361</v>
       </c>
       <c r="B2192" s="2">
-        <v>103109357</v>
+        <v>103169797</v>
       </c>
       <c r="C2192" s="1" t="s">
-        <v>175</v>
+        <v>260</v>
       </c>
       <c r="D2192" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2193" spans="1:4">
@@ -32154,13 +32157,13 @@
         <v>361</v>
       </c>
       <c r="B2193" s="2">
-        <v>103110013</v>
+        <v>103169814</v>
       </c>
       <c r="C2193" s="1" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="D2193" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2194" spans="1:4">
@@ -32168,13 +32171,13 @@
         <v>361</v>
       </c>
       <c r="B2194" s="2">
-        <v>103110453</v>
+        <v>103169816</v>
       </c>
       <c r="C2194" s="1" t="s">
-        <v>178</v>
+        <v>263</v>
       </c>
       <c r="D2194" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2195" spans="1:4">
@@ -32182,13 +32185,13 @@
         <v>361</v>
       </c>
       <c r="B2195" s="2">
-        <v>103111713</v>
+        <v>103171084</v>
       </c>
       <c r="C2195" s="1" t="s">
-        <v>180</v>
+        <v>272</v>
       </c>
       <c r="D2195" s="2">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2196" spans="1:4">
@@ -32196,13 +32199,13 @@
         <v>361</v>
       </c>
       <c r="B2196" s="2">
-        <v>103111920</v>
+        <v>103171103</v>
       </c>
       <c r="C2196" s="1" t="s">
-        <v>181</v>
+        <v>273</v>
       </c>
       <c r="D2196" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2197" spans="1:4">
@@ -32210,13 +32213,13 @@
         <v>361</v>
       </c>
       <c r="B2197" s="2">
-        <v>103111956</v>
+        <v>103173195</v>
       </c>
       <c r="C2197" s="1" t="s">
-        <v>182</v>
+        <v>276</v>
       </c>
       <c r="D2197" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2198" spans="1:4">
@@ -32224,13 +32227,13 @@
         <v>361</v>
       </c>
       <c r="B2198" s="2">
-        <v>103113926</v>
+        <v>103173197</v>
       </c>
       <c r="C2198" s="1" t="s">
-        <v>183</v>
+        <v>277</v>
       </c>
       <c r="D2198" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2199" spans="1:4">
@@ -32238,13 +32241,13 @@
         <v>361</v>
       </c>
       <c r="B2199" s="2">
-        <v>103115341</v>
+        <v>103283831</v>
       </c>
       <c r="C2199" s="1" t="s">
-        <v>184</v>
+        <v>341</v>
       </c>
       <c r="D2199" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2200" spans="1:4">
@@ -32252,10 +32255,10 @@
         <v>361</v>
       </c>
       <c r="B2200" s="2">
-        <v>103116487</v>
+        <v>103293732</v>
       </c>
       <c r="C2200" s="1" t="s">
-        <v>186</v>
+        <v>286</v>
       </c>
       <c r="D2200" s="2">
         <v>22</v>
@@ -32266,13 +32269,13 @@
         <v>361</v>
       </c>
       <c r="B2201" s="2">
-        <v>103116496</v>
+        <v>103293737</v>
       </c>
       <c r="C2201" s="1" t="s">
-        <v>187</v>
+        <v>287</v>
       </c>
       <c r="D2201" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2202" spans="1:4">
@@ -32280,10 +32283,10 @@
         <v>361</v>
       </c>
       <c r="B2202" s="2">
-        <v>103117188</v>
+        <v>103293745</v>
       </c>
       <c r="C2202" s="1" t="s">
-        <v>189</v>
+        <v>342</v>
       </c>
       <c r="D2202" s="2">
         <v>20</v>
@@ -32294,13 +32297,13 @@
         <v>361</v>
       </c>
       <c r="B2203" s="2">
-        <v>103119654</v>
+        <v>103293751</v>
       </c>
       <c r="C2203" s="1" t="s">
-        <v>191</v>
+        <v>288</v>
       </c>
       <c r="D2203" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2204" spans="1:4">
@@ -32308,10 +32311,10 @@
         <v>361</v>
       </c>
       <c r="B2204" s="2">
-        <v>103121097</v>
+        <v>103293756</v>
       </c>
       <c r="C2204" s="1" t="s">
-        <v>193</v>
+        <v>289</v>
       </c>
       <c r="D2204" s="2">
         <v>17</v>
@@ -32322,10 +32325,10 @@
         <v>361</v>
       </c>
       <c r="B2205" s="2">
-        <v>103121098</v>
+        <v>103293766</v>
       </c>
       <c r="C2205" s="1" t="s">
-        <v>194</v>
+        <v>290</v>
       </c>
       <c r="D2205" s="2">
         <v>21</v>
@@ -32336,13 +32339,13 @@
         <v>361</v>
       </c>
       <c r="B2206" s="2">
-        <v>103124232</v>
+        <v>103293773</v>
       </c>
       <c r="C2206" s="1" t="s">
-        <v>198</v>
+        <v>291</v>
       </c>
       <c r="D2206" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2207" spans="1:4">
@@ -32350,13 +32353,13 @@
         <v>361</v>
       </c>
       <c r="B2207" s="2">
-        <v>103124248</v>
+        <v>103294755</v>
       </c>
       <c r="C2207" s="1" t="s">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D2207" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2208" spans="1:4">
@@ -32364,13 +32367,13 @@
         <v>361</v>
       </c>
       <c r="B2208" s="2">
-        <v>103124249</v>
+        <v>103296160</v>
       </c>
       <c r="C2208" s="1" t="s">
-        <v>201</v>
+        <v>292</v>
       </c>
       <c r="D2208" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2209" spans="1:4">
@@ -32378,10 +32381,10 @@
         <v>361</v>
       </c>
       <c r="B2209" s="2">
-        <v>103124250</v>
+        <v>103296167</v>
       </c>
       <c r="C2209" s="1" t="s">
-        <v>202</v>
+        <v>345</v>
       </c>
       <c r="D2209" s="2">
         <v>20</v>
@@ -32392,13 +32395,13 @@
         <v>361</v>
       </c>
       <c r="B2210" s="2">
-        <v>103124266</v>
+        <v>103297566</v>
       </c>
       <c r="C2210" s="1" t="s">
-        <v>203</v>
+        <v>293</v>
       </c>
       <c r="D2210" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2211" spans="1:4">
@@ -32406,13 +32409,13 @@
         <v>361</v>
       </c>
       <c r="B2211" s="2">
-        <v>103124268</v>
+        <v>103300418</v>
       </c>
       <c r="C2211" s="1" t="s">
-        <v>204</v>
+        <v>294</v>
       </c>
       <c r="D2211" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2212" spans="1:4">
@@ -32420,13 +32423,13 @@
         <v>361</v>
       </c>
       <c r="B2212" s="2">
-        <v>103125208</v>
+        <v>103304841</v>
       </c>
       <c r="C2212" s="1" t="s">
-        <v>206</v>
+        <v>290</v>
       </c>
       <c r="D2212" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2213" spans="1:4">
@@ -32434,10 +32437,10 @@
         <v>361</v>
       </c>
       <c r="B2213" s="2">
-        <v>103125228</v>
+        <v>103304846</v>
       </c>
       <c r="C2213" s="1" t="s">
-        <v>208</v>
+        <v>348</v>
       </c>
       <c r="D2213" s="2">
         <v>20</v>
@@ -32448,13 +32451,13 @@
         <v>361</v>
       </c>
       <c r="B2214" s="2">
-        <v>103125229</v>
+        <v>103304863</v>
       </c>
       <c r="C2214" s="1" t="s">
-        <v>209</v>
+        <v>349</v>
       </c>
       <c r="D2214" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2215" spans="1:4">
@@ -32462,13 +32465,13 @@
         <v>361</v>
       </c>
       <c r="B2215" s="2">
-        <v>103126016</v>
+        <v>103304866</v>
       </c>
       <c r="C2215" s="1" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="D2215" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2216" spans="1:4">
@@ -32476,13 +32479,13 @@
         <v>361</v>
       </c>
       <c r="B2216" s="2">
-        <v>103127936</v>
+        <v>103304868</v>
       </c>
       <c r="C2216" s="1" t="s">
-        <v>211</v>
+        <v>350</v>
       </c>
       <c r="D2216" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2217" spans="1:4">
@@ -32490,13 +32493,13 @@
         <v>361</v>
       </c>
       <c r="B2217" s="2">
-        <v>103129049</v>
+        <v>103304875</v>
       </c>
       <c r="C2217" s="1" t="s">
-        <v>215</v>
+        <v>295</v>
       </c>
       <c r="D2217" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2218" spans="1:4">
@@ -32504,13 +32507,13 @@
         <v>361</v>
       </c>
       <c r="B2218" s="2">
-        <v>103129359</v>
+        <v>103305150</v>
       </c>
       <c r="C2218" s="1" t="s">
-        <v>219</v>
+        <v>296</v>
       </c>
       <c r="D2218" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2219" spans="1:4">
@@ -32518,13 +32521,13 @@
         <v>361</v>
       </c>
       <c r="B2219" s="2">
-        <v>103129371</v>
+        <v>103305154</v>
       </c>
       <c r="C2219" s="1" t="s">
-        <v>220</v>
+        <v>297</v>
       </c>
       <c r="D2219" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2220" spans="1:4">
@@ -32532,13 +32535,13 @@
         <v>361</v>
       </c>
       <c r="B2220" s="2">
-        <v>103129415</v>
+        <v>103305160</v>
       </c>
       <c r="C2220" s="1" t="s">
-        <v>222</v>
+        <v>298</v>
       </c>
       <c r="D2220" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2221" spans="1:4">
@@ -32546,108 +32549,108 @@
         <v>361</v>
       </c>
       <c r="B2221" s="2">
-        <v>103129416</v>
+        <v>103305165</v>
       </c>
       <c r="C2221" s="1" t="s">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="D2221" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2222" spans="1:4">
       <c r="A2222" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2222" s="2">
-        <v>103130518</v>
+        <v>102029874</v>
       </c>
       <c r="C2222" s="1" t="s">
-        <v>225</v>
+        <v>6</v>
       </c>
       <c r="D2222" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2223" spans="1:4">
       <c r="A2223" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2223" s="2">
-        <v>103130519</v>
+        <v>102173363</v>
       </c>
       <c r="C2223" s="1" t="s">
-        <v>226</v>
+        <v>7</v>
       </c>
       <c r="D2223" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2224" spans="1:4">
       <c r="A2224" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2224" s="2">
-        <v>103132423</v>
+        <v>102211179</v>
       </c>
       <c r="C2224" s="1" t="s">
-        <v>229</v>
+        <v>10</v>
       </c>
       <c r="D2224" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2225" spans="1:4">
       <c r="A2225" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2225" s="2">
-        <v>103132424</v>
+        <v>102219144</v>
       </c>
       <c r="C2225" s="1" t="s">
-        <v>230</v>
+        <v>12</v>
       </c>
       <c r="D2225" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2226" spans="1:4">
       <c r="A2226" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2226" s="2">
-        <v>103132932</v>
+        <v>102326882</v>
       </c>
       <c r="C2226" s="1" t="s">
-        <v>231</v>
+        <v>16</v>
       </c>
       <c r="D2226" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2227" spans="1:4">
       <c r="A2227" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2227" s="2">
-        <v>103132933</v>
+        <v>102343359</v>
       </c>
       <c r="C2227" s="1" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="D2227" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2228" spans="1:4">
       <c r="A2228" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2228" s="2">
-        <v>103132934</v>
+        <v>102351853</v>
       </c>
       <c r="C2228" s="1" t="s">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="D2228" s="2">
         <v>21</v>
@@ -32655,209 +32658,209 @@
     </row>
     <row r="2229" spans="1:4">
       <c r="A2229" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2229" s="2">
-        <v>103132938</v>
+        <v>102369579</v>
       </c>
       <c r="C2229" s="1" t="s">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="D2229" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2230" spans="1:4">
       <c r="A2230" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2230" s="2">
-        <v>103133036</v>
+        <v>102370804</v>
       </c>
       <c r="C2230" s="1" t="s">
-        <v>235</v>
+        <v>22</v>
       </c>
       <c r="D2230" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2231" spans="1:4">
       <c r="A2231" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2231" s="2">
-        <v>103133037</v>
+        <v>102371964</v>
       </c>
       <c r="C2231" s="1" t="s">
-        <v>236</v>
+        <v>25</v>
       </c>
       <c r="D2231" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2232" spans="1:4">
       <c r="A2232" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2232" s="2">
-        <v>103133047</v>
+        <v>102456914</v>
       </c>
       <c r="C2232" s="1" t="s">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="D2232" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2233" spans="1:4">
       <c r="A2233" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2233" s="2">
-        <v>103133765</v>
+        <v>102456984</v>
       </c>
       <c r="C2233" s="1" t="s">
-        <v>238</v>
+        <v>28</v>
       </c>
       <c r="D2233" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2234" spans="1:4">
       <c r="A2234" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2234" s="2">
-        <v>103133767</v>
+        <v>102456993</v>
       </c>
       <c r="C2234" s="1" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="D2234" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2235" spans="1:4">
       <c r="A2235" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2235" s="2">
-        <v>103136099</v>
+        <v>102457124</v>
       </c>
       <c r="C2235" s="1" t="s">
-        <v>241</v>
+        <v>30</v>
       </c>
       <c r="D2235" s="2">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2236" spans="1:4">
       <c r="A2236" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2236" s="2">
-        <v>103136107</v>
+        <v>102457937</v>
       </c>
       <c r="C2236" s="1" t="s">
-        <v>242</v>
+        <v>33</v>
       </c>
       <c r="D2236" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2237" spans="1:4">
       <c r="A2237" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2237" s="2">
-        <v>103136108</v>
+        <v>102458550</v>
       </c>
       <c r="C2237" s="1" t="s">
-        <v>243</v>
+        <v>35</v>
       </c>
       <c r="D2237" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2238" spans="1:4">
       <c r="A2238" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2238" s="2">
-        <v>103137756</v>
+        <v>102464498</v>
       </c>
       <c r="C2238" s="1" t="s">
-        <v>245</v>
+        <v>36</v>
       </c>
       <c r="D2238" s="2">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2239" spans="1:4">
       <c r="A2239" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2239" s="2">
-        <v>103139871</v>
+        <v>102466917</v>
       </c>
       <c r="C2239" s="1" t="s">
-        <v>246</v>
+        <v>44</v>
       </c>
       <c r="D2239" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2240" spans="1:4">
       <c r="A2240" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2240" s="2">
-        <v>103142315</v>
+        <v>102477288</v>
       </c>
       <c r="C2240" s="1" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="D2240" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2241" spans="1:4">
       <c r="A2241" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2241" s="2">
-        <v>103142316</v>
+        <v>102477293</v>
       </c>
       <c r="C2241" s="1" t="s">
-        <v>251</v>
+        <v>48</v>
       </c>
       <c r="D2241" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2242" spans="1:4">
       <c r="A2242" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2242" s="2">
-        <v>103145144</v>
+        <v>102477371</v>
       </c>
       <c r="C2242" s="1" t="s">
-        <v>252</v>
+        <v>49</v>
       </c>
       <c r="D2242" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2243" spans="1:4">
       <c r="A2243" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2243" s="2">
-        <v>103145154</v>
+        <v>102477422</v>
       </c>
       <c r="C2243" s="1" t="s">
-        <v>253</v>
+        <v>50</v>
       </c>
       <c r="D2243" s="2">
         <v>20</v>
@@ -32865,13 +32868,13 @@
     </row>
     <row r="2244" spans="1:4">
       <c r="A2244" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2244" s="2">
-        <v>103145155</v>
+        <v>102477510</v>
       </c>
       <c r="C2244" s="1" t="s">
-        <v>254</v>
+        <v>51</v>
       </c>
       <c r="D2244" s="2">
         <v>19</v>
@@ -32879,69 +32882,69 @@
     </row>
     <row r="2245" spans="1:4">
       <c r="A2245" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2245" s="2">
-        <v>103145248</v>
+        <v>102478278</v>
       </c>
       <c r="C2245" s="1" t="s">
-        <v>255</v>
+        <v>54</v>
       </c>
       <c r="D2245" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2246" spans="1:4">
       <c r="A2246" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2246" s="2">
-        <v>103146147</v>
+        <v>102482237</v>
       </c>
       <c r="C2246" s="1" t="s">
-        <v>256</v>
+        <v>55</v>
       </c>
       <c r="D2246" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2247" spans="1:4">
       <c r="A2247" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2247" s="2">
-        <v>103169793</v>
+        <v>102484482</v>
       </c>
       <c r="C2247" s="1" t="s">
-        <v>258</v>
+        <v>56</v>
       </c>
       <c r="D2247" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2248" spans="1:4">
       <c r="A2248" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2248" s="2">
-        <v>103169795</v>
+        <v>102502720</v>
       </c>
       <c r="C2248" s="1" t="s">
-        <v>259</v>
+        <v>58</v>
       </c>
       <c r="D2248" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2249" spans="1:4">
       <c r="A2249" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2249" s="2">
-        <v>103169797</v>
+        <v>102502737</v>
       </c>
       <c r="C2249" s="1" t="s">
-        <v>260</v>
+        <v>61</v>
       </c>
       <c r="D2249" s="2">
         <v>22</v>
@@ -32949,27 +32952,27 @@
     </row>
     <row r="2250" spans="1:4">
       <c r="A2250" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2250" s="2">
-        <v>103169814</v>
+        <v>102502871</v>
       </c>
       <c r="C2250" s="1" t="s">
-        <v>262</v>
+        <v>67</v>
       </c>
       <c r="D2250" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2251" spans="1:4">
       <c r="A2251" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2251" s="2">
-        <v>103169816</v>
+        <v>102503478</v>
       </c>
       <c r="C2251" s="1" t="s">
-        <v>263</v>
+        <v>68</v>
       </c>
       <c r="D2251" s="2">
         <v>21</v>
@@ -32977,27 +32980,27 @@
     </row>
     <row r="2252" spans="1:4">
       <c r="A2252" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2252" s="2">
-        <v>103169997</v>
+        <v>102507584</v>
       </c>
       <c r="C2252" s="1" t="s">
-        <v>264</v>
+        <v>69</v>
       </c>
       <c r="D2252" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2253" spans="1:4">
       <c r="A2253" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2253" s="2">
-        <v>103170002</v>
+        <v>102509109</v>
       </c>
       <c r="C2253" s="1" t="s">
-        <v>265</v>
+        <v>72</v>
       </c>
       <c r="D2253" s="2">
         <v>18</v>
@@ -33005,111 +33008,111 @@
     </row>
     <row r="2254" spans="1:4">
       <c r="A2254" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2254" s="2">
-        <v>103170019</v>
+        <v>102511945</v>
       </c>
       <c r="C2254" s="1" t="s">
-        <v>266</v>
+        <v>73</v>
       </c>
       <c r="D2254" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2255" spans="1:4">
       <c r="A2255" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2255" s="2">
-        <v>103170021</v>
+        <v>102517330</v>
       </c>
       <c r="C2255" s="1" t="s">
-        <v>267</v>
+        <v>75</v>
       </c>
       <c r="D2255" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2256" spans="1:4">
       <c r="A2256" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2256" s="2">
-        <v>103170024</v>
+        <v>102517333</v>
       </c>
       <c r="C2256" s="1" t="s">
-        <v>268</v>
+        <v>76</v>
       </c>
       <c r="D2256" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2257" spans="1:4">
       <c r="A2257" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2257" s="2">
-        <v>103170927</v>
+        <v>102517346</v>
       </c>
       <c r="C2257" s="1" t="s">
-        <v>269</v>
+        <v>77</v>
       </c>
       <c r="D2257" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2258" spans="1:4">
       <c r="A2258" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2258" s="2">
-        <v>103171002</v>
+        <v>102821757</v>
       </c>
       <c r="C2258" s="1" t="s">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="D2258" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2259" spans="1:4">
       <c r="A2259" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2259" s="2">
-        <v>103171084</v>
+        <v>102821761</v>
       </c>
       <c r="C2259" s="1" t="s">
-        <v>272</v>
+        <v>81</v>
       </c>
       <c r="D2259" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2260" spans="1:4">
       <c r="A2260" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2260" s="2">
-        <v>103171103</v>
+        <v>102830253</v>
       </c>
       <c r="C2260" s="1" t="s">
-        <v>273</v>
+        <v>85</v>
       </c>
       <c r="D2260" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2261" spans="1:4">
       <c r="A2261" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2261" s="2">
-        <v>103173195</v>
+        <v>102830316</v>
       </c>
       <c r="C2261" s="1" t="s">
-        <v>276</v>
+        <v>88</v>
       </c>
       <c r="D2261" s="2">
         <v>22</v>
@@ -33117,83 +33120,83 @@
     </row>
     <row r="2262" spans="1:4">
       <c r="A2262" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2262" s="2">
-        <v>103173197</v>
+        <v>102831065</v>
       </c>
       <c r="C2262" s="1" t="s">
-        <v>277</v>
+        <v>92</v>
       </c>
       <c r="D2262" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2263" spans="1:4">
       <c r="A2263" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2263" s="2">
-        <v>103173208</v>
+        <v>102837399</v>
       </c>
       <c r="C2263" s="1" t="s">
-        <v>278</v>
+        <v>94</v>
       </c>
       <c r="D2263" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2264" spans="1:4">
       <c r="A2264" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2264" s="2">
-        <v>103173212</v>
+        <v>102843519</v>
       </c>
       <c r="C2264" s="1" t="s">
-        <v>279</v>
+        <v>96</v>
       </c>
       <c r="D2264" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2265" spans="1:4">
       <c r="A2265" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2265" s="2">
-        <v>103173218</v>
+        <v>102850964</v>
       </c>
       <c r="C2265" s="1" t="s">
-        <v>280</v>
+        <v>101</v>
       </c>
       <c r="D2265" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2266" spans="1:4">
       <c r="A2266" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2266" s="2">
-        <v>103283831</v>
+        <v>102855952</v>
       </c>
       <c r="C2266" s="1" t="s">
-        <v>341</v>
+        <v>102</v>
       </c>
       <c r="D2266" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2267" spans="1:4">
       <c r="A2267" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2267" s="2">
-        <v>103293732</v>
+        <v>102864715</v>
       </c>
       <c r="C2267" s="1" t="s">
-        <v>286</v>
+        <v>103</v>
       </c>
       <c r="D2267" s="2">
         <v>19</v>
@@ -33201,41 +33204,41 @@
     </row>
     <row r="2268" spans="1:4">
       <c r="A2268" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2268" s="2">
-        <v>103293737</v>
+        <v>102871040</v>
       </c>
       <c r="C2268" s="1" t="s">
-        <v>287</v>
+        <v>104</v>
       </c>
       <c r="D2268" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2269" spans="1:4">
       <c r="A2269" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2269" s="2">
-        <v>103293745</v>
+        <v>102879799</v>
       </c>
       <c r="C2269" s="1" t="s">
-        <v>342</v>
+        <v>106</v>
       </c>
       <c r="D2269" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2270" spans="1:4">
       <c r="A2270" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2270" s="2">
-        <v>103293751</v>
+        <v>102884064</v>
       </c>
       <c r="C2270" s="1" t="s">
-        <v>288</v>
+        <v>107</v>
       </c>
       <c r="D2270" s="2">
         <v>21</v>
@@ -33243,55 +33246,55 @@
     </row>
     <row r="2271" spans="1:4">
       <c r="A2271" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2271" s="2">
-        <v>103293756</v>
+        <v>102884675</v>
       </c>
       <c r="C2271" s="1" t="s">
-        <v>289</v>
+        <v>111</v>
       </c>
       <c r="D2271" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2272" spans="1:4">
       <c r="A2272" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2272" s="2">
-        <v>103293766</v>
+        <v>102908267</v>
       </c>
       <c r="C2272" s="1" t="s">
-        <v>290</v>
+        <v>113</v>
       </c>
       <c r="D2272" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2273" spans="1:4">
       <c r="A2273" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2273" s="2">
-        <v>103293773</v>
+        <v>103001864</v>
       </c>
       <c r="C2273" s="1" t="s">
-        <v>291</v>
+        <v>114</v>
       </c>
       <c r="D2273" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2274" spans="1:4">
       <c r="A2274" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2274" s="2">
-        <v>103294755</v>
+        <v>103028093</v>
       </c>
       <c r="C2274" s="1" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="D2274" s="2">
         <v>20</v>
@@ -33299,195 +33302,195 @@
     </row>
     <row r="2275" spans="1:4">
       <c r="A2275" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2275" s="2">
-        <v>103294767</v>
+        <v>103060430</v>
       </c>
       <c r="C2275" s="1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D2275" s="2">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2276" spans="1:4">
       <c r="A2276" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2276" s="2">
-        <v>103296160</v>
+        <v>103060435</v>
       </c>
       <c r="C2276" s="1" t="s">
-        <v>292</v>
+        <v>123</v>
       </c>
       <c r="D2276" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2277" spans="1:4">
       <c r="A2277" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2277" s="2">
-        <v>103296167</v>
+        <v>103060453</v>
       </c>
       <c r="C2277" s="1" t="s">
-        <v>345</v>
+        <v>125</v>
       </c>
       <c r="D2277" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2278" spans="1:4">
       <c r="A2278" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2278" s="2">
-        <v>103297566</v>
+        <v>103060459</v>
       </c>
       <c r="C2278" s="1" t="s">
-        <v>293</v>
+        <v>126</v>
       </c>
       <c r="D2278" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2279" spans="1:4">
       <c r="A2279" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2279" s="2">
-        <v>103300418</v>
+        <v>103060462</v>
       </c>
       <c r="C2279" s="1" t="s">
-        <v>294</v>
+        <v>127</v>
       </c>
       <c r="D2279" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2280" spans="1:4">
       <c r="A2280" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2280" s="2">
-        <v>103304841</v>
+        <v>103060467</v>
       </c>
       <c r="C2280" s="1" t="s">
-        <v>290</v>
+        <v>128</v>
       </c>
       <c r="D2280" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2281" spans="1:4">
       <c r="A2281" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2281" s="2">
-        <v>103304846</v>
+        <v>103060471</v>
       </c>
       <c r="C2281" s="1" t="s">
-        <v>348</v>
+        <v>129</v>
       </c>
       <c r="D2281" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2282" spans="1:4">
       <c r="A2282" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2282" s="2">
-        <v>103304863</v>
+        <v>103082092</v>
       </c>
       <c r="C2282" s="1" t="s">
-        <v>349</v>
+        <v>132</v>
       </c>
       <c r="D2282" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2283" spans="1:4">
       <c r="A2283" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2283" s="2">
-        <v>103304866</v>
+        <v>103082095</v>
       </c>
       <c r="C2283" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D2283" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2284" spans="1:4">
       <c r="A2284" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2284" s="2">
-        <v>103304868</v>
+        <v>103082112</v>
       </c>
       <c r="C2284" s="1" t="s">
-        <v>350</v>
+        <v>135</v>
       </c>
       <c r="D2284" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2285" spans="1:4">
       <c r="A2285" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2285" s="2">
-        <v>103304875</v>
+        <v>103082113</v>
       </c>
       <c r="C2285" s="1" t="s">
-        <v>295</v>
+        <v>136</v>
       </c>
       <c r="D2285" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2286" spans="1:4">
       <c r="A2286" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2286" s="2">
-        <v>103305150</v>
+        <v>103082118</v>
       </c>
       <c r="C2286" s="1" t="s">
-        <v>296</v>
+        <v>137</v>
       </c>
       <c r="D2286" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2287" spans="1:4">
       <c r="A2287" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2287" s="2">
-        <v>103305154</v>
+        <v>103082119</v>
       </c>
       <c r="C2287" s="1" t="s">
-        <v>297</v>
+        <v>138</v>
       </c>
       <c r="D2287" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2288" spans="1:4">
       <c r="A2288" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2288" s="2">
-        <v>103305160</v>
+        <v>103082121</v>
       </c>
       <c r="C2288" s="1" t="s">
-        <v>298</v>
+        <v>139</v>
       </c>
       <c r="D2288" s="2">
         <v>20</v>
@@ -33495,15 +33498,1737 @@
     </row>
     <row r="2289" spans="1:4">
       <c r="A2289" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B2289" s="2">
+        <v>103082160</v>
+      </c>
+      <c r="C2289" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2289" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:4">
+      <c r="A2290" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2290" s="2">
+        <v>103082161</v>
+      </c>
+      <c r="C2290" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2290" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:4">
+      <c r="A2291" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2291" s="2">
+        <v>103082166</v>
+      </c>
+      <c r="C2291" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2291" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:4">
+      <c r="A2292" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2292" s="2">
+        <v>103082385</v>
+      </c>
+      <c r="C2292" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2292" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:4">
+      <c r="A2293" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2293" s="2">
+        <v>103085298</v>
+      </c>
+      <c r="C2293" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2293" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:4">
+      <c r="A2294" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2294" s="2">
+        <v>103088009</v>
+      </c>
+      <c r="C2294" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2294" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:4">
+      <c r="A2295" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2295" s="2">
+        <v>103092092</v>
+      </c>
+      <c r="C2295" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2295" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:4">
+      <c r="A2296" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2296" s="2">
+        <v>103092141</v>
+      </c>
+      <c r="C2296" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2296" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:4">
+      <c r="A2297" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2297" s="2">
+        <v>103092310</v>
+      </c>
+      <c r="C2297" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2297" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:4">
+      <c r="A2298" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2298" s="2">
+        <v>103092316</v>
+      </c>
+      <c r="C2298" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2298" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:4">
+      <c r="A2299" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2299" s="2">
+        <v>103101197</v>
+      </c>
+      <c r="C2299" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2299" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:4">
+      <c r="A2300" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2300" s="2">
+        <v>103101206</v>
+      </c>
+      <c r="C2300" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2300" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:4">
+      <c r="A2301" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2301" s="2">
+        <v>103101215</v>
+      </c>
+      <c r="C2301" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2301" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:4">
+      <c r="A2302" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2302" s="2">
+        <v>103101217</v>
+      </c>
+      <c r="C2302" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2302" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:4">
+      <c r="A2303" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2303" s="2">
+        <v>103103196</v>
+      </c>
+      <c r="C2303" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2303" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:4">
+      <c r="A2304" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2304" s="2">
+        <v>103103198</v>
+      </c>
+      <c r="C2304" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2304" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:4">
+      <c r="A2305" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2305" s="2">
+        <v>103103213</v>
+      </c>
+      <c r="C2305" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2305" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:4">
+      <c r="A2306" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2306" s="2">
+        <v>103105143</v>
+      </c>
+      <c r="C2306" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2306" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:4">
+      <c r="A2307" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2307" s="2">
+        <v>103109089</v>
+      </c>
+      <c r="C2307" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2307" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:4">
+      <c r="A2308" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2308" s="2">
+        <v>103109090</v>
+      </c>
+      <c r="C2308" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2308" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:4">
+      <c r="A2309" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2309" s="2">
+        <v>103109091</v>
+      </c>
+      <c r="C2309" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2309" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:4">
+      <c r="A2310" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2310" s="2">
+        <v>103109136</v>
+      </c>
+      <c r="C2310" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2310" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:4">
+      <c r="A2311" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2311" s="2">
+        <v>103109151</v>
+      </c>
+      <c r="C2311" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2311" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:4">
+      <c r="A2312" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2312" s="2">
+        <v>103109336</v>
+      </c>
+      <c r="C2312" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2312" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:4">
+      <c r="A2313" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2313" s="2">
+        <v>103109339</v>
+      </c>
+      <c r="C2313" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2313" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:4">
+      <c r="A2314" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2314" s="2">
+        <v>103109343</v>
+      </c>
+      <c r="C2314" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2314" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:4">
+      <c r="A2315" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2315" s="2">
+        <v>103109357</v>
+      </c>
+      <c r="C2315" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2315" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:4">
+      <c r="A2316" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2316" s="2">
+        <v>103110013</v>
+      </c>
+      <c r="C2316" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2316" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:4">
+      <c r="A2317" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2317" s="2">
+        <v>103110453</v>
+      </c>
+      <c r="C2317" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2317" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:4">
+      <c r="A2318" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2318" s="2">
+        <v>103111713</v>
+      </c>
+      <c r="C2318" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2318" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:4">
+      <c r="A2319" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2319" s="2">
+        <v>103111920</v>
+      </c>
+      <c r="C2319" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2319" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:4">
+      <c r="A2320" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2320" s="2">
+        <v>103111956</v>
+      </c>
+      <c r="C2320" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2320" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:4">
+      <c r="A2321" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2321" s="2">
+        <v>103113926</v>
+      </c>
+      <c r="C2321" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2321" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:4">
+      <c r="A2322" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2322" s="2">
+        <v>103115341</v>
+      </c>
+      <c r="C2322" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2322" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:4">
+      <c r="A2323" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2323" s="2">
+        <v>103116487</v>
+      </c>
+      <c r="C2323" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D2323" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:4">
+      <c r="A2324" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2324" s="2">
+        <v>103116496</v>
+      </c>
+      <c r="C2324" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2324" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:4">
+      <c r="A2325" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2325" s="2">
+        <v>103117188</v>
+      </c>
+      <c r="C2325" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2325" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:4">
+      <c r="A2326" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2326" s="2">
+        <v>103119654</v>
+      </c>
+      <c r="C2326" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2326" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:4">
+      <c r="A2327" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2327" s="2">
+        <v>103121097</v>
+      </c>
+      <c r="C2327" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2327" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:4">
+      <c r="A2328" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2328" s="2">
+        <v>103121098</v>
+      </c>
+      <c r="C2328" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2328" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:4">
+      <c r="A2329" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2329" s="2">
+        <v>103124232</v>
+      </c>
+      <c r="C2329" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2329" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:4">
+      <c r="A2330" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2330" s="2">
+        <v>103124248</v>
+      </c>
+      <c r="C2330" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2330" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:4">
+      <c r="A2331" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2331" s="2">
+        <v>103124249</v>
+      </c>
+      <c r="C2331" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D2331" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:4">
+      <c r="A2332" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2332" s="2">
+        <v>103124250</v>
+      </c>
+      <c r="C2332" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2332" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:4">
+      <c r="A2333" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2333" s="2">
+        <v>103124266</v>
+      </c>
+      <c r="C2333" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2333" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:4">
+      <c r="A2334" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2334" s="2">
+        <v>103124268</v>
+      </c>
+      <c r="C2334" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2334" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:4">
+      <c r="A2335" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2335" s="2">
+        <v>103125208</v>
+      </c>
+      <c r="C2335" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D2335" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:4">
+      <c r="A2336" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2336" s="2">
+        <v>103125228</v>
+      </c>
+      <c r="C2336" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D2336" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:4">
+      <c r="A2337" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2337" s="2">
+        <v>103125229</v>
+      </c>
+      <c r="C2337" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2337" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:4">
+      <c r="A2338" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2338" s="2">
+        <v>103126016</v>
+      </c>
+      <c r="C2338" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2338" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:4">
+      <c r="A2339" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2339" s="2">
+        <v>103127936</v>
+      </c>
+      <c r="C2339" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2339" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:4">
+      <c r="A2340" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2340" s="2">
+        <v>103129049</v>
+      </c>
+      <c r="C2340" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2340" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:4">
+      <c r="A2341" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2341" s="2">
+        <v>103129359</v>
+      </c>
+      <c r="C2341" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2341" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:4">
+      <c r="A2342" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2342" s="2">
+        <v>103129371</v>
+      </c>
+      <c r="C2342" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D2342" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:4">
+      <c r="A2343" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2343" s="2">
+        <v>103129415</v>
+      </c>
+      <c r="C2343" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D2343" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:4">
+      <c r="A2344" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2344" s="2">
+        <v>103129416</v>
+      </c>
+      <c r="C2344" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D2344" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:4">
+      <c r="A2345" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2345" s="2">
+        <v>103130518</v>
+      </c>
+      <c r="C2345" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2345" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:4">
+      <c r="A2346" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2346" s="2">
+        <v>103130519</v>
+      </c>
+      <c r="C2346" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2346" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:4">
+      <c r="A2347" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2347" s="2">
+        <v>103132423</v>
+      </c>
+      <c r="C2347" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2347" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:4">
+      <c r="A2348" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2348" s="2">
+        <v>103132424</v>
+      </c>
+      <c r="C2348" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2348" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:4">
+      <c r="A2349" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2349" s="2">
+        <v>103132932</v>
+      </c>
+      <c r="C2349" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D2349" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:4">
+      <c r="A2350" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2350" s="2">
+        <v>103132933</v>
+      </c>
+      <c r="C2350" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D2350" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:4">
+      <c r="A2351" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2351" s="2">
+        <v>103132934</v>
+      </c>
+      <c r="C2351" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2351" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:4">
+      <c r="A2352" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2352" s="2">
+        <v>103132938</v>
+      </c>
+      <c r="C2352" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D2352" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:4">
+      <c r="A2353" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2353" s="2">
+        <v>103133036</v>
+      </c>
+      <c r="C2353" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2353" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:4">
+      <c r="A2354" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2354" s="2">
+        <v>103133037</v>
+      </c>
+      <c r="C2354" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2354" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:4">
+      <c r="A2355" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2355" s="2">
+        <v>103133047</v>
+      </c>
+      <c r="C2355" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D2355" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:4">
+      <c r="A2356" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2356" s="2">
+        <v>103133765</v>
+      </c>
+      <c r="C2356" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D2356" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:4">
+      <c r="A2357" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2357" s="2">
+        <v>103133767</v>
+      </c>
+      <c r="C2357" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2357" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:4">
+      <c r="A2358" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2358" s="2">
+        <v>103136099</v>
+      </c>
+      <c r="C2358" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2358" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:4">
+      <c r="A2359" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2359" s="2">
+        <v>103136107</v>
+      </c>
+      <c r="C2359" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2359" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:4">
+      <c r="A2360" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2360" s="2">
+        <v>103136108</v>
+      </c>
+      <c r="C2360" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2360" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:4">
+      <c r="A2361" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2361" s="2">
+        <v>103137756</v>
+      </c>
+      <c r="C2361" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D2361" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:4">
+      <c r="A2362" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2362" s="2">
+        <v>103139871</v>
+      </c>
+      <c r="C2362" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2362" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:4">
+      <c r="A2363" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2363" s="2">
+        <v>103142315</v>
+      </c>
+      <c r="C2363" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D2363" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:4">
+      <c r="A2364" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2364" s="2">
+        <v>103142316</v>
+      </c>
+      <c r="C2364" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D2364" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:4">
+      <c r="A2365" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2365" s="2">
+        <v>103145144</v>
+      </c>
+      <c r="C2365" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2365" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:4">
+      <c r="A2366" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2366" s="2">
+        <v>103145154</v>
+      </c>
+      <c r="C2366" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2366" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:4">
+      <c r="A2367" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2367" s="2">
+        <v>103145155</v>
+      </c>
+      <c r="C2367" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2367" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:4">
+      <c r="A2368" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2368" s="2">
+        <v>103145248</v>
+      </c>
+      <c r="C2368" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2368" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:4">
+      <c r="A2369" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2369" s="2">
+        <v>103146147</v>
+      </c>
+      <c r="C2369" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D2369" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:4">
+      <c r="A2370" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2370" s="2">
+        <v>103169793</v>
+      </c>
+      <c r="C2370" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2370" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:4">
+      <c r="A2371" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2371" s="2">
+        <v>103169795</v>
+      </c>
+      <c r="C2371" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D2371" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:4">
+      <c r="A2372" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2372" s="2">
+        <v>103169797</v>
+      </c>
+      <c r="C2372" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2372" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:4">
+      <c r="A2373" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2373" s="2">
+        <v>103169814</v>
+      </c>
+      <c r="C2373" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D2373" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:4">
+      <c r="A2374" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2374" s="2">
+        <v>103169816</v>
+      </c>
+      <c r="C2374" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2374" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:4">
+      <c r="A2375" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2375" s="2">
+        <v>103169997</v>
+      </c>
+      <c r="C2375" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D2375" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:4">
+      <c r="A2376" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2376" s="2">
+        <v>103170002</v>
+      </c>
+      <c r="C2376" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2376" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:4">
+      <c r="A2377" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2377" s="2">
+        <v>103170019</v>
+      </c>
+      <c r="C2377" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2377" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:4">
+      <c r="A2378" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2378" s="2">
+        <v>103170021</v>
+      </c>
+      <c r="C2378" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2378" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:4">
+      <c r="A2379" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2379" s="2">
+        <v>103170024</v>
+      </c>
+      <c r="C2379" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D2379" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:4">
+      <c r="A2380" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2380" s="2">
+        <v>103170927</v>
+      </c>
+      <c r="C2380" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D2380" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:4">
+      <c r="A2381" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2381" s="2">
+        <v>103171002</v>
+      </c>
+      <c r="C2381" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D2381" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:4">
+      <c r="A2382" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2382" s="2">
+        <v>103171084</v>
+      </c>
+      <c r="C2382" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2382" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:4">
+      <c r="A2383" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2383" s="2">
+        <v>103171103</v>
+      </c>
+      <c r="C2383" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D2383" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:4">
+      <c r="A2384" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2384" s="2">
+        <v>103173195</v>
+      </c>
+      <c r="C2384" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D2384" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:4">
+      <c r="A2385" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2385" s="2">
+        <v>103173197</v>
+      </c>
+      <c r="C2385" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D2385" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:4">
+      <c r="A2386" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2386" s="2">
+        <v>103173208</v>
+      </c>
+      <c r="C2386" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2386" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:4">
+      <c r="A2387" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2387" s="2">
+        <v>103173212</v>
+      </c>
+      <c r="C2387" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D2387" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:4">
+      <c r="A2388" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2388" s="2">
+        <v>103173218</v>
+      </c>
+      <c r="C2388" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D2388" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:4">
+      <c r="A2389" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2389" s="2">
+        <v>103283831</v>
+      </c>
+      <c r="C2389" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D2389" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:4">
+      <c r="A2390" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2390" s="2">
+        <v>103293732</v>
+      </c>
+      <c r="C2390" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D2390" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:4">
+      <c r="A2391" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2391" s="2">
+        <v>103293737</v>
+      </c>
+      <c r="C2391" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2391" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:4">
+      <c r="A2392" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2392" s="2">
+        <v>103293745</v>
+      </c>
+      <c r="C2392" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D2392" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:4">
+      <c r="A2393" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2393" s="2">
+        <v>103293751</v>
+      </c>
+      <c r="C2393" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D2393" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:4">
+      <c r="A2394" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2394" s="2">
+        <v>103293756</v>
+      </c>
+      <c r="C2394" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D2394" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:4">
+      <c r="A2395" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2395" s="2">
+        <v>103293766</v>
+      </c>
+      <c r="C2395" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2395" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:4">
+      <c r="A2396" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2396" s="2">
+        <v>103293773</v>
+      </c>
+      <c r="C2396" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D2396" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:4">
+      <c r="A2397" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2397" s="2">
+        <v>103294755</v>
+      </c>
+      <c r="C2397" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2397" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:4">
+      <c r="A2398" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2398" s="2">
+        <v>103294767</v>
+      </c>
+      <c r="C2398" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2398" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:4">
+      <c r="A2399" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2399" s="2">
+        <v>103296160</v>
+      </c>
+      <c r="C2399" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2399" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:4">
+      <c r="A2400" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2400" s="2">
+        <v>103296167</v>
+      </c>
+      <c r="C2400" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D2400" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:4">
+      <c r="A2401" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2401" s="2">
+        <v>103297566</v>
+      </c>
+      <c r="C2401" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D2401" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:4">
+      <c r="A2402" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2402" s="2">
+        <v>103300418</v>
+      </c>
+      <c r="C2402" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2402" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:4">
+      <c r="A2403" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2403" s="2">
+        <v>103304841</v>
+      </c>
+      <c r="C2403" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2403" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:4">
+      <c r="A2404" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2404" s="2">
+        <v>103304846</v>
+      </c>
+      <c r="C2404" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D2404" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:4">
+      <c r="A2405" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2405" s="2">
+        <v>103304863</v>
+      </c>
+      <c r="C2405" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D2405" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:4">
+      <c r="A2406" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2406" s="2">
+        <v>103304866</v>
+      </c>
+      <c r="C2406" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2406" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:4">
+      <c r="A2407" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2407" s="2">
+        <v>103304868</v>
+      </c>
+      <c r="C2407" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D2407" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:4">
+      <c r="A2408" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2408" s="2">
+        <v>103304875</v>
+      </c>
+      <c r="C2408" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D2408" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:4">
+      <c r="A2409" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2409" s="2">
+        <v>103305150</v>
+      </c>
+      <c r="C2409" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D2409" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:4">
+      <c r="A2410" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2410" s="2">
+        <v>103305154</v>
+      </c>
+      <c r="C2410" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D2410" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:4">
+      <c r="A2411" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2411" s="2">
+        <v>103305160</v>
+      </c>
+      <c r="C2411" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D2411" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:4">
+      <c r="A2412" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2412" s="2">
         <v>103305165</v>
       </c>
-      <c r="C2289" s="1" t="s">
+      <c r="C2412" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D2289" s="2">
+      <c r="D2412" s="2">
         <v>20</v>
       </c>
     </row>
@@ -33764,13 +35489,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9866B1EF-3823-4132-A163-728D7CF78D88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31F3CD76-D724-49FF-B0DF-5B69D009EE15}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E61B77E1-6412-40E0-8E85-3919EFF8E9A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9676AEF2-239D-41F5-8139-D24CF9BD3778}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{826A87F8-0FAC-4D76-A5E7-E84D7B1F8BC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E76079F2-E942-4CDC-81B6-399BFA299D88}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4870" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4884" uniqueCount="381">
   <si>
     <t>Month</t>
   </si>
@@ -1127,6 +1127,27 @@
   </si>
   <si>
     <t>May-26</t>
+  </si>
+  <si>
+    <t>QUANG DO  NGUYEN</t>
+  </si>
+  <si>
+    <t>THU HANG  TRAN</t>
+  </si>
+  <si>
+    <t>QUANG HUNG  NGUYEN</t>
+  </si>
+  <si>
+    <t>THI TO UYEN  NGUYEN</t>
+  </si>
+  <si>
+    <t>NGOC HIEN  LY</t>
+  </si>
+  <si>
+    <t>THI ANH DUONG  NGUYEN</t>
+  </si>
+  <si>
+    <t>QUOC THUAN  DOAN</t>
   </si>
   <si>
     <t>Nov-25</t>
@@ -1197,8 +1218,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:D2434" totalsRowShown="0">
-  <autoFilter ref="A1:D2434"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:D2441" totalsRowShown="0">
+  <autoFilter ref="A1:D2441"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Month" dataDxfId="0"/>
     <tableColumn id="2" name="EID" dataDxfId="1"/>
@@ -1494,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2434"/>
+  <dimension ref="A1:D2441"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -27296,7 +27317,7 @@
         <v>29</v>
       </c>
       <c r="D1843" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1844" spans="1:4">
@@ -27380,7 +27401,7 @@
         <v>54</v>
       </c>
       <c r="D1849" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1850" spans="1:4">
@@ -27422,7 +27443,7 @@
         <v>72</v>
       </c>
       <c r="D1852" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1853" spans="1:4">
@@ -27450,7 +27471,7 @@
         <v>85</v>
       </c>
       <c r="D1854" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1855" spans="1:4">
@@ -27506,7 +27527,7 @@
         <v>102</v>
       </c>
       <c r="D1858" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1859" spans="1:4">
@@ -27548,7 +27569,7 @@
         <v>107</v>
       </c>
       <c r="D1861" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1862" spans="1:4">
@@ -27604,7 +27625,7 @@
         <v>123</v>
       </c>
       <c r="D1865" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1866" spans="1:4">
@@ -27632,7 +27653,7 @@
         <v>126</v>
       </c>
       <c r="D1867" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1868" spans="1:4">
@@ -27660,7 +27681,7 @@
         <v>129</v>
       </c>
       <c r="D1869" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1870" spans="1:4">
@@ -27674,7 +27695,7 @@
         <v>135</v>
       </c>
       <c r="D1870" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1871" spans="1:4">
@@ -27730,7 +27751,7 @@
         <v>148</v>
       </c>
       <c r="D1874" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1875" spans="1:4">
@@ -27744,7 +27765,7 @@
         <v>151</v>
       </c>
       <c r="D1875" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1876" spans="1:4">
@@ -27786,7 +27807,7 @@
         <v>160</v>
       </c>
       <c r="D1878" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1879" spans="1:4">
@@ -27814,7 +27835,7 @@
         <v>166</v>
       </c>
       <c r="D1880" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1881" spans="1:4">
@@ -27842,7 +27863,7 @@
         <v>171</v>
       </c>
       <c r="D1882" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1883" spans="1:4">
@@ -27870,7 +27891,7 @@
         <v>173</v>
       </c>
       <c r="D1884" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1885" spans="1:4">
@@ -27926,7 +27947,7 @@
         <v>182</v>
       </c>
       <c r="D1888" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1889" spans="1:4">
@@ -28248,7 +28269,7 @@
         <v>287</v>
       </c>
       <c r="D1911" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1912" spans="1:4">
@@ -28304,7 +28325,7 @@
         <v>291</v>
       </c>
       <c r="D1915" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1916" spans="1:4">
@@ -28318,7 +28339,7 @@
         <v>150</v>
       </c>
       <c r="D1916" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1917" spans="1:4">
@@ -28416,7 +28437,7 @@
         <v>300</v>
       </c>
       <c r="D1923" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1924" spans="1:4">
@@ -28458,7 +28479,7 @@
         <v>303</v>
       </c>
       <c r="D1926" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1927" spans="1:4">
@@ -28584,7 +28605,7 @@
         <v>313</v>
       </c>
       <c r="D1935" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1936" spans="1:4">
@@ -28598,7 +28619,7 @@
         <v>314</v>
       </c>
       <c r="D1936" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1937" spans="1:4">
@@ -28626,7 +28647,7 @@
         <v>316</v>
       </c>
       <c r="D1938" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1939" spans="1:4">
@@ -28640,7 +28661,7 @@
         <v>317</v>
       </c>
       <c r="D1939" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1940" spans="1:4">
@@ -29079,181 +29100,181 @@
     </row>
     <row r="1971" spans="1:4">
       <c r="A1971" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1971" s="2">
+        <v>103578428</v>
+      </c>
+      <c r="C1971" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B1971" s="2">
-        <v>102029874</v>
-      </c>
-      <c r="C1971" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="D1971" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1972" spans="1:4">
       <c r="A1972" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B1972" s="2">
-        <v>102173363</v>
+        <v>103578433</v>
       </c>
       <c r="C1972" s="1" t="s">
-        <v>7</v>
+        <v>372</v>
       </c>
       <c r="D1972" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1973" spans="1:4">
       <c r="A1973" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B1973" s="2">
-        <v>102211179</v>
+        <v>103578435</v>
       </c>
       <c r="C1973" s="1" t="s">
-        <v>10</v>
+        <v>373</v>
       </c>
       <c r="D1973" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1974" spans="1:4">
       <c r="A1974" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B1974" s="2">
-        <v>102219144</v>
+        <v>103578438</v>
       </c>
       <c r="C1974" s="1" t="s">
-        <v>12</v>
+        <v>374</v>
       </c>
       <c r="D1974" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1975" spans="1:4">
       <c r="A1975" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B1975" s="2">
-        <v>102326882</v>
+        <v>103578443</v>
       </c>
       <c r="C1975" s="1" t="s">
-        <v>16</v>
+        <v>375</v>
       </c>
       <c r="D1975" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1976" spans="1:4">
       <c r="A1976" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B1976" s="2">
-        <v>102343359</v>
+        <v>103578446</v>
       </c>
       <c r="C1976" s="1" t="s">
-        <v>17</v>
+        <v>376</v>
       </c>
       <c r="D1976" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1977" spans="1:4">
       <c r="A1977" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B1977" s="2">
-        <v>102369579</v>
+        <v>103579593</v>
       </c>
       <c r="C1977" s="1" t="s">
-        <v>19</v>
+        <v>377</v>
       </c>
       <c r="D1977" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1978" spans="1:4">
       <c r="A1978" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1978" s="2">
-        <v>102370804</v>
+        <v>102029874</v>
       </c>
       <c r="C1978" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1978" s="2">
         <v>22</v>
-      </c>
-      <c r="D1978" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="1979" spans="1:4">
       <c r="A1979" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1979" s="2">
-        <v>102371964</v>
+        <v>102173363</v>
       </c>
       <c r="C1979" s="1" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D1979" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1980" spans="1:4">
       <c r="A1980" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1980" s="2">
-        <v>102456914</v>
+        <v>102211179</v>
       </c>
       <c r="C1980" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D1980" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1981" spans="1:4">
       <c r="A1981" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1981" s="2">
-        <v>102456984</v>
+        <v>102219144</v>
       </c>
       <c r="C1981" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D1981" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1982" spans="1:4">
       <c r="A1982" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1982" s="2">
-        <v>102456993</v>
+        <v>102326882</v>
       </c>
       <c r="C1982" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D1982" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1983" spans="1:4">
       <c r="A1983" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1983" s="2">
-        <v>102457937</v>
+        <v>102343359</v>
       </c>
       <c r="C1983" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D1983" s="2">
         <v>19</v>
@@ -29261,69 +29282,69 @@
     </row>
     <row r="1984" spans="1:4">
       <c r="A1984" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1984" s="2">
-        <v>102458550</v>
+        <v>102369579</v>
       </c>
       <c r="C1984" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D1984" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1985" spans="1:4">
       <c r="A1985" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1985" s="2">
-        <v>102464498</v>
+        <v>102370804</v>
       </c>
       <c r="C1985" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D1985" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1986" spans="1:4">
       <c r="A1986" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1986" s="2">
-        <v>102477288</v>
+        <v>102371964</v>
       </c>
       <c r="C1986" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D1986" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1987" spans="1:4">
       <c r="A1987" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1987" s="2">
-        <v>102477293</v>
+        <v>102456914</v>
       </c>
       <c r="C1987" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D1987" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1988" spans="1:4">
       <c r="A1988" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1988" s="2">
-        <v>102477371</v>
+        <v>102456984</v>
       </c>
       <c r="C1988" s="1" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D1988" s="2">
         <v>20</v>
@@ -29331,13 +29352,13 @@
     </row>
     <row r="1989" spans="1:4">
       <c r="A1989" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1989" s="2">
-        <v>102477422</v>
+        <v>102456993</v>
       </c>
       <c r="C1989" s="1" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D1989" s="2">
         <v>20</v>
@@ -29345,13 +29366,13 @@
     </row>
     <row r="1990" spans="1:4">
       <c r="A1990" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1990" s="2">
-        <v>102477510</v>
+        <v>102457937</v>
       </c>
       <c r="C1990" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D1990" s="2">
         <v>19</v>
@@ -29359,55 +29380,55 @@
     </row>
     <row r="1991" spans="1:4">
       <c r="A1991" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1991" s="2">
-        <v>102478278</v>
+        <v>102458550</v>
       </c>
       <c r="C1991" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D1991" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1992" spans="1:4">
       <c r="A1992" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1992" s="2">
-        <v>102482237</v>
+        <v>102464498</v>
       </c>
       <c r="C1992" s="1" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D1992" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1993" spans="1:4">
       <c r="A1993" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1993" s="2">
-        <v>102484482</v>
+        <v>102477288</v>
       </c>
       <c r="C1993" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D1993" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1994" spans="1:4">
       <c r="A1994" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1994" s="2">
-        <v>102502720</v>
+        <v>102477293</v>
       </c>
       <c r="C1994" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D1994" s="2">
         <v>21</v>
@@ -29415,27 +29436,27 @@
     </row>
     <row r="1995" spans="1:4">
       <c r="A1995" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1995" s="2">
-        <v>102502737</v>
+        <v>102477371</v>
       </c>
       <c r="C1995" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D1995" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1996" spans="1:4">
       <c r="A1996" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1996" s="2">
-        <v>102502871</v>
+        <v>102477422</v>
       </c>
       <c r="C1996" s="1" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D1996" s="2">
         <v>20</v>
@@ -29443,41 +29464,41 @@
     </row>
     <row r="1997" spans="1:4">
       <c r="A1997" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1997" s="2">
-        <v>102503478</v>
+        <v>102477510</v>
       </c>
       <c r="C1997" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D1997" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1998" spans="1:4">
       <c r="A1998" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1998" s="2">
-        <v>102507584</v>
+        <v>102478278</v>
       </c>
       <c r="C1998" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D1998" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1999" spans="1:4">
       <c r="A1999" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B1999" s="2">
-        <v>102509109</v>
+        <v>102482237</v>
       </c>
       <c r="C1999" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D1999" s="2">
         <v>19</v>
@@ -29485,83 +29506,83 @@
     </row>
     <row r="2000" spans="1:4">
       <c r="A2000" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2000" s="2">
-        <v>102511945</v>
+        <v>102484482</v>
       </c>
       <c r="C2000" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D2000" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2001" spans="1:4">
       <c r="A2001" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2001" s="2">
-        <v>102517333</v>
+        <v>102502720</v>
       </c>
       <c r="C2001" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D2001" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2002" spans="1:4">
       <c r="A2002" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2002" s="2">
-        <v>102517346</v>
+        <v>102502737</v>
       </c>
       <c r="C2002" s="1" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D2002" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2003" spans="1:4">
       <c r="A2003" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2003" s="2">
-        <v>102821757</v>
+        <v>102502871</v>
       </c>
       <c r="C2003" s="1" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D2003" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2004" spans="1:4">
       <c r="A2004" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2004" s="2">
-        <v>102830253</v>
+        <v>102503478</v>
       </c>
       <c r="C2004" s="1" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D2004" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2005" spans="1:4">
       <c r="A2005" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2005" s="2">
-        <v>102830316</v>
+        <v>102507584</v>
       </c>
       <c r="C2005" s="1" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="D2005" s="2">
         <v>21</v>
@@ -29569,27 +29590,27 @@
     </row>
     <row r="2006" spans="1:4">
       <c r="A2006" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2006" s="2">
-        <v>102831065</v>
+        <v>102509109</v>
       </c>
       <c r="C2006" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D2006" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2007" spans="1:4">
       <c r="A2007" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2007" s="2">
-        <v>102843519</v>
+        <v>102511945</v>
       </c>
       <c r="C2007" s="1" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D2007" s="2">
         <v>18</v>
@@ -29597,69 +29618,69 @@
     </row>
     <row r="2008" spans="1:4">
       <c r="A2008" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2008" s="2">
-        <v>102855952</v>
+        <v>102517333</v>
       </c>
       <c r="C2008" s="1" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="D2008" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2009" spans="1:4">
       <c r="A2009" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2009" s="2">
-        <v>102864715</v>
+        <v>102517346</v>
       </c>
       <c r="C2009" s="1" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="D2009" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2010" spans="1:4">
       <c r="A2010" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2010" s="2">
-        <v>102871040</v>
+        <v>102821757</v>
       </c>
       <c r="C2010" s="1" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="D2010" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2011" spans="1:4">
       <c r="A2011" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2011" s="2">
-        <v>102879799</v>
+        <v>102830253</v>
       </c>
       <c r="C2011" s="1" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="D2011" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2012" spans="1:4">
       <c r="A2012" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2012" s="2">
-        <v>102884064</v>
+        <v>102830316</v>
       </c>
       <c r="C2012" s="1" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D2012" s="2">
         <v>21</v>
@@ -29667,13 +29688,13 @@
     </row>
     <row r="2013" spans="1:4">
       <c r="A2013" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2013" s="2">
-        <v>102884675</v>
+        <v>102831065</v>
       </c>
       <c r="C2013" s="1" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D2013" s="2">
         <v>20</v>
@@ -29681,167 +29702,167 @@
     </row>
     <row r="2014" spans="1:4">
       <c r="A2014" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2014" s="2">
-        <v>102908267</v>
+        <v>102843519</v>
       </c>
       <c r="C2014" s="1" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D2014" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2015" spans="1:4">
       <c r="A2015" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2015" s="2">
-        <v>103028093</v>
+        <v>102855952</v>
       </c>
       <c r="C2015" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D2015" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2016" spans="1:4">
       <c r="A2016" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2016" s="2">
-        <v>103060430</v>
+        <v>102864715</v>
       </c>
       <c r="C2016" s="1" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D2016" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2017" spans="1:4">
       <c r="A2017" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2017" s="2">
-        <v>103060435</v>
+        <v>102871040</v>
       </c>
       <c r="C2017" s="1" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D2017" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2018" spans="1:4">
       <c r="A2018" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2018" s="2">
-        <v>103060453</v>
+        <v>102879799</v>
       </c>
       <c r="C2018" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D2018" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2019" spans="1:4">
       <c r="A2019" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2019" s="2">
-        <v>103060459</v>
+        <v>102884064</v>
       </c>
       <c r="C2019" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D2019" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2020" spans="1:4">
       <c r="A2020" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2020" s="2">
-        <v>103060462</v>
+        <v>102884675</v>
       </c>
       <c r="C2020" s="1" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="D2020" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2021" spans="1:4">
       <c r="A2021" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2021" s="2">
-        <v>103060467</v>
+        <v>102908267</v>
       </c>
       <c r="C2021" s="1" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D2021" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2022" spans="1:4">
       <c r="A2022" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2022" s="2">
-        <v>103060471</v>
+        <v>103028093</v>
       </c>
       <c r="C2022" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D2022" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2023" spans="1:4">
       <c r="A2023" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2023" s="2">
-        <v>103082092</v>
+        <v>103060430</v>
       </c>
       <c r="C2023" s="1" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D2023" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2024" spans="1:4">
       <c r="A2024" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2024" s="2">
-        <v>103082095</v>
+        <v>103060435</v>
       </c>
       <c r="C2024" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D2024" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2025" spans="1:4">
       <c r="A2025" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2025" s="2">
-        <v>103082112</v>
+        <v>103060453</v>
       </c>
       <c r="C2025" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D2025" s="2">
         <v>20</v>
@@ -29849,27 +29870,27 @@
     </row>
     <row r="2026" spans="1:4">
       <c r="A2026" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2026" s="2">
-        <v>103082113</v>
+        <v>103060459</v>
       </c>
       <c r="C2026" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D2026" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2027" spans="1:4">
       <c r="A2027" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2027" s="2">
-        <v>103082118</v>
+        <v>103060462</v>
       </c>
       <c r="C2027" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D2027" s="2">
         <v>18</v>
@@ -29877,83 +29898,83 @@
     </row>
     <row r="2028" spans="1:4">
       <c r="A2028" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2028" s="2">
-        <v>103082121</v>
+        <v>103060467</v>
       </c>
       <c r="C2028" s="1" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D2028" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2029" spans="1:4">
       <c r="A2029" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2029" s="2">
-        <v>103082161</v>
+        <v>103060471</v>
       </c>
       <c r="C2029" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D2029" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2030" spans="1:4">
       <c r="A2030" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2030" s="2">
-        <v>103082166</v>
+        <v>103082092</v>
       </c>
       <c r="C2030" s="1" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D2030" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2031" spans="1:4">
       <c r="A2031" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2031" s="2">
-        <v>103082385</v>
+        <v>103082095</v>
       </c>
       <c r="C2031" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D2031" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2032" spans="1:4">
       <c r="A2032" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2032" s="2">
-        <v>103085298</v>
+        <v>103082112</v>
       </c>
       <c r="C2032" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D2032" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2033" spans="1:4">
       <c r="A2033" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2033" s="2">
-        <v>103088009</v>
+        <v>103082113</v>
       </c>
       <c r="C2033" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D2033" s="2">
         <v>20</v>
@@ -29961,27 +29982,27 @@
     </row>
     <row r="2034" spans="1:4">
       <c r="A2034" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2034" s="2">
-        <v>103092092</v>
+        <v>103082118</v>
       </c>
       <c r="C2034" s="1" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D2034" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2035" spans="1:4">
       <c r="A2035" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2035" s="2">
-        <v>103092310</v>
+        <v>103082121</v>
       </c>
       <c r="C2035" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D2035" s="2">
         <v>17</v>
@@ -29989,83 +30010,83 @@
     </row>
     <row r="2036" spans="1:4">
       <c r="A2036" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2036" s="2">
-        <v>103092316</v>
+        <v>103082161</v>
       </c>
       <c r="C2036" s="1" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D2036" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2037" spans="1:4">
       <c r="A2037" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2037" s="2">
-        <v>103101206</v>
+        <v>103082166</v>
       </c>
       <c r="C2037" s="1" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D2037" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2038" spans="1:4">
       <c r="A2038" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2038" s="2">
-        <v>103103196</v>
+        <v>103082385</v>
       </c>
       <c r="C2038" s="1" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D2038" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2039" spans="1:4">
       <c r="A2039" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2039" s="2">
-        <v>103103198</v>
+        <v>103085298</v>
       </c>
       <c r="C2039" s="1" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="D2039" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2040" spans="1:4">
       <c r="A2040" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2040" s="2">
-        <v>103103213</v>
+        <v>103088009</v>
       </c>
       <c r="C2040" s="1" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D2040" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2041" spans="1:4">
       <c r="A2041" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2041" s="2">
-        <v>103105143</v>
+        <v>103092092</v>
       </c>
       <c r="C2041" s="1" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D2041" s="2">
         <v>20</v>
@@ -30073,41 +30094,41 @@
     </row>
     <row r="2042" spans="1:4">
       <c r="A2042" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2042" s="2">
-        <v>103109089</v>
+        <v>103092310</v>
       </c>
       <c r="C2042" s="1" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="D2042" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2043" spans="1:4">
       <c r="A2043" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2043" s="2">
-        <v>103109090</v>
+        <v>103092316</v>
       </c>
       <c r="C2043" s="1" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D2043" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2044" spans="1:4">
       <c r="A2044" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2044" s="2">
-        <v>103109091</v>
+        <v>103101206</v>
       </c>
       <c r="C2044" s="1" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="D2044" s="2">
         <v>18</v>
@@ -30115,27 +30136,27 @@
     </row>
     <row r="2045" spans="1:4">
       <c r="A2045" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2045" s="2">
-        <v>103109136</v>
+        <v>103103196</v>
       </c>
       <c r="C2045" s="1" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D2045" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2046" spans="1:4">
       <c r="A2046" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2046" s="2">
-        <v>103109151</v>
+        <v>103103198</v>
       </c>
       <c r="C2046" s="1" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D2046" s="2">
         <v>20</v>
@@ -30143,27 +30164,27 @@
     </row>
     <row r="2047" spans="1:4">
       <c r="A2047" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2047" s="2">
-        <v>103109336</v>
+        <v>103103213</v>
       </c>
       <c r="C2047" s="1" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D2047" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2048" spans="1:4">
       <c r="A2048" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2048" s="2">
-        <v>103109339</v>
+        <v>103105143</v>
       </c>
       <c r="C2048" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D2048" s="2">
         <v>20</v>
@@ -30171,153 +30192,153 @@
     </row>
     <row r="2049" spans="1:4">
       <c r="A2049" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2049" s="2">
-        <v>103109343</v>
+        <v>103109089</v>
       </c>
       <c r="C2049" s="1" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D2049" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2050" spans="1:4">
       <c r="A2050" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2050" s="2">
-        <v>103109357</v>
+        <v>103109090</v>
       </c>
       <c r="C2050" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D2050" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2051" spans="1:4">
       <c r="A2051" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2051" s="2">
-        <v>103110013</v>
+        <v>103109091</v>
       </c>
       <c r="C2051" s="1" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="D2051" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2052" spans="1:4">
       <c r="A2052" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2052" s="2">
-        <v>103111713</v>
+        <v>103109136</v>
       </c>
       <c r="C2052" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D2052" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2053" spans="1:4">
       <c r="A2053" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2053" s="2">
-        <v>103111956</v>
+        <v>103109151</v>
       </c>
       <c r="C2053" s="1" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D2053" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2054" spans="1:4">
       <c r="A2054" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2054" s="2">
-        <v>103113926</v>
+        <v>103109336</v>
       </c>
       <c r="C2054" s="1" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="D2054" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2055" spans="1:4">
       <c r="A2055" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2055" s="2">
-        <v>103115341</v>
+        <v>103109339</v>
       </c>
       <c r="C2055" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D2055" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2056" spans="1:4">
       <c r="A2056" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2056" s="2">
-        <v>103116487</v>
+        <v>103109343</v>
       </c>
       <c r="C2056" s="1" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="D2056" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2057" spans="1:4">
       <c r="A2057" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2057" s="2">
-        <v>103116496</v>
+        <v>103109357</v>
       </c>
       <c r="C2057" s="1" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D2057" s="2">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2058" spans="1:4">
       <c r="A2058" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2058" s="2">
-        <v>103117188</v>
+        <v>103110013</v>
       </c>
       <c r="C2058" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D2058" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2059" spans="1:4">
       <c r="A2059" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2059" s="2">
-        <v>103121097</v>
+        <v>103111713</v>
       </c>
       <c r="C2059" s="1" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D2059" s="2">
         <v>18</v>
@@ -30325,55 +30346,55 @@
     </row>
     <row r="2060" spans="1:4">
       <c r="A2060" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2060" s="2">
-        <v>103121098</v>
+        <v>103111956</v>
       </c>
       <c r="C2060" s="1" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D2060" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2061" spans="1:4">
       <c r="A2061" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2061" s="2">
-        <v>103125208</v>
+        <v>103113926</v>
       </c>
       <c r="C2061" s="1" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="D2061" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2062" spans="1:4">
       <c r="A2062" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2062" s="2">
-        <v>103125228</v>
+        <v>103115341</v>
       </c>
       <c r="C2062" s="1" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="D2062" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2063" spans="1:4">
       <c r="A2063" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2063" s="2">
-        <v>103125229</v>
+        <v>103116487</v>
       </c>
       <c r="C2063" s="1" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="D2063" s="2">
         <v>20</v>
@@ -30381,55 +30402,55 @@
     </row>
     <row r="2064" spans="1:4">
       <c r="A2064" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2064" s="2">
-        <v>103127936</v>
+        <v>103116496</v>
       </c>
       <c r="C2064" s="1" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="D2064" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2065" spans="1:4">
       <c r="A2065" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2065" s="2">
-        <v>103130519</v>
+        <v>103117188</v>
       </c>
       <c r="C2065" s="1" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="D2065" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2066" spans="1:4">
       <c r="A2066" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2066" s="2">
-        <v>103132423</v>
+        <v>103121097</v>
       </c>
       <c r="C2066" s="1" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="D2066" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2067" spans="1:4">
       <c r="A2067" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2067" s="2">
-        <v>103132424</v>
+        <v>103121098</v>
       </c>
       <c r="C2067" s="1" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="D2067" s="2">
         <v>20</v>
@@ -30437,13 +30458,13 @@
     </row>
     <row r="2068" spans="1:4">
       <c r="A2068" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2068" s="2">
-        <v>103133036</v>
+        <v>103125208</v>
       </c>
       <c r="C2068" s="1" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="D2068" s="2">
         <v>20</v>
@@ -30451,27 +30472,27 @@
     </row>
     <row r="2069" spans="1:4">
       <c r="A2069" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2069" s="2">
-        <v>103136107</v>
+        <v>103125228</v>
       </c>
       <c r="C2069" s="1" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="D2069" s="2">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2070" spans="1:4">
       <c r="A2070" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2070" s="2">
-        <v>103139871</v>
+        <v>103125229</v>
       </c>
       <c r="C2070" s="1" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="D2070" s="2">
         <v>20</v>
@@ -30479,125 +30500,125 @@
     </row>
     <row r="2071" spans="1:4">
       <c r="A2071" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2071" s="2">
-        <v>103145144</v>
+        <v>103127936</v>
       </c>
       <c r="C2071" s="1" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="D2071" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2072" spans="1:4">
       <c r="A2072" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2072" s="2">
-        <v>103169793</v>
+        <v>103130519</v>
       </c>
       <c r="C2072" s="1" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="D2072" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2073" spans="1:4">
       <c r="A2073" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2073" s="2">
-        <v>103169795</v>
+        <v>103132423</v>
       </c>
       <c r="C2073" s="1" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="D2073" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2074" spans="1:4">
       <c r="A2074" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2074" s="2">
-        <v>103169797</v>
+        <v>103132424</v>
       </c>
       <c r="C2074" s="1" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="D2074" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2075" spans="1:4">
       <c r="A2075" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2075" s="2">
-        <v>103169814</v>
+        <v>103133036</v>
       </c>
       <c r="C2075" s="1" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="D2075" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2076" spans="1:4">
       <c r="A2076" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2076" s="2">
-        <v>103169816</v>
+        <v>103136107</v>
       </c>
       <c r="C2076" s="1" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D2076" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2077" spans="1:4">
       <c r="A2077" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2077" s="2">
-        <v>103171103</v>
+        <v>103139871</v>
       </c>
       <c r="C2077" s="1" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="D2077" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2078" spans="1:4">
       <c r="A2078" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2078" s="2">
-        <v>103173195</v>
+        <v>103145144</v>
       </c>
       <c r="C2078" s="1" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="D2078" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2079" spans="1:4">
       <c r="A2079" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2079" s="2">
-        <v>103173197</v>
+        <v>103169793</v>
       </c>
       <c r="C2079" s="1" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="D2079" s="2">
         <v>20</v>
@@ -30605,83 +30626,83 @@
     </row>
     <row r="2080" spans="1:4">
       <c r="A2080" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2080" s="2">
-        <v>103283831</v>
+        <v>103169795</v>
       </c>
       <c r="C2080" s="1" t="s">
-        <v>352</v>
+        <v>259</v>
       </c>
       <c r="D2080" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2081" spans="1:4">
       <c r="A2081" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2081" s="2">
-        <v>103293732</v>
+        <v>103169797</v>
       </c>
       <c r="C2081" s="1" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="D2081" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2082" spans="1:4">
       <c r="A2082" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2082" s="2">
-        <v>103293737</v>
+        <v>103169814</v>
       </c>
       <c r="C2082" s="1" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="D2082" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2083" spans="1:4">
       <c r="A2083" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2083" s="2">
-        <v>103293745</v>
+        <v>103169816</v>
       </c>
       <c r="C2083" s="1" t="s">
-        <v>353</v>
+        <v>263</v>
       </c>
       <c r="D2083" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2084" spans="1:4">
       <c r="A2084" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2084" s="2">
-        <v>103293751</v>
+        <v>103171103</v>
       </c>
       <c r="C2084" s="1" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="D2084" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2085" spans="1:4">
       <c r="A2085" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2085" s="2">
-        <v>103293756</v>
+        <v>103173195</v>
       </c>
       <c r="C2085" s="1" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="D2085" s="2">
         <v>20</v>
@@ -30689,13 +30710,13 @@
     </row>
     <row r="2086" spans="1:4">
       <c r="A2086" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2086" s="2">
-        <v>103293766</v>
+        <v>103173197</v>
       </c>
       <c r="C2086" s="1" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="D2086" s="2">
         <v>20</v>
@@ -30703,265 +30724,265 @@
     </row>
     <row r="2087" spans="1:4">
       <c r="A2087" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2087" s="2">
-        <v>103293773</v>
+        <v>103283831</v>
       </c>
       <c r="C2087" s="1" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="D2087" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2088" spans="1:4">
       <c r="A2088" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2088" s="2">
-        <v>103294755</v>
+        <v>103293732</v>
       </c>
       <c r="C2088" s="1" t="s">
-        <v>150</v>
+        <v>286</v>
       </c>
       <c r="D2088" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2089" spans="1:4">
       <c r="A2089" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2089" s="2">
-        <v>103296160</v>
+        <v>103293737</v>
       </c>
       <c r="C2089" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D2089" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2090" spans="1:4">
       <c r="A2090" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2090" s="2">
-        <v>103296167</v>
+        <v>103293745</v>
       </c>
       <c r="C2090" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D2090" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2091" spans="1:4">
       <c r="A2091" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2091" s="2">
-        <v>103297566</v>
+        <v>103293751</v>
       </c>
       <c r="C2091" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D2091" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2092" spans="1:4">
       <c r="A2092" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2092" s="2">
-        <v>103300418</v>
+        <v>103293756</v>
       </c>
       <c r="C2092" s="1" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D2092" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2093" spans="1:4">
       <c r="A2093" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2093" s="2">
-        <v>103304841</v>
+        <v>103293766</v>
       </c>
       <c r="C2093" s="1" t="s">
         <v>290</v>
       </c>
       <c r="D2093" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2094" spans="1:4">
       <c r="A2094" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2094" s="2">
-        <v>103304846</v>
+        <v>103293773</v>
       </c>
       <c r="C2094" s="1" t="s">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="D2094" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2095" spans="1:4">
       <c r="A2095" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2095" s="2">
-        <v>103304863</v>
+        <v>103294755</v>
       </c>
       <c r="C2095" s="1" t="s">
-        <v>360</v>
+        <v>150</v>
       </c>
       <c r="D2095" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2096" spans="1:4">
       <c r="A2096" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2096" s="2">
-        <v>103304866</v>
+        <v>103296160</v>
       </c>
       <c r="C2096" s="1" t="s">
-        <v>130</v>
+        <v>292</v>
       </c>
       <c r="D2096" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2097" spans="1:4">
       <c r="A2097" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2097" s="2">
-        <v>103304875</v>
+        <v>103296167</v>
       </c>
       <c r="C2097" s="1" t="s">
-        <v>295</v>
+        <v>356</v>
       </c>
       <c r="D2097" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2098" spans="1:4">
       <c r="A2098" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2098" s="2">
-        <v>103305150</v>
+        <v>103297566</v>
       </c>
       <c r="C2098" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D2098" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2099" spans="1:4">
       <c r="A2099" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2099" s="2">
-        <v>103305154</v>
+        <v>103300418</v>
       </c>
       <c r="C2099" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D2099" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2100" spans="1:4">
       <c r="A2100" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2100" s="2">
-        <v>103305160</v>
+        <v>103304841</v>
       </c>
       <c r="C2100" s="1" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D2100" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2101" spans="1:4">
       <c r="A2101" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B2101" s="2">
-        <v>103305165</v>
+        <v>103304846</v>
       </c>
       <c r="C2101" s="1" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="D2101" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2102" spans="1:4">
       <c r="A2102" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B2102" s="2">
-        <v>102029874</v>
+        <v>103304863</v>
       </c>
       <c r="C2102" s="1" t="s">
-        <v>6</v>
+        <v>360</v>
       </c>
       <c r="D2102" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2103" spans="1:4">
       <c r="A2103" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B2103" s="2">
-        <v>102173363</v>
+        <v>103304866</v>
       </c>
       <c r="C2103" s="1" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="D2103" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2104" spans="1:4">
       <c r="A2104" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B2104" s="2">
-        <v>102211179</v>
+        <v>103304875</v>
       </c>
       <c r="C2104" s="1" t="s">
-        <v>10</v>
+        <v>295</v>
       </c>
       <c r="D2104" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2105" spans="1:4">
       <c r="A2105" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B2105" s="2">
-        <v>102219144</v>
+        <v>103305150</v>
       </c>
       <c r="C2105" s="1" t="s">
-        <v>12</v>
+        <v>296</v>
       </c>
       <c r="D2105" s="2">
         <v>21</v>
@@ -30969,55 +30990,55 @@
     </row>
     <row r="2106" spans="1:4">
       <c r="A2106" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B2106" s="2">
-        <v>102326882</v>
+        <v>103305154</v>
       </c>
       <c r="C2106" s="1" t="s">
-        <v>16</v>
+        <v>297</v>
       </c>
       <c r="D2106" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2107" spans="1:4">
       <c r="A2107" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B2107" s="2">
-        <v>102343359</v>
+        <v>103305160</v>
       </c>
       <c r="C2107" s="1" t="s">
-        <v>17</v>
+        <v>298</v>
       </c>
       <c r="D2107" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2108" spans="1:4">
       <c r="A2108" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B2108" s="2">
-        <v>102369579</v>
+        <v>103305165</v>
       </c>
       <c r="C2108" s="1" t="s">
-        <v>19</v>
+        <v>299</v>
       </c>
       <c r="D2108" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2109" spans="1:4">
       <c r="A2109" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2109" s="2">
-        <v>102370804</v>
+        <v>102029874</v>
       </c>
       <c r="C2109" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D2109" s="2">
         <v>21</v>
@@ -31025,13 +31046,13 @@
     </row>
     <row r="2110" spans="1:4">
       <c r="A2110" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2110" s="2">
-        <v>102371964</v>
+        <v>102173363</v>
       </c>
       <c r="C2110" s="1" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D2110" s="2">
         <v>22</v>
@@ -31039,111 +31060,111 @@
     </row>
     <row r="2111" spans="1:4">
       <c r="A2111" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2111" s="2">
-        <v>102456914</v>
+        <v>102211179</v>
       </c>
       <c r="C2111" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D2111" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2112" spans="1:4">
       <c r="A2112" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2112" s="2">
-        <v>102456984</v>
+        <v>102219144</v>
       </c>
       <c r="C2112" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D2112" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2113" spans="1:4">
       <c r="A2113" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2113" s="2">
-        <v>102456993</v>
+        <v>102326882</v>
       </c>
       <c r="C2113" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D2113" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2114" spans="1:4">
       <c r="A2114" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2114" s="2">
-        <v>102457937</v>
+        <v>102343359</v>
       </c>
       <c r="C2114" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D2114" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2115" spans="1:4">
       <c r="A2115" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2115" s="2">
-        <v>102458550</v>
+        <v>102369579</v>
       </c>
       <c r="C2115" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D2115" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2116" spans="1:4">
       <c r="A2116" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2116" s="2">
-        <v>102464498</v>
+        <v>102370804</v>
       </c>
       <c r="C2116" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D2116" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2117" spans="1:4">
       <c r="A2117" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2117" s="2">
-        <v>102477288</v>
+        <v>102371964</v>
       </c>
       <c r="C2117" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D2117" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2118" spans="1:4">
       <c r="A2118" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2118" s="2">
-        <v>102477293</v>
+        <v>102456914</v>
       </c>
       <c r="C2118" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D2118" s="2">
         <v>21</v>
@@ -31151,97 +31172,97 @@
     </row>
     <row r="2119" spans="1:4">
       <c r="A2119" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2119" s="2">
-        <v>102477371</v>
+        <v>102456984</v>
       </c>
       <c r="C2119" s="1" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D2119" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2120" spans="1:4">
       <c r="A2120" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2120" s="2">
-        <v>102477422</v>
+        <v>102456993</v>
       </c>
       <c r="C2120" s="1" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D2120" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2121" spans="1:4">
       <c r="A2121" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2121" s="2">
-        <v>102477510</v>
+        <v>102457937</v>
       </c>
       <c r="C2121" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D2121" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2122" spans="1:4">
       <c r="A2122" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2122" s="2">
-        <v>102478278</v>
+        <v>102458550</v>
       </c>
       <c r="C2122" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D2122" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2123" spans="1:4">
       <c r="A2123" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2123" s="2">
-        <v>102482237</v>
+        <v>102464498</v>
       </c>
       <c r="C2123" s="1" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D2123" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2124" spans="1:4">
       <c r="A2124" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2124" s="2">
-        <v>102484482</v>
+        <v>102477288</v>
       </c>
       <c r="C2124" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D2124" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2125" spans="1:4">
       <c r="A2125" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2125" s="2">
-        <v>102502720</v>
+        <v>102477293</v>
       </c>
       <c r="C2125" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D2125" s="2">
         <v>21</v>
@@ -31249,13 +31270,13 @@
     </row>
     <row r="2126" spans="1:4">
       <c r="A2126" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2126" s="2">
-        <v>102502737</v>
+        <v>102477371</v>
       </c>
       <c r="C2126" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D2126" s="2">
         <v>22</v>
@@ -31263,69 +31284,69 @@
     </row>
     <row r="2127" spans="1:4">
       <c r="A2127" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2127" s="2">
-        <v>102502871</v>
+        <v>102477422</v>
       </c>
       <c r="C2127" s="1" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D2127" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2128" spans="1:4">
       <c r="A2128" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2128" s="2">
-        <v>102503478</v>
+        <v>102477510</v>
       </c>
       <c r="C2128" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D2128" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2129" spans="1:4">
       <c r="A2129" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2129" s="2">
-        <v>102507584</v>
+        <v>102478278</v>
       </c>
       <c r="C2129" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D2129" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2130" spans="1:4">
       <c r="A2130" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2130" s="2">
-        <v>102509109</v>
+        <v>102482237</v>
       </c>
       <c r="C2130" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D2130" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2131" spans="1:4">
       <c r="A2131" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2131" s="2">
-        <v>102511945</v>
+        <v>102484482</v>
       </c>
       <c r="C2131" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D2131" s="2">
         <v>20</v>
@@ -31333,27 +31354,27 @@
     </row>
     <row r="2132" spans="1:4">
       <c r="A2132" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2132" s="2">
-        <v>102517330</v>
+        <v>102502720</v>
       </c>
       <c r="C2132" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D2132" s="2">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2133" spans="1:4">
       <c r="A2133" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2133" s="2">
-        <v>102517333</v>
+        <v>102502737</v>
       </c>
       <c r="C2133" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D2133" s="2">
         <v>22</v>
@@ -31361,111 +31382,111 @@
     </row>
     <row r="2134" spans="1:4">
       <c r="A2134" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2134" s="2">
-        <v>102517346</v>
+        <v>102502871</v>
       </c>
       <c r="C2134" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D2134" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2135" spans="1:4">
       <c r="A2135" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2135" s="2">
-        <v>102821757</v>
+        <v>102503478</v>
       </c>
       <c r="C2135" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D2135" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2136" spans="1:4">
       <c r="A2136" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2136" s="2">
-        <v>102821761</v>
+        <v>102507584</v>
       </c>
       <c r="C2136" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D2136" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2137" spans="1:4">
       <c r="A2137" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2137" s="2">
-        <v>102830253</v>
+        <v>102509109</v>
       </c>
       <c r="C2137" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D2137" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2138" spans="1:4">
       <c r="A2138" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2138" s="2">
-        <v>102830316</v>
+        <v>102511945</v>
       </c>
       <c r="C2138" s="1" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D2138" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2139" spans="1:4">
       <c r="A2139" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2139" s="2">
-        <v>102831065</v>
+        <v>102517330</v>
       </c>
       <c r="C2139" s="1" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D2139" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2140" spans="1:4">
       <c r="A2140" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2140" s="2">
-        <v>102837399</v>
+        <v>102517333</v>
       </c>
       <c r="C2140" s="1" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D2140" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2141" spans="1:4">
       <c r="A2141" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2141" s="2">
-        <v>102843519</v>
+        <v>102517346</v>
       </c>
       <c r="C2141" s="1" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D2141" s="2">
         <v>19</v>
@@ -31473,97 +31494,97 @@
     </row>
     <row r="2142" spans="1:4">
       <c r="A2142" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2142" s="2">
-        <v>102855952</v>
+        <v>102821757</v>
       </c>
       <c r="C2142" s="1" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D2142" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2143" spans="1:4">
       <c r="A2143" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2143" s="2">
-        <v>102864715</v>
+        <v>102821761</v>
       </c>
       <c r="C2143" s="1" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D2143" s="2">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2144" spans="1:4">
       <c r="A2144" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2144" s="2">
-        <v>102871040</v>
+        <v>102830253</v>
       </c>
       <c r="C2144" s="1" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="D2144" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2145" spans="1:4">
       <c r="A2145" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2145" s="2">
-        <v>102879799</v>
+        <v>102830316</v>
       </c>
       <c r="C2145" s="1" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D2145" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2146" spans="1:4">
       <c r="A2146" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2146" s="2">
-        <v>102884064</v>
+        <v>102831065</v>
       </c>
       <c r="C2146" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D2146" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2147" spans="1:4">
       <c r="A2147" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2147" s="2">
-        <v>102884675</v>
+        <v>102837399</v>
       </c>
       <c r="C2147" s="1" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D2147" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2148" spans="1:4">
       <c r="A2148" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2148" s="2">
-        <v>102908267</v>
+        <v>102843519</v>
       </c>
       <c r="C2148" s="1" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D2148" s="2">
         <v>19</v>
@@ -31571,139 +31592,139 @@
     </row>
     <row r="2149" spans="1:4">
       <c r="A2149" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2149" s="2">
-        <v>103028093</v>
+        <v>102855952</v>
       </c>
       <c r="C2149" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D2149" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2150" spans="1:4">
       <c r="A2150" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2150" s="2">
-        <v>103060430</v>
+        <v>102864715</v>
       </c>
       <c r="C2150" s="1" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D2150" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2151" spans="1:4">
       <c r="A2151" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2151" s="2">
-        <v>103060435</v>
+        <v>102871040</v>
       </c>
       <c r="C2151" s="1" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D2151" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2152" spans="1:4">
       <c r="A2152" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2152" s="2">
-        <v>103060453</v>
+        <v>102879799</v>
       </c>
       <c r="C2152" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D2152" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2153" spans="1:4">
       <c r="A2153" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2153" s="2">
-        <v>103060459</v>
+        <v>102884064</v>
       </c>
       <c r="C2153" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D2153" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2154" spans="1:4">
       <c r="A2154" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2154" s="2">
-        <v>103060462</v>
+        <v>102884675</v>
       </c>
       <c r="C2154" s="1" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="D2154" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2155" spans="1:4">
       <c r="A2155" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2155" s="2">
-        <v>103060467</v>
+        <v>102908267</v>
       </c>
       <c r="C2155" s="1" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D2155" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2156" spans="1:4">
       <c r="A2156" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2156" s="2">
-        <v>103060471</v>
+        <v>103028093</v>
       </c>
       <c r="C2156" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D2156" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2157" spans="1:4">
       <c r="A2157" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2157" s="2">
-        <v>103082092</v>
+        <v>103060430</v>
       </c>
       <c r="C2157" s="1" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D2157" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2158" spans="1:4">
       <c r="A2158" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2158" s="2">
-        <v>103082095</v>
+        <v>103060435</v>
       </c>
       <c r="C2158" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D2158" s="2">
         <v>20</v>
@@ -31711,97 +31732,97 @@
     </row>
     <row r="2159" spans="1:4">
       <c r="A2159" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2159" s="2">
-        <v>103082112</v>
+        <v>103060453</v>
       </c>
       <c r="C2159" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D2159" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2160" spans="1:4">
       <c r="A2160" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2160" s="2">
-        <v>103082113</v>
+        <v>103060459</v>
       </c>
       <c r="C2160" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D2160" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2161" spans="1:4">
       <c r="A2161" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2161" s="2">
-        <v>103082118</v>
+        <v>103060462</v>
       </c>
       <c r="C2161" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D2161" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2162" spans="1:4">
       <c r="A2162" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2162" s="2">
-        <v>103082119</v>
+        <v>103060467</v>
       </c>
       <c r="C2162" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D2162" s="2">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2163" spans="1:4">
       <c r="A2163" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2163" s="2">
-        <v>103082121</v>
+        <v>103060471</v>
       </c>
       <c r="C2163" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D2163" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2164" spans="1:4">
       <c r="A2164" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2164" s="2">
-        <v>103082161</v>
+        <v>103082092</v>
       </c>
       <c r="C2164" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D2164" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2165" spans="1:4">
       <c r="A2165" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2165" s="2">
-        <v>103082166</v>
+        <v>103082095</v>
       </c>
       <c r="C2165" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D2165" s="2">
         <v>20</v>
@@ -31809,265 +31830,265 @@
     </row>
     <row r="2166" spans="1:4">
       <c r="A2166" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2166" s="2">
-        <v>103082385</v>
+        <v>103082112</v>
       </c>
       <c r="C2166" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D2166" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2167" spans="1:4">
       <c r="A2167" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2167" s="2">
-        <v>103085298</v>
+        <v>103082113</v>
       </c>
       <c r="C2167" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D2167" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2168" spans="1:4">
       <c r="A2168" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2168" s="2">
-        <v>103088009</v>
+        <v>103082118</v>
       </c>
       <c r="C2168" s="1" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D2168" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2169" spans="1:4">
       <c r="A2169" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2169" s="2">
-        <v>103092092</v>
+        <v>103082119</v>
       </c>
       <c r="C2169" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D2169" s="2">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2170" spans="1:4">
       <c r="A2170" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2170" s="2">
-        <v>103092141</v>
+        <v>103082121</v>
       </c>
       <c r="C2170" s="1" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D2170" s="2">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2171" spans="1:4">
       <c r="A2171" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2171" s="2">
-        <v>103092310</v>
+        <v>103082161</v>
       </c>
       <c r="C2171" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D2171" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2172" spans="1:4">
       <c r="A2172" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2172" s="2">
-        <v>103092316</v>
+        <v>103082166</v>
       </c>
       <c r="C2172" s="1" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D2172" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2173" spans="1:4">
       <c r="A2173" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2173" s="2">
-        <v>103101206</v>
+        <v>103082385</v>
       </c>
       <c r="C2173" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D2173" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2174" spans="1:4">
       <c r="A2174" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2174" s="2">
-        <v>103101215</v>
+        <v>103085298</v>
       </c>
       <c r="C2174" s="1" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D2174" s="2">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2175" spans="1:4">
       <c r="A2175" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2175" s="2">
-        <v>103101217</v>
+        <v>103088009</v>
       </c>
       <c r="C2175" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D2175" s="2">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2176" spans="1:4">
       <c r="A2176" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2176" s="2">
-        <v>103103196</v>
+        <v>103092092</v>
       </c>
       <c r="C2176" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D2176" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2177" spans="1:4">
       <c r="A2177" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2177" s="2">
-        <v>103103198</v>
+        <v>103092141</v>
       </c>
       <c r="C2177" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D2177" s="2">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2178" spans="1:4">
       <c r="A2178" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2178" s="2">
-        <v>103103213</v>
+        <v>103092310</v>
       </c>
       <c r="C2178" s="1" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D2178" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2179" spans="1:4">
       <c r="A2179" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2179" s="2">
-        <v>103105143</v>
+        <v>103092316</v>
       </c>
       <c r="C2179" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D2179" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2180" spans="1:4">
       <c r="A2180" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2180" s="2">
-        <v>103109089</v>
+        <v>103101206</v>
       </c>
       <c r="C2180" s="1" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D2180" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2181" spans="1:4">
       <c r="A2181" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2181" s="2">
-        <v>103109090</v>
+        <v>103101215</v>
       </c>
       <c r="C2181" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D2181" s="2">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2182" spans="1:4">
       <c r="A2182" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2182" s="2">
-        <v>103109091</v>
+        <v>103101217</v>
       </c>
       <c r="C2182" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D2182" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2183" spans="1:4">
       <c r="A2183" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2183" s="2">
-        <v>103109136</v>
+        <v>103103196</v>
       </c>
       <c r="C2183" s="1" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D2183" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2184" spans="1:4">
       <c r="A2184" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2184" s="2">
-        <v>103109151</v>
+        <v>103103198</v>
       </c>
       <c r="C2184" s="1" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D2184" s="2">
         <v>21</v>
@@ -32075,27 +32096,27 @@
     </row>
     <row r="2185" spans="1:4">
       <c r="A2185" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2185" s="2">
-        <v>103109336</v>
+        <v>103103213</v>
       </c>
       <c r="C2185" s="1" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D2185" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2186" spans="1:4">
       <c r="A2186" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2186" s="2">
-        <v>103109339</v>
+        <v>103105143</v>
       </c>
       <c r="C2186" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D2186" s="2">
         <v>20</v>
@@ -32103,27 +32124,27 @@
     </row>
     <row r="2187" spans="1:4">
       <c r="A2187" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2187" s="2">
-        <v>103109343</v>
+        <v>103109089</v>
       </c>
       <c r="C2187" s="1" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D2187" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2188" spans="1:4">
       <c r="A2188" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2188" s="2">
-        <v>103109357</v>
+        <v>103109090</v>
       </c>
       <c r="C2188" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D2188" s="2">
         <v>17</v>
@@ -32131,41 +32152,41 @@
     </row>
     <row r="2189" spans="1:4">
       <c r="A2189" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2189" s="2">
-        <v>103110013</v>
+        <v>103109091</v>
       </c>
       <c r="C2189" s="1" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="D2189" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2190" spans="1:4">
       <c r="A2190" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2190" s="2">
-        <v>103110453</v>
+        <v>103109136</v>
       </c>
       <c r="C2190" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D2190" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2191" spans="1:4">
       <c r="A2191" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2191" s="2">
-        <v>103111713</v>
+        <v>103109151</v>
       </c>
       <c r="C2191" s="1" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D2191" s="2">
         <v>21</v>
@@ -32173,251 +32194,251 @@
     </row>
     <row r="2192" spans="1:4">
       <c r="A2192" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2192" s="2">
-        <v>103111920</v>
+        <v>103109336</v>
       </c>
       <c r="C2192" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D2192" s="2">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2193" spans="1:4">
       <c r="A2193" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2193" s="2">
-        <v>103111956</v>
+        <v>103109339</v>
       </c>
       <c r="C2193" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D2193" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2194" spans="1:4">
       <c r="A2194" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2194" s="2">
-        <v>103113926</v>
+        <v>103109343</v>
       </c>
       <c r="C2194" s="1" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D2194" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2195" spans="1:4">
       <c r="A2195" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2195" s="2">
-        <v>103115341</v>
+        <v>103109357</v>
       </c>
       <c r="C2195" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D2195" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2196" spans="1:4">
       <c r="A2196" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2196" s="2">
-        <v>103116487</v>
+        <v>103110013</v>
       </c>
       <c r="C2196" s="1" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D2196" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2197" spans="1:4">
       <c r="A2197" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2197" s="2">
-        <v>103116496</v>
+        <v>103110453</v>
       </c>
       <c r="C2197" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D2197" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2198" spans="1:4">
       <c r="A2198" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2198" s="2">
-        <v>103117188</v>
+        <v>103111713</v>
       </c>
       <c r="C2198" s="1" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D2198" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2199" spans="1:4">
       <c r="A2199" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2199" s="2">
-        <v>103121097</v>
+        <v>103111920</v>
       </c>
       <c r="C2199" s="1" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D2199" s="2">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2200" spans="1:4">
       <c r="A2200" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2200" s="2">
-        <v>103121098</v>
+        <v>103111956</v>
       </c>
       <c r="C2200" s="1" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D2200" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2201" spans="1:4">
       <c r="A2201" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2201" s="2">
-        <v>103125208</v>
+        <v>103113926</v>
       </c>
       <c r="C2201" s="1" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="D2201" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2202" spans="1:4">
       <c r="A2202" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2202" s="2">
-        <v>103125228</v>
+        <v>103115341</v>
       </c>
       <c r="C2202" s="1" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="D2202" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2203" spans="1:4">
       <c r="A2203" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2203" s="2">
-        <v>103125229</v>
+        <v>103116487</v>
       </c>
       <c r="C2203" s="1" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="D2203" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2204" spans="1:4">
       <c r="A2204" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2204" s="2">
-        <v>103127936</v>
+        <v>103116496</v>
       </c>
       <c r="C2204" s="1" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="D2204" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2205" spans="1:4">
       <c r="A2205" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2205" s="2">
-        <v>103130519</v>
+        <v>103117188</v>
       </c>
       <c r="C2205" s="1" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="D2205" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2206" spans="1:4">
       <c r="A2206" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2206" s="2">
-        <v>103132423</v>
+        <v>103121097</v>
       </c>
       <c r="C2206" s="1" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="D2206" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2207" spans="1:4">
       <c r="A2207" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2207" s="2">
-        <v>103132424</v>
+        <v>103121098</v>
       </c>
       <c r="C2207" s="1" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="D2207" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2208" spans="1:4">
       <c r="A2208" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2208" s="2">
-        <v>103133036</v>
+        <v>103125208</v>
       </c>
       <c r="C2208" s="1" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="D2208" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2209" spans="1:4">
       <c r="A2209" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2209" s="2">
-        <v>103136107</v>
+        <v>103125228</v>
       </c>
       <c r="C2209" s="1" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="D2209" s="2">
         <v>18</v>
@@ -32425,41 +32446,41 @@
     </row>
     <row r="2210" spans="1:4">
       <c r="A2210" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2210" s="2">
-        <v>103139871</v>
+        <v>103125229</v>
       </c>
       <c r="C2210" s="1" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="D2210" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2211" spans="1:4">
       <c r="A2211" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2211" s="2">
-        <v>103145144</v>
+        <v>103127936</v>
       </c>
       <c r="C2211" s="1" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="D2211" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2212" spans="1:4">
       <c r="A2212" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2212" s="2">
-        <v>103169793</v>
+        <v>103130519</v>
       </c>
       <c r="C2212" s="1" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="D2212" s="2">
         <v>18</v>
@@ -32467,251 +32488,251 @@
     </row>
     <row r="2213" spans="1:4">
       <c r="A2213" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2213" s="2">
-        <v>103169795</v>
+        <v>103132423</v>
       </c>
       <c r="C2213" s="1" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="D2213" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2214" spans="1:4">
       <c r="A2214" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2214" s="2">
-        <v>103169797</v>
+        <v>103132424</v>
       </c>
       <c r="C2214" s="1" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="D2214" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2215" spans="1:4">
       <c r="A2215" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2215" s="2">
-        <v>103169814</v>
+        <v>103133036</v>
       </c>
       <c r="C2215" s="1" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="D2215" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2216" spans="1:4">
       <c r="A2216" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2216" s="2">
-        <v>103169816</v>
+        <v>103136107</v>
       </c>
       <c r="C2216" s="1" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D2216" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2217" spans="1:4">
       <c r="A2217" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2217" s="2">
-        <v>103171084</v>
+        <v>103139871</v>
       </c>
       <c r="C2217" s="1" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="D2217" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2218" spans="1:4">
       <c r="A2218" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2218" s="2">
-        <v>103171103</v>
+        <v>103145144</v>
       </c>
       <c r="C2218" s="1" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="D2218" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2219" spans="1:4">
       <c r="A2219" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2219" s="2">
-        <v>103173195</v>
+        <v>103169793</v>
       </c>
       <c r="C2219" s="1" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="D2219" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2220" spans="1:4">
       <c r="A2220" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2220" s="2">
-        <v>103173197</v>
+        <v>103169795</v>
       </c>
       <c r="C2220" s="1" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="D2220" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2221" spans="1:4">
       <c r="A2221" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2221" s="2">
-        <v>103283831</v>
+        <v>103169797</v>
       </c>
       <c r="C2221" s="1" t="s">
-        <v>352</v>
+        <v>260</v>
       </c>
       <c r="D2221" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2222" spans="1:4">
       <c r="A2222" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2222" s="2">
-        <v>103293732</v>
+        <v>103169814</v>
       </c>
       <c r="C2222" s="1" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="D2222" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2223" spans="1:4">
       <c r="A2223" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2223" s="2">
-        <v>103293737</v>
+        <v>103169816</v>
       </c>
       <c r="C2223" s="1" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="D2223" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2224" spans="1:4">
       <c r="A2224" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2224" s="2">
-        <v>103293745</v>
+        <v>103171084</v>
       </c>
       <c r="C2224" s="1" t="s">
-        <v>353</v>
+        <v>272</v>
       </c>
       <c r="D2224" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2225" spans="1:4">
       <c r="A2225" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2225" s="2">
-        <v>103293751</v>
+        <v>103171103</v>
       </c>
       <c r="C2225" s="1" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="D2225" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2226" spans="1:4">
       <c r="A2226" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2226" s="2">
-        <v>103293756</v>
+        <v>103173195</v>
       </c>
       <c r="C2226" s="1" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="D2226" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2227" spans="1:4">
       <c r="A2227" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2227" s="2">
-        <v>103293766</v>
+        <v>103173197</v>
       </c>
       <c r="C2227" s="1" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="D2227" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2228" spans="1:4">
       <c r="A2228" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2228" s="2">
-        <v>103293773</v>
+        <v>103283831</v>
       </c>
       <c r="C2228" s="1" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="D2228" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2229" spans="1:4">
       <c r="A2229" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2229" s="2">
-        <v>103294755</v>
+        <v>103293732</v>
       </c>
       <c r="C2229" s="1" t="s">
-        <v>150</v>
+        <v>286</v>
       </c>
       <c r="D2229" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2230" spans="1:4">
       <c r="A2230" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2230" s="2">
-        <v>103296160</v>
+        <v>103293737</v>
       </c>
       <c r="C2230" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D2230" s="2">
         <v>18</v>
@@ -32719,13 +32740,13 @@
     </row>
     <row r="2231" spans="1:4">
       <c r="A2231" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2231" s="2">
-        <v>103296167</v>
+        <v>103293745</v>
       </c>
       <c r="C2231" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D2231" s="2">
         <v>20</v>
@@ -32733,111 +32754,111 @@
     </row>
     <row r="2232" spans="1:4">
       <c r="A2232" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2232" s="2">
-        <v>103297566</v>
+        <v>103293751</v>
       </c>
       <c r="C2232" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D2232" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2233" spans="1:4">
       <c r="A2233" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2233" s="2">
-        <v>103300418</v>
+        <v>103293756</v>
       </c>
       <c r="C2233" s="1" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D2233" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2234" spans="1:4">
       <c r="A2234" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2234" s="2">
-        <v>103304841</v>
+        <v>103293766</v>
       </c>
       <c r="C2234" s="1" t="s">
         <v>290</v>
       </c>
       <c r="D2234" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2235" spans="1:4">
       <c r="A2235" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2235" s="2">
-        <v>103304846</v>
+        <v>103293773</v>
       </c>
       <c r="C2235" s="1" t="s">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="D2235" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2236" spans="1:4">
       <c r="A2236" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2236" s="2">
-        <v>103304863</v>
+        <v>103294755</v>
       </c>
       <c r="C2236" s="1" t="s">
-        <v>360</v>
+        <v>150</v>
       </c>
       <c r="D2236" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2237" spans="1:4">
       <c r="A2237" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2237" s="2">
-        <v>103304866</v>
+        <v>103296160</v>
       </c>
       <c r="C2237" s="1" t="s">
-        <v>130</v>
+        <v>292</v>
       </c>
       <c r="D2237" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2238" spans="1:4">
       <c r="A2238" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2238" s="2">
-        <v>103304868</v>
+        <v>103296167</v>
       </c>
       <c r="C2238" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D2238" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2239" spans="1:4">
       <c r="A2239" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2239" s="2">
-        <v>103304875</v>
+        <v>103297566</v>
       </c>
       <c r="C2239" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D2239" s="2">
         <v>19</v>
@@ -32845,153 +32866,153 @@
     </row>
     <row r="2240" spans="1:4">
       <c r="A2240" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2240" s="2">
-        <v>103305150</v>
+        <v>103300418</v>
       </c>
       <c r="C2240" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D2240" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2241" spans="1:4">
       <c r="A2241" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2241" s="2">
-        <v>103305154</v>
+        <v>103304841</v>
       </c>
       <c r="C2241" s="1" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="D2241" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2242" spans="1:4">
       <c r="A2242" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2242" s="2">
-        <v>103305160</v>
+        <v>103304846</v>
       </c>
       <c r="C2242" s="1" t="s">
-        <v>298</v>
+        <v>359</v>
       </c>
       <c r="D2242" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2243" spans="1:4">
       <c r="A2243" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B2243" s="2">
-        <v>103305165</v>
+        <v>103304863</v>
       </c>
       <c r="C2243" s="1" t="s">
-        <v>299</v>
+        <v>360</v>
       </c>
       <c r="D2243" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2244" spans="1:4">
       <c r="A2244" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B2244" s="2">
-        <v>102029874</v>
+        <v>103304866</v>
       </c>
       <c r="C2244" s="1" t="s">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="D2244" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2245" spans="1:4">
       <c r="A2245" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B2245" s="2">
-        <v>102173363</v>
+        <v>103304868</v>
       </c>
       <c r="C2245" s="1" t="s">
-        <v>7</v>
+        <v>361</v>
       </c>
       <c r="D2245" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2246" spans="1:4">
       <c r="A2246" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B2246" s="2">
-        <v>102211179</v>
+        <v>103304875</v>
       </c>
       <c r="C2246" s="1" t="s">
-        <v>10</v>
+        <v>295</v>
       </c>
       <c r="D2246" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2247" spans="1:4">
       <c r="A2247" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B2247" s="2">
-        <v>102219144</v>
+        <v>103305150</v>
       </c>
       <c r="C2247" s="1" t="s">
-        <v>12</v>
+        <v>296</v>
       </c>
       <c r="D2247" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2248" spans="1:4">
       <c r="A2248" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B2248" s="2">
-        <v>102326882</v>
+        <v>103305154</v>
       </c>
       <c r="C2248" s="1" t="s">
-        <v>16</v>
+        <v>297</v>
       </c>
       <c r="D2248" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2249" spans="1:4">
       <c r="A2249" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B2249" s="2">
-        <v>102343359</v>
+        <v>103305160</v>
       </c>
       <c r="C2249" s="1" t="s">
-        <v>17</v>
+        <v>298</v>
       </c>
       <c r="D2249" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2250" spans="1:4">
       <c r="A2250" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B2250" s="2">
-        <v>102351853</v>
+        <v>103305165</v>
       </c>
       <c r="C2250" s="1" t="s">
-        <v>18</v>
+        <v>299</v>
       </c>
       <c r="D2250" s="2">
         <v>21</v>
@@ -32999,55 +33020,55 @@
     </row>
     <row r="2251" spans="1:4">
       <c r="A2251" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2251" s="2">
-        <v>102369579</v>
+        <v>102029874</v>
       </c>
       <c r="C2251" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D2251" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2252" spans="1:4">
       <c r="A2252" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2252" s="2">
-        <v>102370804</v>
+        <v>102173363</v>
       </c>
       <c r="C2252" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D2252" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2253" spans="1:4">
       <c r="A2253" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2253" s="2">
-        <v>102371964</v>
+        <v>102211179</v>
       </c>
       <c r="C2253" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D2253" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2254" spans="1:4">
       <c r="A2254" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2254" s="2">
-        <v>102456914</v>
+        <v>102219144</v>
       </c>
       <c r="C2254" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D2254" s="2">
         <v>22</v>
@@ -33055,13 +33076,13 @@
     </row>
     <row r="2255" spans="1:4">
       <c r="A2255" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2255" s="2">
-        <v>102456984</v>
+        <v>102326882</v>
       </c>
       <c r="C2255" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D2255" s="2">
         <v>21</v>
@@ -33069,69 +33090,69 @@
     </row>
     <row r="2256" spans="1:4">
       <c r="A2256" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2256" s="2">
-        <v>102456993</v>
+        <v>102343359</v>
       </c>
       <c r="C2256" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D2256" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2257" spans="1:4">
       <c r="A2257" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2257" s="2">
-        <v>102457124</v>
+        <v>102351853</v>
       </c>
       <c r="C2257" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D2257" s="2">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2258" spans="1:4">
       <c r="A2258" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2258" s="2">
-        <v>102457937</v>
+        <v>102369579</v>
       </c>
       <c r="C2258" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D2258" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2259" spans="1:4">
       <c r="A2259" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2259" s="2">
-        <v>102458550</v>
+        <v>102370804</v>
       </c>
       <c r="C2259" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D2259" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2260" spans="1:4">
       <c r="A2260" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2260" s="2">
-        <v>102464498</v>
+        <v>102371964</v>
       </c>
       <c r="C2260" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D2260" s="2">
         <v>20</v>
@@ -33139,125 +33160,125 @@
     </row>
     <row r="2261" spans="1:4">
       <c r="A2261" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2261" s="2">
-        <v>102466917</v>
+        <v>102456914</v>
       </c>
       <c r="C2261" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D2261" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2262" spans="1:4">
       <c r="A2262" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2262" s="2">
-        <v>102477288</v>
+        <v>102456984</v>
       </c>
       <c r="C2262" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D2262" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2263" spans="1:4">
       <c r="A2263" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2263" s="2">
-        <v>102477293</v>
+        <v>102456993</v>
       </c>
       <c r="C2263" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D2263" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2264" spans="1:4">
       <c r="A2264" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2264" s="2">
-        <v>102477371</v>
+        <v>102457124</v>
       </c>
       <c r="C2264" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="D2264" s="2">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2265" spans="1:4">
       <c r="A2265" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2265" s="2">
-        <v>102477422</v>
+        <v>102457937</v>
       </c>
       <c r="C2265" s="1" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D2265" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2266" spans="1:4">
       <c r="A2266" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2266" s="2">
-        <v>102477510</v>
+        <v>102458550</v>
       </c>
       <c r="C2266" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D2266" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2267" spans="1:4">
       <c r="A2267" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2267" s="2">
-        <v>102478278</v>
+        <v>102464498</v>
       </c>
       <c r="C2267" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D2267" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2268" spans="1:4">
       <c r="A2268" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2268" s="2">
-        <v>102482237</v>
+        <v>102466917</v>
       </c>
       <c r="C2268" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D2268" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2269" spans="1:4">
       <c r="A2269" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2269" s="2">
-        <v>102484482</v>
+        <v>102477288</v>
       </c>
       <c r="C2269" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D2269" s="2">
         <v>22</v>
@@ -33265,167 +33286,167 @@
     </row>
     <row r="2270" spans="1:4">
       <c r="A2270" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2270" s="2">
-        <v>102502720</v>
+        <v>102477293</v>
       </c>
       <c r="C2270" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D2270" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2271" spans="1:4">
       <c r="A2271" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2271" s="2">
-        <v>102502737</v>
+        <v>102477371</v>
       </c>
       <c r="C2271" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D2271" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2272" spans="1:4">
       <c r="A2272" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2272" s="2">
-        <v>102502871</v>
+        <v>102477422</v>
       </c>
       <c r="C2272" s="1" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D2272" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2273" spans="1:4">
       <c r="A2273" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2273" s="2">
-        <v>102503478</v>
+        <v>102477510</v>
       </c>
       <c r="C2273" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D2273" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2274" spans="1:4">
       <c r="A2274" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2274" s="2">
-        <v>102507584</v>
+        <v>102478278</v>
       </c>
       <c r="C2274" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D2274" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2275" spans="1:4">
       <c r="A2275" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2275" s="2">
-        <v>102509109</v>
+        <v>102482237</v>
       </c>
       <c r="C2275" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D2275" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2276" spans="1:4">
       <c r="A2276" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2276" s="2">
-        <v>102511945</v>
+        <v>102484482</v>
       </c>
       <c r="C2276" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D2276" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2277" spans="1:4">
       <c r="A2277" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2277" s="2">
-        <v>102517330</v>
+        <v>102502720</v>
       </c>
       <c r="C2277" s="1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D2277" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2278" spans="1:4">
       <c r="A2278" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2278" s="2">
-        <v>102517333</v>
+        <v>102502737</v>
       </c>
       <c r="C2278" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D2278" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2279" spans="1:4">
       <c r="A2279" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2279" s="2">
-        <v>102517346</v>
+        <v>102502871</v>
       </c>
       <c r="C2279" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D2279" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2280" spans="1:4">
       <c r="A2280" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2280" s="2">
-        <v>102821757</v>
+        <v>102503478</v>
       </c>
       <c r="C2280" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D2280" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2281" spans="1:4">
       <c r="A2281" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2281" s="2">
-        <v>102821761</v>
+        <v>102507584</v>
       </c>
       <c r="C2281" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D2281" s="2">
         <v>21</v>
@@ -33433,139 +33454,139 @@
     </row>
     <row r="2282" spans="1:4">
       <c r="A2282" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2282" s="2">
-        <v>102830253</v>
+        <v>102509109</v>
       </c>
       <c r="C2282" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D2282" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2283" spans="1:4">
       <c r="A2283" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2283" s="2">
-        <v>102830316</v>
+        <v>102511945</v>
       </c>
       <c r="C2283" s="1" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D2283" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2284" spans="1:4">
       <c r="A2284" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2284" s="2">
-        <v>102831065</v>
+        <v>102517330</v>
       </c>
       <c r="C2284" s="1" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D2284" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2285" spans="1:4">
       <c r="A2285" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2285" s="2">
-        <v>102837399</v>
+        <v>102517333</v>
       </c>
       <c r="C2285" s="1" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D2285" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2286" spans="1:4">
       <c r="A2286" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2286" s="2">
-        <v>102843519</v>
+        <v>102517346</v>
       </c>
       <c r="C2286" s="1" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D2286" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2287" spans="1:4">
       <c r="A2287" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2287" s="2">
-        <v>102850964</v>
+        <v>102821757</v>
       </c>
       <c r="C2287" s="1" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D2287" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2288" spans="1:4">
       <c r="A2288" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2288" s="2">
-        <v>102855952</v>
+        <v>102821761</v>
       </c>
       <c r="C2288" s="1" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D2288" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2289" spans="1:4">
       <c r="A2289" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2289" s="2">
-        <v>102864715</v>
+        <v>102830253</v>
       </c>
       <c r="C2289" s="1" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D2289" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2290" spans="1:4">
       <c r="A2290" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2290" s="2">
-        <v>102871040</v>
+        <v>102830316</v>
       </c>
       <c r="C2290" s="1" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D2290" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2291" spans="1:4">
       <c r="A2291" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2291" s="2">
-        <v>102879799</v>
+        <v>102831065</v>
       </c>
       <c r="C2291" s="1" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D2291" s="2">
         <v>12</v>
@@ -33573,83 +33594,83 @@
     </row>
     <row r="2292" spans="1:4">
       <c r="A2292" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2292" s="2">
-        <v>102884064</v>
+        <v>102837399</v>
       </c>
       <c r="C2292" s="1" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D2292" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2293" spans="1:4">
       <c r="A2293" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2293" s="2">
-        <v>102884675</v>
+        <v>102843519</v>
       </c>
       <c r="C2293" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D2293" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2294" spans="1:4">
       <c r="A2294" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2294" s="2">
-        <v>102908267</v>
+        <v>102850964</v>
       </c>
       <c r="C2294" s="1" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D2294" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2295" spans="1:4">
       <c r="A2295" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2295" s="2">
-        <v>103001864</v>
+        <v>102855952</v>
       </c>
       <c r="C2295" s="1" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D2295" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2296" spans="1:4">
       <c r="A2296" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2296" s="2">
-        <v>103028093</v>
+        <v>102864715</v>
       </c>
       <c r="C2296" s="1" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D2296" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2297" spans="1:4">
       <c r="A2297" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2297" s="2">
-        <v>103060430</v>
+        <v>102871040</v>
       </c>
       <c r="C2297" s="1" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="D2297" s="2">
         <v>21</v>
@@ -33657,237 +33678,237 @@
     </row>
     <row r="2298" spans="1:4">
       <c r="A2298" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2298" s="2">
-        <v>103060435</v>
+        <v>102879799</v>
       </c>
       <c r="C2298" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D2298" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2299" spans="1:4">
       <c r="A2299" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2299" s="2">
-        <v>103060453</v>
+        <v>102884064</v>
       </c>
       <c r="C2299" s="1" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="D2299" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2300" spans="1:4">
       <c r="A2300" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2300" s="2">
-        <v>103060459</v>
+        <v>102884675</v>
       </c>
       <c r="C2300" s="1" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D2300" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2301" spans="1:4">
       <c r="A2301" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2301" s="2">
-        <v>103060462</v>
+        <v>102908267</v>
       </c>
       <c r="C2301" s="1" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D2301" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2302" spans="1:4">
       <c r="A2302" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2302" s="2">
-        <v>103060467</v>
+        <v>103001864</v>
       </c>
       <c r="C2302" s="1" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D2302" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2303" spans="1:4">
       <c r="A2303" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2303" s="2">
-        <v>103060471</v>
+        <v>103028093</v>
       </c>
       <c r="C2303" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D2303" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2304" spans="1:4">
       <c r="A2304" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2304" s="2">
-        <v>103082092</v>
+        <v>103060430</v>
       </c>
       <c r="C2304" s="1" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D2304" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2305" spans="1:4">
       <c r="A2305" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2305" s="2">
-        <v>103082095</v>
+        <v>103060435</v>
       </c>
       <c r="C2305" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D2305" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2306" spans="1:4">
       <c r="A2306" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2306" s="2">
-        <v>103082112</v>
+        <v>103060453</v>
       </c>
       <c r="C2306" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D2306" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2307" spans="1:4">
       <c r="A2307" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2307" s="2">
-        <v>103082113</v>
+        <v>103060459</v>
       </c>
       <c r="C2307" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D2307" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2308" spans="1:4">
       <c r="A2308" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2308" s="2">
-        <v>103082118</v>
+        <v>103060462</v>
       </c>
       <c r="C2308" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D2308" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2309" spans="1:4">
       <c r="A2309" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2309" s="2">
-        <v>103082119</v>
+        <v>103060467</v>
       </c>
       <c r="C2309" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D2309" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2310" spans="1:4">
       <c r="A2310" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2310" s="2">
-        <v>103082121</v>
+        <v>103060471</v>
       </c>
       <c r="C2310" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D2310" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2311" spans="1:4">
       <c r="A2311" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2311" s="2">
-        <v>103082160</v>
+        <v>103082092</v>
       </c>
       <c r="C2311" s="1" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D2311" s="2">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2312" spans="1:4">
       <c r="A2312" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2312" s="2">
-        <v>103082161</v>
+        <v>103082095</v>
       </c>
       <c r="C2312" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D2312" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2313" spans="1:4">
       <c r="A2313" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2313" s="2">
-        <v>103082166</v>
+        <v>103082112</v>
       </c>
       <c r="C2313" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D2313" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2314" spans="1:4">
       <c r="A2314" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2314" s="2">
-        <v>103082385</v>
+        <v>103082113</v>
       </c>
       <c r="C2314" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D2314" s="2">
         <v>22</v>
@@ -33895,419 +33916,419 @@
     </row>
     <row r="2315" spans="1:4">
       <c r="A2315" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2315" s="2">
-        <v>103085298</v>
+        <v>103082118</v>
       </c>
       <c r="C2315" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D2315" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2316" spans="1:4">
       <c r="A2316" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2316" s="2">
-        <v>103088009</v>
+        <v>103082119</v>
       </c>
       <c r="C2316" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D2316" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2317" spans="1:4">
       <c r="A2317" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2317" s="2">
-        <v>103092092</v>
+        <v>103082121</v>
       </c>
       <c r="C2317" s="1" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D2317" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2318" spans="1:4">
       <c r="A2318" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2318" s="2">
-        <v>103092141</v>
+        <v>103082160</v>
       </c>
       <c r="C2318" s="1" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D2318" s="2">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2319" spans="1:4">
       <c r="A2319" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2319" s="2">
-        <v>103092310</v>
+        <v>103082161</v>
       </c>
       <c r="C2319" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D2319" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2320" spans="1:4">
       <c r="A2320" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2320" s="2">
-        <v>103092316</v>
+        <v>103082166</v>
       </c>
       <c r="C2320" s="1" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D2320" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2321" spans="1:4">
       <c r="A2321" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2321" s="2">
-        <v>103101197</v>
+        <v>103082385</v>
       </c>
       <c r="C2321" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D2321" s="2">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2322" spans="1:4">
       <c r="A2322" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2322" s="2">
-        <v>103101206</v>
+        <v>103085298</v>
       </c>
       <c r="C2322" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D2322" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2323" spans="1:4">
       <c r="A2323" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2323" s="2">
-        <v>103101215</v>
+        <v>103088009</v>
       </c>
       <c r="C2323" s="1" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D2323" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2324" spans="1:4">
       <c r="A2324" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2324" s="2">
-        <v>103101217</v>
+        <v>103092092</v>
       </c>
       <c r="C2324" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D2324" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2325" spans="1:4">
       <c r="A2325" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2325" s="2">
-        <v>103103196</v>
+        <v>103092141</v>
       </c>
       <c r="C2325" s="1" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D2325" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2326" spans="1:4">
       <c r="A2326" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2326" s="2">
-        <v>103103198</v>
+        <v>103092310</v>
       </c>
       <c r="C2326" s="1" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D2326" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2327" spans="1:4">
       <c r="A2327" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2327" s="2">
-        <v>103103213</v>
+        <v>103092316</v>
       </c>
       <c r="C2327" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D2327" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2328" spans="1:4">
       <c r="A2328" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2328" s="2">
-        <v>103105143</v>
+        <v>103101197</v>
       </c>
       <c r="C2328" s="1" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D2328" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2329" spans="1:4">
       <c r="A2329" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2329" s="2">
-        <v>103109089</v>
+        <v>103101206</v>
       </c>
       <c r="C2329" s="1" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D2329" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2330" spans="1:4">
       <c r="A2330" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2330" s="2">
-        <v>103109090</v>
+        <v>103101215</v>
       </c>
       <c r="C2330" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D2330" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2331" spans="1:4">
       <c r="A2331" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2331" s="2">
-        <v>103109091</v>
+        <v>103101217</v>
       </c>
       <c r="C2331" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D2331" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2332" spans="1:4">
       <c r="A2332" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2332" s="2">
-        <v>103109136</v>
+        <v>103103196</v>
       </c>
       <c r="C2332" s="1" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D2332" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2333" spans="1:4">
       <c r="A2333" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2333" s="2">
-        <v>103109151</v>
+        <v>103103198</v>
       </c>
       <c r="C2333" s="1" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D2333" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2334" spans="1:4">
       <c r="A2334" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2334" s="2">
-        <v>103109336</v>
+        <v>103103213</v>
       </c>
       <c r="C2334" s="1" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D2334" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2335" spans="1:4">
       <c r="A2335" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2335" s="2">
-        <v>103109339</v>
+        <v>103105143</v>
       </c>
       <c r="C2335" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D2335" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2336" spans="1:4">
       <c r="A2336" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2336" s="2">
-        <v>103109343</v>
+        <v>103109089</v>
       </c>
       <c r="C2336" s="1" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D2336" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2337" spans="1:4">
       <c r="A2337" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2337" s="2">
-        <v>103109357</v>
+        <v>103109090</v>
       </c>
       <c r="C2337" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D2337" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2338" spans="1:4">
       <c r="A2338" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2338" s="2">
-        <v>103110013</v>
+        <v>103109091</v>
       </c>
       <c r="C2338" s="1" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="D2338" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2339" spans="1:4">
       <c r="A2339" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2339" s="2">
-        <v>103110453</v>
+        <v>103109136</v>
       </c>
       <c r="C2339" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D2339" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2340" spans="1:4">
       <c r="A2340" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2340" s="2">
-        <v>103111713</v>
+        <v>103109151</v>
       </c>
       <c r="C2340" s="1" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D2340" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2341" spans="1:4">
       <c r="A2341" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2341" s="2">
-        <v>103111920</v>
+        <v>103109336</v>
       </c>
       <c r="C2341" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D2341" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2342" spans="1:4">
       <c r="A2342" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2342" s="2">
-        <v>103111956</v>
+        <v>103109339</v>
       </c>
       <c r="C2342" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D2342" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2343" spans="1:4">
       <c r="A2343" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2343" s="2">
-        <v>103113926</v>
+        <v>103109343</v>
       </c>
       <c r="C2343" s="1" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D2343" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2344" spans="1:4">
       <c r="A2344" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2344" s="2">
-        <v>103115341</v>
+        <v>103109357</v>
       </c>
       <c r="C2344" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D2344" s="2">
         <v>19</v>
@@ -34315,13 +34336,13 @@
     </row>
     <row r="2345" spans="1:4">
       <c r="A2345" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2345" s="2">
-        <v>103116487</v>
+        <v>103110013</v>
       </c>
       <c r="C2345" s="1" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D2345" s="2">
         <v>22</v>
@@ -34329,125 +34350,125 @@
     </row>
     <row r="2346" spans="1:4">
       <c r="A2346" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2346" s="2">
-        <v>103116496</v>
+        <v>103110453</v>
       </c>
       <c r="C2346" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D2346" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2347" spans="1:4">
       <c r="A2347" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2347" s="2">
-        <v>103117188</v>
+        <v>103111713</v>
       </c>
       <c r="C2347" s="1" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D2347" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2348" spans="1:4">
       <c r="A2348" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2348" s="2">
-        <v>103119654</v>
+        <v>103111920</v>
       </c>
       <c r="C2348" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D2348" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2349" spans="1:4">
       <c r="A2349" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2349" s="2">
-        <v>103121097</v>
+        <v>103111956</v>
       </c>
       <c r="C2349" s="1" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D2349" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2350" spans="1:4">
       <c r="A2350" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2350" s="2">
-        <v>103121098</v>
+        <v>103113926</v>
       </c>
       <c r="C2350" s="1" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="D2350" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2351" spans="1:4">
       <c r="A2351" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2351" s="2">
-        <v>103124232</v>
+        <v>103115341</v>
       </c>
       <c r="C2351" s="1" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D2351" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2352" spans="1:4">
       <c r="A2352" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2352" s="2">
-        <v>103124248</v>
+        <v>103116487</v>
       </c>
       <c r="C2352" s="1" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="D2352" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2353" spans="1:4">
       <c r="A2353" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2353" s="2">
-        <v>103124249</v>
+        <v>103116496</v>
       </c>
       <c r="C2353" s="1" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D2353" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2354" spans="1:4">
       <c r="A2354" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2354" s="2">
-        <v>103124250</v>
+        <v>103117188</v>
       </c>
       <c r="C2354" s="1" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D2354" s="2">
         <v>20</v>
@@ -34455,13 +34476,13 @@
     </row>
     <row r="2355" spans="1:4">
       <c r="A2355" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2355" s="2">
-        <v>103124266</v>
+        <v>103119654</v>
       </c>
       <c r="C2355" s="1" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="D2355" s="2">
         <v>21</v>
@@ -34469,27 +34490,27 @@
     </row>
     <row r="2356" spans="1:4">
       <c r="A2356" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2356" s="2">
-        <v>103124268</v>
+        <v>103121097</v>
       </c>
       <c r="C2356" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="D2356" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2357" spans="1:4">
       <c r="A2357" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2357" s="2">
-        <v>103125208</v>
+        <v>103121098</v>
       </c>
       <c r="C2357" s="1" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D2357" s="2">
         <v>21</v>
@@ -34497,41 +34518,41 @@
     </row>
     <row r="2358" spans="1:4">
       <c r="A2358" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2358" s="2">
-        <v>103125228</v>
+        <v>103124232</v>
       </c>
       <c r="C2358" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="D2358" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2359" spans="1:4">
       <c r="A2359" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2359" s="2">
-        <v>103125229</v>
+        <v>103124248</v>
       </c>
       <c r="C2359" s="1" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D2359" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2360" spans="1:4">
       <c r="A2360" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2360" s="2">
-        <v>103126016</v>
+        <v>103124249</v>
       </c>
       <c r="C2360" s="1" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D2360" s="2">
         <v>21</v>
@@ -34539,461 +34560,461 @@
     </row>
     <row r="2361" spans="1:4">
       <c r="A2361" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2361" s="2">
-        <v>103127936</v>
+        <v>103124250</v>
       </c>
       <c r="C2361" s="1" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D2361" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2362" spans="1:4">
       <c r="A2362" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2362" s="2">
-        <v>103129049</v>
+        <v>103124266</v>
       </c>
       <c r="C2362" s="1" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D2362" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2363" spans="1:4">
       <c r="A2363" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2363" s="2">
-        <v>103129359</v>
+        <v>103124268</v>
       </c>
       <c r="C2363" s="1" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D2363" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2364" spans="1:4">
       <c r="A2364" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2364" s="2">
-        <v>103129371</v>
+        <v>103125208</v>
       </c>
       <c r="C2364" s="1" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D2364" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2365" spans="1:4">
       <c r="A2365" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2365" s="2">
-        <v>103129415</v>
+        <v>103125228</v>
       </c>
       <c r="C2365" s="1" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D2365" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2366" spans="1:4">
       <c r="A2366" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2366" s="2">
-        <v>103129416</v>
+        <v>103125229</v>
       </c>
       <c r="C2366" s="1" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D2366" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2367" spans="1:4">
       <c r="A2367" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2367" s="2">
-        <v>103130518</v>
+        <v>103126016</v>
       </c>
       <c r="C2367" s="1" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="D2367" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2368" spans="1:4">
       <c r="A2368" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2368" s="2">
-        <v>103130519</v>
+        <v>103127936</v>
       </c>
       <c r="C2368" s="1" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="D2368" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2369" spans="1:4">
       <c r="A2369" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2369" s="2">
-        <v>103132423</v>
+        <v>103129049</v>
       </c>
       <c r="C2369" s="1" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D2369" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2370" spans="1:4">
       <c r="A2370" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2370" s="2">
-        <v>103132424</v>
+        <v>103129359</v>
       </c>
       <c r="C2370" s="1" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D2370" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2371" spans="1:4">
       <c r="A2371" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2371" s="2">
-        <v>103132932</v>
+        <v>103129371</v>
       </c>
       <c r="C2371" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D2371" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2372" spans="1:4">
       <c r="A2372" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2372" s="2">
-        <v>103132933</v>
+        <v>103129415</v>
       </c>
       <c r="C2372" s="1" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D2372" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2373" spans="1:4">
       <c r="A2373" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2373" s="2">
-        <v>103132934</v>
+        <v>103129416</v>
       </c>
       <c r="C2373" s="1" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D2373" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2374" spans="1:4">
       <c r="A2374" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2374" s="2">
-        <v>103132938</v>
+        <v>103130518</v>
       </c>
       <c r="C2374" s="1" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D2374" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2375" spans="1:4">
       <c r="A2375" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2375" s="2">
-        <v>103133036</v>
+        <v>103130519</v>
       </c>
       <c r="C2375" s="1" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D2375" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2376" spans="1:4">
       <c r="A2376" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2376" s="2">
-        <v>103133037</v>
+        <v>103132423</v>
       </c>
       <c r="C2376" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D2376" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2377" spans="1:4">
       <c r="A2377" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2377" s="2">
-        <v>103133047</v>
+        <v>103132424</v>
       </c>
       <c r="C2377" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D2377" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2378" spans="1:4">
       <c r="A2378" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2378" s="2">
-        <v>103133765</v>
+        <v>103132932</v>
       </c>
       <c r="C2378" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D2378" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2379" spans="1:4">
       <c r="A2379" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2379" s="2">
-        <v>103133767</v>
+        <v>103132933</v>
       </c>
       <c r="C2379" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D2379" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2380" spans="1:4">
       <c r="A2380" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2380" s="2">
-        <v>103136099</v>
+        <v>103132934</v>
       </c>
       <c r="C2380" s="1" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D2380" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2381" spans="1:4">
       <c r="A2381" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2381" s="2">
-        <v>103136107</v>
+        <v>103132938</v>
       </c>
       <c r="C2381" s="1" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D2381" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2382" spans="1:4">
       <c r="A2382" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2382" s="2">
-        <v>103136108</v>
+        <v>103133036</v>
       </c>
       <c r="C2382" s="1" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D2382" s="2">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2383" spans="1:4">
       <c r="A2383" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2383" s="2">
-        <v>103137756</v>
+        <v>103133037</v>
       </c>
       <c r="C2383" s="1" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D2383" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2384" spans="1:4">
       <c r="A2384" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2384" s="2">
-        <v>103139871</v>
+        <v>103133047</v>
       </c>
       <c r="C2384" s="1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="D2384" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2385" spans="1:4">
       <c r="A2385" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2385" s="2">
-        <v>103142315</v>
+        <v>103133765</v>
       </c>
       <c r="C2385" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D2385" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2386" spans="1:4">
       <c r="A2386" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2386" s="2">
-        <v>103142316</v>
+        <v>103133767</v>
       </c>
       <c r="C2386" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D2386" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2387" spans="1:4">
       <c r="A2387" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2387" s="2">
-        <v>103145144</v>
+        <v>103136099</v>
       </c>
       <c r="C2387" s="1" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="D2387" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2388" spans="1:4">
       <c r="A2388" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2388" s="2">
-        <v>103145154</v>
+        <v>103136107</v>
       </c>
       <c r="C2388" s="1" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="D2388" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2389" spans="1:4">
       <c r="A2389" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2389" s="2">
-        <v>103145155</v>
+        <v>103136108</v>
       </c>
       <c r="C2389" s="1" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="D2389" s="2">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2390" spans="1:4">
       <c r="A2390" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2390" s="2">
-        <v>103145248</v>
+        <v>103137756</v>
       </c>
       <c r="C2390" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="D2390" s="2">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2391" spans="1:4">
       <c r="A2391" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2391" s="2">
-        <v>103146147</v>
+        <v>103139871</v>
       </c>
       <c r="C2391" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="D2391" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2392" spans="1:4">
       <c r="A2392" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2392" s="2">
-        <v>103169793</v>
+        <v>103142315</v>
       </c>
       <c r="C2392" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D2392" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2393" spans="1:4">
       <c r="A2393" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2393" s="2">
-        <v>103169795</v>
+        <v>103142316</v>
       </c>
       <c r="C2393" s="1" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D2393" s="2">
         <v>19</v>
@@ -35001,27 +35022,27 @@
     </row>
     <row r="2394" spans="1:4">
       <c r="A2394" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2394" s="2">
-        <v>103169797</v>
+        <v>103145144</v>
       </c>
       <c r="C2394" s="1" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="D2394" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2395" spans="1:4">
       <c r="A2395" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2395" s="2">
-        <v>103169814</v>
+        <v>103145154</v>
       </c>
       <c r="C2395" s="1" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="D2395" s="2">
         <v>20</v>
@@ -35029,69 +35050,69 @@
     </row>
     <row r="2396" spans="1:4">
       <c r="A2396" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2396" s="2">
-        <v>103169816</v>
+        <v>103145155</v>
       </c>
       <c r="C2396" s="1" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="D2396" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2397" spans="1:4">
       <c r="A2397" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2397" s="2">
-        <v>103169997</v>
+        <v>103145248</v>
       </c>
       <c r="C2397" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="D2397" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2398" spans="1:4">
       <c r="A2398" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2398" s="2">
-        <v>103170002</v>
+        <v>103146147</v>
       </c>
       <c r="C2398" s="1" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D2398" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2399" spans="1:4">
       <c r="A2399" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2399" s="2">
-        <v>103170019</v>
+        <v>103169793</v>
       </c>
       <c r="C2399" s="1" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="D2399" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2400" spans="1:4">
       <c r="A2400" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2400" s="2">
-        <v>103170021</v>
+        <v>103169795</v>
       </c>
       <c r="C2400" s="1" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D2400" s="2">
         <v>19</v>
@@ -35099,97 +35120,97 @@
     </row>
     <row r="2401" spans="1:4">
       <c r="A2401" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2401" s="2">
-        <v>103170024</v>
+        <v>103169797</v>
       </c>
       <c r="C2401" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D2401" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2402" spans="1:4">
       <c r="A2402" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2402" s="2">
-        <v>103170927</v>
+        <v>103169814</v>
       </c>
       <c r="C2402" s="1" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D2402" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2403" spans="1:4">
       <c r="A2403" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2403" s="2">
-        <v>103171002</v>
+        <v>103169816</v>
       </c>
       <c r="C2403" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D2403" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2404" spans="1:4">
       <c r="A2404" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2404" s="2">
-        <v>103171084</v>
+        <v>103169997</v>
       </c>
       <c r="C2404" s="1" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D2404" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2405" spans="1:4">
       <c r="A2405" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2405" s="2">
-        <v>103171103</v>
+        <v>103170002</v>
       </c>
       <c r="C2405" s="1" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D2405" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2406" spans="1:4">
       <c r="A2406" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2406" s="2">
-        <v>103173195</v>
+        <v>103170019</v>
       </c>
       <c r="C2406" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D2406" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2407" spans="1:4">
       <c r="A2407" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2407" s="2">
-        <v>103173197</v>
+        <v>103170021</v>
       </c>
       <c r="C2407" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D2407" s="2">
         <v>19</v>
@@ -35197,251 +35218,251 @@
     </row>
     <row r="2408" spans="1:4">
       <c r="A2408" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2408" s="2">
-        <v>103173208</v>
+        <v>103170024</v>
       </c>
       <c r="C2408" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D2408" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2409" spans="1:4">
       <c r="A2409" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2409" s="2">
-        <v>103173212</v>
+        <v>103170927</v>
       </c>
       <c r="C2409" s="1" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D2409" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2410" spans="1:4">
       <c r="A2410" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2410" s="2">
-        <v>103173218</v>
+        <v>103171002</v>
       </c>
       <c r="C2410" s="1" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D2410" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2411" spans="1:4">
       <c r="A2411" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2411" s="2">
-        <v>103283831</v>
+        <v>103171084</v>
       </c>
       <c r="C2411" s="1" t="s">
-        <v>352</v>
+        <v>272</v>
       </c>
       <c r="D2411" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2412" spans="1:4">
       <c r="A2412" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2412" s="2">
-        <v>103293732</v>
+        <v>103171103</v>
       </c>
       <c r="C2412" s="1" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="D2412" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2413" spans="1:4">
       <c r="A2413" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2413" s="2">
-        <v>103293737</v>
+        <v>103173195</v>
       </c>
       <c r="C2413" s="1" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="D2413" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2414" spans="1:4">
       <c r="A2414" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2414" s="2">
-        <v>103293745</v>
+        <v>103173197</v>
       </c>
       <c r="C2414" s="1" t="s">
-        <v>353</v>
+        <v>277</v>
       </c>
       <c r="D2414" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2415" spans="1:4">
       <c r="A2415" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2415" s="2">
-        <v>103293751</v>
+        <v>103173208</v>
       </c>
       <c r="C2415" s="1" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D2415" s="2">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2416" spans="1:4">
       <c r="A2416" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2416" s="2">
-        <v>103293756</v>
+        <v>103173212</v>
       </c>
       <c r="C2416" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D2416" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2417" spans="1:4">
       <c r="A2417" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2417" s="2">
-        <v>103293766</v>
+        <v>103173218</v>
       </c>
       <c r="C2417" s="1" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="D2417" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2418" spans="1:4">
       <c r="A2418" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2418" s="2">
-        <v>103293773</v>
+        <v>103283831</v>
       </c>
       <c r="C2418" s="1" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="D2418" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2419" spans="1:4">
       <c r="A2419" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2419" s="2">
-        <v>103294755</v>
+        <v>103293732</v>
       </c>
       <c r="C2419" s="1" t="s">
-        <v>150</v>
+        <v>286</v>
       </c>
       <c r="D2419" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2420" spans="1:4">
       <c r="A2420" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2420" s="2">
-        <v>103294767</v>
+        <v>103293737</v>
       </c>
       <c r="C2420" s="1" t="s">
-        <v>131</v>
+        <v>287</v>
       </c>
       <c r="D2420" s="2">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2421" spans="1:4">
       <c r="A2421" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2421" s="2">
-        <v>103296160</v>
+        <v>103293745</v>
       </c>
       <c r="C2421" s="1" t="s">
-        <v>292</v>
+        <v>353</v>
       </c>
       <c r="D2421" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2422" spans="1:4">
       <c r="A2422" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2422" s="2">
-        <v>103296167</v>
+        <v>103293751</v>
       </c>
       <c r="C2422" s="1" t="s">
-        <v>356</v>
+        <v>288</v>
       </c>
       <c r="D2422" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2423" spans="1:4">
       <c r="A2423" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2423" s="2">
-        <v>103297566</v>
+        <v>103293756</v>
       </c>
       <c r="C2423" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D2423" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2424" spans="1:4">
       <c r="A2424" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2424" s="2">
-        <v>103300418</v>
+        <v>103293766</v>
       </c>
       <c r="C2424" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D2424" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2425" spans="1:4">
       <c r="A2425" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2425" s="2">
-        <v>103304841</v>
+        <v>103293773</v>
       </c>
       <c r="C2425" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D2425" s="2">
         <v>22</v>
@@ -35449,127 +35470,225 @@
     </row>
     <row r="2426" spans="1:4">
       <c r="A2426" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2426" s="2">
-        <v>103304846</v>
+        <v>103294755</v>
       </c>
       <c r="C2426" s="1" t="s">
-        <v>359</v>
+        <v>150</v>
       </c>
       <c r="D2426" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2427" spans="1:4">
       <c r="A2427" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2427" s="2">
-        <v>103304863</v>
+        <v>103294767</v>
       </c>
       <c r="C2427" s="1" t="s">
-        <v>360</v>
+        <v>131</v>
       </c>
       <c r="D2427" s="2">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2428" spans="1:4">
       <c r="A2428" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2428" s="2">
-        <v>103304866</v>
+        <v>103296160</v>
       </c>
       <c r="C2428" s="1" t="s">
-        <v>130</v>
+        <v>292</v>
       </c>
       <c r="D2428" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2429" spans="1:4">
       <c r="A2429" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2429" s="2">
-        <v>103304868</v>
+        <v>103296167</v>
       </c>
       <c r="C2429" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D2429" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2430" spans="1:4">
       <c r="A2430" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2430" s="2">
-        <v>103304875</v>
+        <v>103297566</v>
       </c>
       <c r="C2430" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D2430" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2431" spans="1:4">
       <c r="A2431" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2431" s="2">
-        <v>103305150</v>
+        <v>103300418</v>
       </c>
       <c r="C2431" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D2431" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2432" spans="1:4">
       <c r="A2432" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2432" s="2">
-        <v>103305154</v>
+        <v>103304841</v>
       </c>
       <c r="C2432" s="1" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="D2432" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2433" spans="1:4">
       <c r="A2433" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2433" s="2">
-        <v>103305160</v>
+        <v>103304846</v>
       </c>
       <c r="C2433" s="1" t="s">
-        <v>298</v>
+        <v>359</v>
       </c>
       <c r="D2433" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2434" spans="1:4">
       <c r="A2434" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B2434" s="2">
+        <v>103304863</v>
+      </c>
+      <c r="C2434" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D2434" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:4">
+      <c r="A2435" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2435" s="2">
+        <v>103304866</v>
+      </c>
+      <c r="C2435" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2435" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:4">
+      <c r="A2436" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2436" s="2">
+        <v>103304868</v>
+      </c>
+      <c r="C2436" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D2436" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:4">
+      <c r="A2437" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2437" s="2">
+        <v>103304875</v>
+      </c>
+      <c r="C2437" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D2437" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:4">
+      <c r="A2438" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2438" s="2">
+        <v>103305150</v>
+      </c>
+      <c r="C2438" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D2438" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:4">
+      <c r="A2439" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2439" s="2">
+        <v>103305154</v>
+      </c>
+      <c r="C2439" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D2439" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:4">
+      <c r="A2440" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2440" s="2">
+        <v>103305160</v>
+      </c>
+      <c r="C2440" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D2440" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:4">
+      <c r="A2441" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2441" s="2">
         <v>103305165</v>
       </c>
-      <c r="C2434" s="1" t="s">
+      <c r="C2441" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D2434" s="2">
+      <c r="D2441" s="2">
         <v>20</v>
       </c>
     </row>
@@ -35830,13 +35949,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFC45AC5-9DDA-47B1-9511-201BEC9E1D82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD605EF-CAA2-4A4A-94E6-D41270E477BF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{742D6CC6-D2CB-4B6D-B25A-E1F8B1AFF5BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FDEA82D-3C2B-422C-B5C3-C5AF66DFE184}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{836DA267-2B96-407D-9940-7648BA7861F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2ED09EF-C117-4F2D-805B-F88628158D6C}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -6527,7 +6527,7 @@
         <v>287</v>
       </c>
       <c r="D358" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -27247,7 +27247,7 @@
         <v>7</v>
       </c>
       <c r="D1838" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1839" spans="1:4">
@@ -27331,7 +27331,7 @@
         <v>283</v>
       </c>
       <c r="D1844" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1845" spans="1:4">
@@ -27345,7 +27345,7 @@
         <v>48</v>
       </c>
       <c r="D1845" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1846" spans="1:4">
@@ -27373,7 +27373,7 @@
         <v>50</v>
       </c>
       <c r="D1847" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1848" spans="1:4">
@@ -27387,7 +27387,7 @@
         <v>51</v>
       </c>
       <c r="D1848" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1849" spans="1:4">
@@ -27401,7 +27401,7 @@
         <v>54</v>
       </c>
       <c r="D1849" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1850" spans="1:4">
@@ -27429,7 +27429,7 @@
         <v>56</v>
       </c>
       <c r="D1851" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1852" spans="1:4">
@@ -27443,7 +27443,7 @@
         <v>72</v>
       </c>
       <c r="D1852" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1853" spans="1:4">
@@ -27457,7 +27457,7 @@
         <v>77</v>
       </c>
       <c r="D1853" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1854" spans="1:4">
@@ -27485,7 +27485,7 @@
         <v>88</v>
       </c>
       <c r="D1855" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1856" spans="1:4">
@@ -27499,7 +27499,7 @@
         <v>92</v>
       </c>
       <c r="D1856" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1857" spans="1:4">
@@ -27513,7 +27513,7 @@
         <v>96</v>
       </c>
       <c r="D1857" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1858" spans="1:4">
@@ -27555,7 +27555,7 @@
         <v>104</v>
       </c>
       <c r="D1860" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1861" spans="1:4">
@@ -27569,7 +27569,7 @@
         <v>107</v>
       </c>
       <c r="D1861" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1862" spans="1:4">
@@ -27625,7 +27625,7 @@
         <v>123</v>
       </c>
       <c r="D1865" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1866" spans="1:4">
@@ -27639,7 +27639,7 @@
         <v>125</v>
       </c>
       <c r="D1866" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1867" spans="1:4">
@@ -27653,7 +27653,7 @@
         <v>126</v>
       </c>
       <c r="D1867" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1868" spans="1:4">
@@ -27667,7 +27667,7 @@
         <v>128</v>
       </c>
       <c r="D1868" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1869" spans="1:4">
@@ -27709,7 +27709,7 @@
         <v>136</v>
       </c>
       <c r="D1871" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1872" spans="1:4">
@@ -27723,7 +27723,7 @@
         <v>139</v>
       </c>
       <c r="D1872" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1873" spans="1:4">
@@ -27737,7 +27737,7 @@
         <v>145</v>
       </c>
       <c r="D1873" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1874" spans="1:4">
@@ -27779,7 +27779,7 @@
         <v>154</v>
       </c>
       <c r="D1876" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1877" spans="1:4">
@@ -27793,7 +27793,7 @@
         <v>159</v>
       </c>
       <c r="D1877" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1878" spans="1:4">
@@ -27821,7 +27821,7 @@
         <v>162</v>
       </c>
       <c r="D1879" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1880" spans="1:4">
@@ -27849,7 +27849,7 @@
         <v>170</v>
       </c>
       <c r="D1881" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1882" spans="1:4">
@@ -27919,7 +27919,7 @@
         <v>175</v>
       </c>
       <c r="D1886" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1887" spans="1:4">
@@ -27961,7 +27961,7 @@
         <v>183</v>
       </c>
       <c r="D1889" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1890" spans="1:4">
@@ -27975,7 +27975,7 @@
         <v>186</v>
       </c>
       <c r="D1890" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1891" spans="1:4">
@@ -28017,7 +28017,7 @@
         <v>194</v>
       </c>
       <c r="D1893" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1894" spans="1:4">
@@ -28031,7 +28031,7 @@
         <v>206</v>
       </c>
       <c r="D1894" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1895" spans="1:4">
@@ -28045,7 +28045,7 @@
         <v>208</v>
       </c>
       <c r="D1895" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1896" spans="1:4">
@@ -28087,7 +28087,7 @@
         <v>229</v>
       </c>
       <c r="D1898" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1899" spans="1:4">
@@ -28101,7 +28101,7 @@
         <v>230</v>
       </c>
       <c r="D1899" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1900" spans="1:4">
@@ -28115,7 +28115,7 @@
         <v>235</v>
       </c>
       <c r="D1900" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1901" spans="1:4">
@@ -28129,7 +28129,7 @@
         <v>246</v>
       </c>
       <c r="D1901" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1902" spans="1:4">
@@ -28143,7 +28143,7 @@
         <v>259</v>
       </c>
       <c r="D1902" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1903" spans="1:4">
@@ -28157,7 +28157,7 @@
         <v>260</v>
       </c>
       <c r="D1903" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1904" spans="1:4">
@@ -28171,7 +28171,7 @@
         <v>262</v>
       </c>
       <c r="D1904" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1905" spans="1:4">
@@ -28185,7 +28185,7 @@
         <v>263</v>
       </c>
       <c r="D1905" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1906" spans="1:4">
@@ -28199,7 +28199,7 @@
         <v>273</v>
       </c>
       <c r="D1906" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1907" spans="1:4">
@@ -28213,7 +28213,7 @@
         <v>276</v>
       </c>
       <c r="D1907" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1908" spans="1:4">
@@ -28227,7 +28227,7 @@
         <v>277</v>
       </c>
       <c r="D1908" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1909" spans="1:4">
@@ -28269,7 +28269,7 @@
         <v>287</v>
       </c>
       <c r="D1911" s="2">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1912" spans="1:4">
@@ -28283,7 +28283,7 @@
         <v>288</v>
       </c>
       <c r="D1912" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1913" spans="1:4">
@@ -28367,7 +28367,7 @@
         <v>293</v>
       </c>
       <c r="D1918" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1919" spans="1:4">
@@ -28395,7 +28395,7 @@
         <v>130</v>
       </c>
       <c r="D1920" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1921" spans="1:4">
@@ -28409,7 +28409,7 @@
         <v>295</v>
       </c>
       <c r="D1921" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1922" spans="1:4">
@@ -28423,7 +28423,7 @@
         <v>296</v>
       </c>
       <c r="D1922" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1923" spans="1:4">
@@ -28451,7 +28451,7 @@
         <v>301</v>
       </c>
       <c r="D1924" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1925" spans="1:4">
@@ -28465,7 +28465,7 @@
         <v>302</v>
       </c>
       <c r="D1925" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1926" spans="1:4">
@@ -28479,7 +28479,7 @@
         <v>303</v>
       </c>
       <c r="D1926" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1927" spans="1:4">
@@ -28493,7 +28493,7 @@
         <v>304</v>
       </c>
       <c r="D1927" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1928" spans="1:4">
@@ -28507,7 +28507,7 @@
         <v>305</v>
       </c>
       <c r="D1928" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1929" spans="1:4">
@@ -28521,7 +28521,7 @@
         <v>306</v>
       </c>
       <c r="D1929" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1930" spans="1:4">
@@ -28535,7 +28535,7 @@
         <v>307</v>
       </c>
       <c r="D1930" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1931" spans="1:4">
@@ -28549,7 +28549,7 @@
         <v>308</v>
       </c>
       <c r="D1931" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1932" spans="1:4">
@@ -28563,7 +28563,7 @@
         <v>309</v>
       </c>
       <c r="D1932" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1933" spans="1:4">
@@ -28577,7 +28577,7 @@
         <v>310</v>
       </c>
       <c r="D1933" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1934" spans="1:4">
@@ -28591,7 +28591,7 @@
         <v>312</v>
       </c>
       <c r="D1934" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1935" spans="1:4">
@@ -28633,7 +28633,7 @@
         <v>315</v>
       </c>
       <c r="D1937" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1938" spans="1:4">
@@ -28647,7 +28647,7 @@
         <v>316</v>
       </c>
       <c r="D1938" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1939" spans="1:4">
@@ -28661,7 +28661,7 @@
         <v>317</v>
       </c>
       <c r="D1939" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1940" spans="1:4">
@@ -28731,7 +28731,7 @@
         <v>322</v>
       </c>
       <c r="D1944" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1945" spans="1:4">
@@ -28745,7 +28745,7 @@
         <v>323</v>
       </c>
       <c r="D1945" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1946" spans="1:4">
@@ -28759,7 +28759,7 @@
         <v>324</v>
       </c>
       <c r="D1946" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1947" spans="1:4">
@@ -28773,7 +28773,7 @@
         <v>325</v>
       </c>
       <c r="D1947" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1948" spans="1:4">
@@ -28787,7 +28787,7 @@
         <v>326</v>
       </c>
       <c r="D1948" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1949" spans="1:4">
@@ -28801,7 +28801,7 @@
         <v>327</v>
       </c>
       <c r="D1949" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1950" spans="1:4">
@@ -28815,7 +28815,7 @@
         <v>328</v>
       </c>
       <c r="D1950" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1951" spans="1:4">
@@ -28829,7 +28829,7 @@
         <v>329</v>
       </c>
       <c r="D1951" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1952" spans="1:4">
@@ -28843,7 +28843,7 @@
         <v>330</v>
       </c>
       <c r="D1952" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1953" spans="1:4">
@@ -28857,7 +28857,7 @@
         <v>332</v>
       </c>
       <c r="D1953" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1954" spans="1:4">
@@ -28885,7 +28885,7 @@
         <v>334</v>
       </c>
       <c r="D1955" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1956" spans="1:4">
@@ -28899,7 +28899,7 @@
         <v>335</v>
       </c>
       <c r="D1956" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1957" spans="1:4">
@@ -28913,7 +28913,7 @@
         <v>336</v>
       </c>
       <c r="D1957" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1958" spans="1:4">
@@ -28927,7 +28927,7 @@
         <v>337</v>
       </c>
       <c r="D1958" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1959" spans="1:4">
@@ -28941,7 +28941,7 @@
         <v>339</v>
       </c>
       <c r="D1959" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1960" spans="1:4">
@@ -28955,7 +28955,7 @@
         <v>340</v>
       </c>
       <c r="D1960" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1961" spans="1:4">
@@ -28969,7 +28969,7 @@
         <v>341</v>
       </c>
       <c r="D1961" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1962" spans="1:4">
@@ -28983,7 +28983,7 @@
         <v>342</v>
       </c>
       <c r="D1962" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1963" spans="1:4">
@@ -28997,7 +28997,7 @@
         <v>343</v>
       </c>
       <c r="D1963" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1964" spans="1:4">
@@ -29011,7 +29011,7 @@
         <v>344</v>
       </c>
       <c r="D1964" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1965" spans="1:4">
@@ -29025,7 +29025,7 @@
         <v>345</v>
       </c>
       <c r="D1965" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1966" spans="1:4">
@@ -29039,7 +29039,7 @@
         <v>346</v>
       </c>
       <c r="D1966" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1967" spans="1:4">
@@ -29053,7 +29053,7 @@
         <v>347</v>
       </c>
       <c r="D1967" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1968" spans="1:4">
@@ -29067,7 +29067,7 @@
         <v>348</v>
       </c>
       <c r="D1968" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1969" spans="1:4">
@@ -29081,7 +29081,7 @@
         <v>349</v>
       </c>
       <c r="D1969" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1970" spans="1:4">
@@ -29095,7 +29095,7 @@
         <v>350</v>
       </c>
       <c r="D1970" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1971" spans="1:4">
@@ -29109,7 +29109,7 @@
         <v>371</v>
       </c>
       <c r="D1971" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1972" spans="1:4">
@@ -29123,7 +29123,7 @@
         <v>372</v>
       </c>
       <c r="D1972" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1973" spans="1:4">
@@ -29137,7 +29137,7 @@
         <v>373</v>
       </c>
       <c r="D1973" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1974" spans="1:4">
@@ -29151,7 +29151,7 @@
         <v>374</v>
       </c>
       <c r="D1974" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1975" spans="1:4">
@@ -29165,7 +29165,7 @@
         <v>375</v>
       </c>
       <c r="D1975" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1976" spans="1:4">
@@ -29179,7 +29179,7 @@
         <v>376</v>
       </c>
       <c r="D1976" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1977" spans="1:4">
@@ -29193,7 +29193,7 @@
         <v>377</v>
       </c>
       <c r="D1977" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1978" spans="1:4">
@@ -35949,13 +35949,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD605EF-CAA2-4A4A-94E6-D41270E477BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97541B61-6F30-4001-AC77-F82C1683B312}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FDEA82D-3C2B-422C-B5C3-C5AF66DFE184}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CFFF59-244F-4FD2-99C2-0CF68F91D291}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2ED09EF-C117-4F2D-805B-F88628158D6C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D39B66AE-D2DE-4611-B6A5-1ED6932DB57E}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -27233,7 +27233,7 @@
         <v>6</v>
       </c>
       <c r="D1837" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1838" spans="1:4">
@@ -27289,7 +27289,7 @@
         <v>25</v>
       </c>
       <c r="D1841" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1842" spans="1:4">
@@ -27317,7 +27317,7 @@
         <v>29</v>
       </c>
       <c r="D1843" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1844" spans="1:4">
@@ -27359,7 +27359,7 @@
         <v>49</v>
       </c>
       <c r="D1846" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1847" spans="1:4">
@@ -27401,7 +27401,7 @@
         <v>54</v>
       </c>
       <c r="D1849" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1850" spans="1:4">
@@ -27415,7 +27415,7 @@
         <v>55</v>
       </c>
       <c r="D1850" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1851" spans="1:4">
@@ -27429,7 +27429,7 @@
         <v>56</v>
       </c>
       <c r="D1851" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1852" spans="1:4">
@@ -27443,7 +27443,7 @@
         <v>72</v>
       </c>
       <c r="D1852" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1853" spans="1:4">
@@ -27471,7 +27471,7 @@
         <v>85</v>
       </c>
       <c r="D1854" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1855" spans="1:4">
@@ -27527,7 +27527,7 @@
         <v>102</v>
       </c>
       <c r="D1858" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1859" spans="1:4">
@@ -27569,7 +27569,7 @@
         <v>107</v>
       </c>
       <c r="D1861" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1862" spans="1:4">
@@ -27695,7 +27695,7 @@
         <v>135</v>
       </c>
       <c r="D1870" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1871" spans="1:4">
@@ -27709,7 +27709,7 @@
         <v>136</v>
       </c>
       <c r="D1871" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1872" spans="1:4">
@@ -27737,7 +27737,7 @@
         <v>145</v>
       </c>
       <c r="D1873" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1874" spans="1:4">
@@ -27751,7 +27751,7 @@
         <v>148</v>
       </c>
       <c r="D1874" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1875" spans="1:4">
@@ -27765,7 +27765,7 @@
         <v>151</v>
       </c>
       <c r="D1875" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1876" spans="1:4">
@@ -27779,7 +27779,7 @@
         <v>154</v>
       </c>
       <c r="D1876" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1877" spans="1:4">
@@ -27807,7 +27807,7 @@
         <v>160</v>
       </c>
       <c r="D1878" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1879" spans="1:4">
@@ -27835,7 +27835,7 @@
         <v>166</v>
       </c>
       <c r="D1880" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1881" spans="1:4">
@@ -27863,7 +27863,7 @@
         <v>171</v>
       </c>
       <c r="D1882" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1883" spans="1:4">
@@ -27877,7 +27877,7 @@
         <v>172</v>
       </c>
       <c r="D1883" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1884" spans="1:4">
@@ -27891,7 +27891,7 @@
         <v>173</v>
       </c>
       <c r="D1884" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1885" spans="1:4">
@@ -27905,7 +27905,7 @@
         <v>174</v>
       </c>
       <c r="D1885" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1886" spans="1:4">
@@ -27933,7 +27933,7 @@
         <v>177</v>
       </c>
       <c r="D1887" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1888" spans="1:4">
@@ -27947,7 +27947,7 @@
         <v>182</v>
       </c>
       <c r="D1888" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1889" spans="1:4">
@@ -27989,7 +27989,7 @@
         <v>189</v>
       </c>
       <c r="D1891" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1892" spans="1:4">
@@ -28017,7 +28017,7 @@
         <v>194</v>
       </c>
       <c r="D1893" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1894" spans="1:4">
@@ -28073,7 +28073,7 @@
         <v>226</v>
       </c>
       <c r="D1897" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1898" spans="1:4">
@@ -28143,7 +28143,7 @@
         <v>259</v>
       </c>
       <c r="D1902" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1903" spans="1:4">
@@ -28241,7 +28241,7 @@
         <v>285</v>
       </c>
       <c r="D1909" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1910" spans="1:4">
@@ -28255,7 +28255,7 @@
         <v>286</v>
       </c>
       <c r="D1910" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1911" spans="1:4">
@@ -28297,7 +28297,7 @@
         <v>289</v>
       </c>
       <c r="D1913" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1914" spans="1:4">
@@ -28311,7 +28311,7 @@
         <v>290</v>
       </c>
       <c r="D1914" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1915" spans="1:4">
@@ -28325,7 +28325,7 @@
         <v>291</v>
       </c>
       <c r="D1915" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1916" spans="1:4">
@@ -28353,7 +28353,7 @@
         <v>292</v>
       </c>
       <c r="D1917" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1918" spans="1:4">
@@ -28381,7 +28381,7 @@
         <v>294</v>
       </c>
       <c r="D1919" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1920" spans="1:4">
@@ -28451,7 +28451,7 @@
         <v>301</v>
       </c>
       <c r="D1924" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1925" spans="1:4">
@@ -28535,7 +28535,7 @@
         <v>307</v>
       </c>
       <c r="D1930" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1931" spans="1:4">
@@ -28549,7 +28549,7 @@
         <v>308</v>
       </c>
       <c r="D1931" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1932" spans="1:4">
@@ -28563,7 +28563,7 @@
         <v>309</v>
       </c>
       <c r="D1932" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1933" spans="1:4">
@@ -28591,7 +28591,7 @@
         <v>312</v>
       </c>
       <c r="D1934" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1935" spans="1:4">
@@ -28619,7 +28619,7 @@
         <v>314</v>
       </c>
       <c r="D1936" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1937" spans="1:4">
@@ -28633,7 +28633,7 @@
         <v>315</v>
       </c>
       <c r="D1937" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1938" spans="1:4">
@@ -28647,7 +28647,7 @@
         <v>316</v>
       </c>
       <c r="D1938" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1939" spans="1:4">
@@ -28661,7 +28661,7 @@
         <v>317</v>
       </c>
       <c r="D1939" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1940" spans="1:4">
@@ -35949,13 +35949,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97541B61-6F30-4001-AC77-F82C1683B312}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F5A3788-06F6-4B1F-973E-040CE9BA0B42}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CFFF59-244F-4FD2-99C2-0CF68F91D291}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D7EA24D-E725-47B4-B940-19CD6D70FB94}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D39B66AE-D2DE-4611-B6A5-1ED6932DB57E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8241E3A-AAD4-49E3-99E5-6E88A8768D1D}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -41219,13 +41219,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60FE52C4-01AE-42AC-9CEC-C5DD782D1ED0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B1C0E58-2A3B-4490-BA8A-00FC08EBDA94}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1440D819-3B94-4E37-B1FB-6A27AD962283}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7BE1F8-143B-41F1-BF8B-921EAFA83910}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B4EA013-C467-4117-B3F6-4178EA5C0A2D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62EA2766-88EF-49C2-BEE4-A1B36C5B3C2E}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -41219,13 +41219,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B1C0E58-2A3B-4490-BA8A-00FC08EBDA94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0FDBC58-BA65-44DB-B9A2-75D6A32B408E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E7BE1F8-143B-41F1-BF8B-921EAFA83910}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55009C6-C44E-453B-A951-8A4EA218B1AA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62EA2766-88EF-49C2-BEE4-A1B36C5B3C2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{785C95CE-2589-40B5-B65E-22021F947729}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -18797,7 +18797,7 @@
         <v>6</v>
       </c>
       <c r="D1225" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1226" spans="1:4">
@@ -18811,7 +18811,7 @@
         <v>7</v>
       </c>
       <c r="D1226" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1227" spans="1:4">
@@ -18825,7 +18825,7 @@
         <v>19</v>
       </c>
       <c r="D1227" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1228" spans="1:4">
@@ -18839,7 +18839,7 @@
         <v>22</v>
       </c>
       <c r="D1228" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1229" spans="1:4">
@@ -18853,7 +18853,7 @@
         <v>25</v>
       </c>
       <c r="D1229" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1230" spans="1:4">
@@ -18867,7 +18867,7 @@
         <v>28</v>
       </c>
       <c r="D1230" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1231" spans="1:4">
@@ -18881,7 +18881,7 @@
         <v>283</v>
       </c>
       <c r="D1231" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1232" spans="1:4">
@@ -18895,7 +18895,7 @@
         <v>48</v>
       </c>
       <c r="D1232" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1233" spans="1:4">
@@ -18909,7 +18909,7 @@
         <v>49</v>
       </c>
       <c r="D1233" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1234" spans="1:4">
@@ -18923,7 +18923,7 @@
         <v>50</v>
       </c>
       <c r="D1234" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1235" spans="1:4">
@@ -18937,7 +18937,7 @@
         <v>51</v>
       </c>
       <c r="D1235" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1236" spans="1:4">
@@ -18951,7 +18951,7 @@
         <v>54</v>
       </c>
       <c r="D1236" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1237" spans="1:4">
@@ -18965,7 +18965,7 @@
         <v>55</v>
       </c>
       <c r="D1237" s="2">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1238" spans="1:4">
@@ -18979,7 +18979,7 @@
         <v>56</v>
       </c>
       <c r="D1238" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1239" spans="1:4">
@@ -18993,7 +18993,7 @@
         <v>72</v>
       </c>
       <c r="D1239" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1240" spans="1:4">
@@ -19007,7 +19007,7 @@
         <v>77</v>
       </c>
       <c r="D1240" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1241" spans="1:4">
@@ -19021,7 +19021,7 @@
         <v>85</v>
       </c>
       <c r="D1241" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1242" spans="1:4">
@@ -19035,7 +19035,7 @@
         <v>88</v>
       </c>
       <c r="D1242" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1243" spans="1:4">
@@ -19049,7 +19049,7 @@
         <v>92</v>
       </c>
       <c r="D1243" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1244" spans="1:4">
@@ -19077,7 +19077,7 @@
         <v>102</v>
       </c>
       <c r="D1245" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1246" spans="1:4">
@@ -19091,7 +19091,7 @@
         <v>103</v>
       </c>
       <c r="D1246" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1247" spans="1:4">
@@ -19119,7 +19119,7 @@
         <v>107</v>
       </c>
       <c r="D1248" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1249" spans="1:4">
@@ -19147,7 +19147,7 @@
         <v>284</v>
       </c>
       <c r="D1250" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1251" spans="1:4">
@@ -19161,7 +19161,7 @@
         <v>122</v>
       </c>
       <c r="D1251" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1252" spans="1:4">
@@ -19175,7 +19175,7 @@
         <v>123</v>
       </c>
       <c r="D1252" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1253" spans="1:4">
@@ -19189,7 +19189,7 @@
         <v>125</v>
       </c>
       <c r="D1253" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1254" spans="1:4">
@@ -19203,7 +19203,7 @@
         <v>126</v>
       </c>
       <c r="D1254" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1255" spans="1:4">
@@ -19217,7 +19217,7 @@
         <v>128</v>
       </c>
       <c r="D1255" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1256" spans="1:4">
@@ -19231,7 +19231,7 @@
         <v>129</v>
       </c>
       <c r="D1256" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1257" spans="1:4">
@@ -19245,7 +19245,7 @@
         <v>135</v>
       </c>
       <c r="D1257" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1258" spans="1:4">
@@ -19259,7 +19259,7 @@
         <v>139</v>
       </c>
       <c r="D1258" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1259" spans="1:4">
@@ -19273,7 +19273,7 @@
         <v>145</v>
       </c>
       <c r="D1259" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1260" spans="1:4">
@@ -19287,7 +19287,7 @@
         <v>148</v>
       </c>
       <c r="D1260" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1261" spans="1:4">
@@ -19301,7 +19301,7 @@
         <v>151</v>
       </c>
       <c r="D1261" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1262" spans="1:4">
@@ -19315,7 +19315,7 @@
         <v>154</v>
       </c>
       <c r="D1262" s="2">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1263" spans="1:4">
@@ -19329,7 +19329,7 @@
         <v>159</v>
       </c>
       <c r="D1263" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1264" spans="1:4">
@@ -19343,7 +19343,7 @@
         <v>160</v>
       </c>
       <c r="D1264" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1265" spans="1:4">
@@ -19357,7 +19357,7 @@
         <v>162</v>
       </c>
       <c r="D1265" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1266" spans="1:4">
@@ -19371,7 +19371,7 @@
         <v>166</v>
       </c>
       <c r="D1266" s="2">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1267" spans="1:4">
@@ -19385,7 +19385,7 @@
         <v>170</v>
       </c>
       <c r="D1267" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1268" spans="1:4">
@@ -19399,7 +19399,7 @@
         <v>171</v>
       </c>
       <c r="D1268" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1269" spans="1:4">
@@ -19413,7 +19413,7 @@
         <v>172</v>
       </c>
       <c r="D1269" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1270" spans="1:4">
@@ -19427,7 +19427,7 @@
         <v>173</v>
       </c>
       <c r="D1270" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1271" spans="1:4">
@@ -19441,7 +19441,7 @@
         <v>174</v>
       </c>
       <c r="D1271" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1272" spans="1:4">
@@ -19455,7 +19455,7 @@
         <v>175</v>
       </c>
       <c r="D1272" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1273" spans="1:4">
@@ -19469,7 +19469,7 @@
         <v>177</v>
       </c>
       <c r="D1273" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1274" spans="1:4">
@@ -19483,7 +19483,7 @@
         <v>182</v>
       </c>
       <c r="D1274" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1275" spans="1:4">
@@ -19497,7 +19497,7 @@
         <v>183</v>
       </c>
       <c r="D1275" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1276" spans="1:4">
@@ -19511,7 +19511,7 @@
         <v>186</v>
       </c>
       <c r="D1276" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1277" spans="1:4">
@@ -19525,7 +19525,7 @@
         <v>189</v>
       </c>
       <c r="D1277" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1278" spans="1:4">
@@ -19539,7 +19539,7 @@
         <v>194</v>
       </c>
       <c r="D1278" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1279" spans="1:4">
@@ -19553,7 +19553,7 @@
         <v>206</v>
       </c>
       <c r="D1279" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1280" spans="1:4">
@@ -19567,7 +19567,7 @@
         <v>208</v>
       </c>
       <c r="D1280" s="2">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1281" spans="1:4">
@@ -19581,7 +19581,7 @@
         <v>209</v>
       </c>
       <c r="D1281" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1282" spans="1:4">
@@ -19595,7 +19595,7 @@
         <v>226</v>
       </c>
       <c r="D1282" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1283" spans="1:4">
@@ -19609,7 +19609,7 @@
         <v>229</v>
       </c>
       <c r="D1283" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1284" spans="1:4">
@@ -19623,7 +19623,7 @@
         <v>230</v>
       </c>
       <c r="D1284" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1285" spans="1:4">
@@ -19637,7 +19637,7 @@
         <v>235</v>
       </c>
       <c r="D1285" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1286" spans="1:4">
@@ -19651,7 +19651,7 @@
         <v>246</v>
       </c>
       <c r="D1286" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1287" spans="1:4">
@@ -19665,7 +19665,7 @@
         <v>259</v>
       </c>
       <c r="D1287" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1288" spans="1:4">
@@ -19693,7 +19693,7 @@
         <v>262</v>
       </c>
       <c r="D1289" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1290" spans="1:4">
@@ -19707,7 +19707,7 @@
         <v>263</v>
       </c>
       <c r="D1290" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1291" spans="1:4">
@@ -19721,7 +19721,7 @@
         <v>273</v>
       </c>
       <c r="D1291" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1292" spans="1:4">
@@ -19735,7 +19735,7 @@
         <v>276</v>
       </c>
       <c r="D1292" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1293" spans="1:4">
@@ -19749,7 +19749,7 @@
         <v>277</v>
       </c>
       <c r="D1293" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1294" spans="1:4">
@@ -19763,7 +19763,7 @@
         <v>285</v>
       </c>
       <c r="D1294" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1295" spans="1:4">
@@ -19777,7 +19777,7 @@
         <v>286</v>
       </c>
       <c r="D1295" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1296" spans="1:4">
@@ -19791,7 +19791,7 @@
         <v>288</v>
       </c>
       <c r="D1296" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1297" spans="1:4">
@@ -19805,7 +19805,7 @@
         <v>289</v>
       </c>
       <c r="D1297" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1298" spans="1:4">
@@ -19819,7 +19819,7 @@
         <v>290</v>
       </c>
       <c r="D1298" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1299" spans="1:4">
@@ -19833,7 +19833,7 @@
         <v>291</v>
       </c>
       <c r="D1299" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1300" spans="1:4">
@@ -19847,7 +19847,7 @@
         <v>150</v>
       </c>
       <c r="D1300" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1301" spans="1:4">
@@ -19861,7 +19861,7 @@
         <v>292</v>
       </c>
       <c r="D1301" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1302" spans="1:4">
@@ -19875,7 +19875,7 @@
         <v>293</v>
       </c>
       <c r="D1302" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1303" spans="1:4">
@@ -19889,7 +19889,7 @@
         <v>294</v>
       </c>
       <c r="D1303" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1304" spans="1:4">
@@ -19903,7 +19903,7 @@
         <v>130</v>
       </c>
       <c r="D1304" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1305" spans="1:4">
@@ -19917,7 +19917,7 @@
         <v>295</v>
       </c>
       <c r="D1305" s="2">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1306" spans="1:4">
@@ -19931,7 +19931,7 @@
         <v>296</v>
       </c>
       <c r="D1306" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1307" spans="1:4">
@@ -19945,7 +19945,7 @@
         <v>301</v>
       </c>
       <c r="D1307" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1308" spans="1:4">
@@ -19959,7 +19959,7 @@
         <v>302</v>
       </c>
       <c r="D1308" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1309" spans="1:4">
@@ -19973,7 +19973,7 @@
         <v>303</v>
       </c>
       <c r="D1309" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1310" spans="1:4">
@@ -19987,7 +19987,7 @@
         <v>304</v>
       </c>
       <c r="D1310" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1311" spans="1:4">
@@ -20001,7 +20001,7 @@
         <v>305</v>
       </c>
       <c r="D1311" s="2">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1312" spans="1:4">
@@ -20015,7 +20015,7 @@
         <v>306</v>
       </c>
       <c r="D1312" s="2">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1313" spans="1:4">
@@ -20029,7 +20029,7 @@
         <v>307</v>
       </c>
       <c r="D1313" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1314" spans="1:4">
@@ -20043,7 +20043,7 @@
         <v>308</v>
       </c>
       <c r="D1314" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1315" spans="1:4">
@@ -20057,7 +20057,7 @@
         <v>309</v>
       </c>
       <c r="D1315" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1316" spans="1:4">
@@ -20071,7 +20071,7 @@
         <v>310</v>
       </c>
       <c r="D1316" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1317" spans="1:4">
@@ -20085,7 +20085,7 @@
         <v>312</v>
       </c>
       <c r="D1317" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1318" spans="1:4">
@@ -20099,7 +20099,7 @@
         <v>313</v>
       </c>
       <c r="D1318" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1319" spans="1:4">
@@ -20113,7 +20113,7 @@
         <v>314</v>
       </c>
       <c r="D1319" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1320" spans="1:4">
@@ -20127,7 +20127,7 @@
         <v>315</v>
       </c>
       <c r="D1320" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1321" spans="1:4">
@@ -20141,7 +20141,7 @@
         <v>316</v>
       </c>
       <c r="D1321" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1322" spans="1:4">
@@ -20155,7 +20155,7 @@
         <v>317</v>
       </c>
       <c r="D1322" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1323" spans="1:4">
@@ -20169,7 +20169,7 @@
         <v>318</v>
       </c>
       <c r="D1323" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1324" spans="1:4">
@@ -20183,7 +20183,7 @@
         <v>319</v>
       </c>
       <c r="D1324" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1325" spans="1:4">
@@ -20211,7 +20211,7 @@
         <v>321</v>
       </c>
       <c r="D1326" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1327" spans="1:4">
@@ -20225,7 +20225,7 @@
         <v>323</v>
       </c>
       <c r="D1327" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1328" spans="1:4">
@@ -20239,7 +20239,7 @@
         <v>324</v>
       </c>
       <c r="D1328" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1329" spans="1:4">
@@ -20253,7 +20253,7 @@
         <v>325</v>
       </c>
       <c r="D1329" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1330" spans="1:4">
@@ -20267,7 +20267,7 @@
         <v>326</v>
       </c>
       <c r="D1330" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1331" spans="1:4">
@@ -20281,7 +20281,7 @@
         <v>328</v>
       </c>
       <c r="D1331" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1332" spans="1:4">
@@ -20295,7 +20295,7 @@
         <v>330</v>
       </c>
       <c r="D1332" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1333" spans="1:4">
@@ -20309,7 +20309,7 @@
         <v>332</v>
       </c>
       <c r="D1333" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1334" spans="1:4">
@@ -20323,7 +20323,7 @@
         <v>334</v>
       </c>
       <c r="D1334" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1335" spans="1:4">
@@ -20337,7 +20337,7 @@
         <v>335</v>
       </c>
       <c r="D1335" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1336" spans="1:4">
@@ -20351,7 +20351,7 @@
         <v>337</v>
       </c>
       <c r="D1336" s="2">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1337" spans="1:4">
@@ -20365,7 +20365,7 @@
         <v>339</v>
       </c>
       <c r="D1337" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1338" spans="1:4">
@@ -20379,7 +20379,7 @@
         <v>340</v>
       </c>
       <c r="D1338" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1339" spans="1:4">
@@ -20393,7 +20393,7 @@
         <v>341</v>
       </c>
       <c r="D1339" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1340" spans="1:4">
@@ -20407,7 +20407,7 @@
         <v>342</v>
       </c>
       <c r="D1340" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1341" spans="1:4">
@@ -20421,7 +20421,7 @@
         <v>343</v>
       </c>
       <c r="D1341" s="2">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1342" spans="1:4">
@@ -20435,7 +20435,7 @@
         <v>344</v>
       </c>
       <c r="D1342" s="2">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1343" spans="1:4">
@@ -20449,7 +20449,7 @@
         <v>346</v>
       </c>
       <c r="D1343" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1344" spans="1:4">
@@ -20463,7 +20463,7 @@
         <v>347</v>
       </c>
       <c r="D1344" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1345" spans="1:4">
@@ -20477,7 +20477,7 @@
         <v>348</v>
       </c>
       <c r="D1345" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1346" spans="1:4">
@@ -20491,7 +20491,7 @@
         <v>349</v>
       </c>
       <c r="D1346" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1347" spans="1:4">
@@ -20505,7 +20505,7 @@
         <v>350</v>
       </c>
       <c r="D1347" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1348" spans="1:4">
@@ -20519,7 +20519,7 @@
         <v>368</v>
       </c>
       <c r="D1348" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1349" spans="1:4">
@@ -20533,7 +20533,7 @@
         <v>369</v>
       </c>
       <c r="D1349" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1350" spans="1:4">
@@ -20547,7 +20547,7 @@
         <v>370</v>
       </c>
       <c r="D1350" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1351" spans="1:4">
@@ -20561,7 +20561,7 @@
         <v>371</v>
       </c>
       <c r="D1351" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1352" spans="1:4">
@@ -20575,7 +20575,7 @@
         <v>372</v>
       </c>
       <c r="D1352" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1353" spans="1:4">
@@ -20589,7 +20589,7 @@
         <v>373</v>
       </c>
       <c r="D1353" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1354" spans="1:4">
@@ -20603,7 +20603,7 @@
         <v>374</v>
       </c>
       <c r="D1354" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1355" spans="1:4">
@@ -20617,7 +20617,7 @@
         <v>375</v>
       </c>
       <c r="D1355" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1356" spans="1:4">
@@ -20631,7 +20631,7 @@
         <v>376</v>
       </c>
       <c r="D1356" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1357" spans="1:4">
@@ -20645,7 +20645,7 @@
         <v>377</v>
       </c>
       <c r="D1357" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1358" spans="1:4">
@@ -20659,7 +20659,7 @@
         <v>378</v>
       </c>
       <c r="D1358" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1359" spans="1:4">
@@ -20673,7 +20673,7 @@
         <v>379</v>
       </c>
       <c r="D1359" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1360" spans="1:4">
@@ -20701,7 +20701,7 @@
         <v>381</v>
       </c>
       <c r="D1361" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1362" spans="1:4">
@@ -20715,7 +20715,7 @@
         <v>382</v>
       </c>
       <c r="D1362" s="2">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1363" spans="1:4">
@@ -20729,7 +20729,7 @@
         <v>383</v>
       </c>
       <c r="D1363" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1364" spans="1:4">
@@ -20743,7 +20743,7 @@
         <v>384</v>
       </c>
       <c r="D1364" s="2">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1365" spans="1:4">
@@ -20757,7 +20757,7 @@
         <v>385</v>
       </c>
       <c r="D1365" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1366" spans="1:4">
@@ -20771,7 +20771,7 @@
         <v>386</v>
       </c>
       <c r="D1366" s="2">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1367" spans="1:4">
@@ -20785,7 +20785,7 @@
         <v>387</v>
       </c>
       <c r="D1367" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1368" spans="1:4">
@@ -20813,7 +20813,7 @@
         <v>389</v>
       </c>
       <c r="D1369" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1370" spans="1:4">
@@ -20827,7 +20827,7 @@
         <v>390</v>
       </c>
       <c r="D1370" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1371" spans="1:4">
@@ -20841,7 +20841,7 @@
         <v>391</v>
       </c>
       <c r="D1371" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1372" spans="1:4">
@@ -20855,7 +20855,7 @@
         <v>392</v>
       </c>
       <c r="D1372" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1373" spans="1:4">
@@ -20869,7 +20869,7 @@
         <v>393</v>
       </c>
       <c r="D1373" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1374" spans="1:4">
@@ -20883,7 +20883,7 @@
         <v>394</v>
       </c>
       <c r="D1374" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1375" spans="1:4">
@@ -20897,7 +20897,7 @@
         <v>395</v>
       </c>
       <c r="D1375" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1376" spans="1:4">
@@ -20911,7 +20911,7 @@
         <v>396</v>
       </c>
       <c r="D1376" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1377" spans="1:4">
@@ -20925,7 +20925,7 @@
         <v>397</v>
       </c>
       <c r="D1377" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1378" spans="1:4">
@@ -20939,7 +20939,7 @@
         <v>398</v>
       </c>
       <c r="D1378" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1379" spans="1:4">
@@ -20953,7 +20953,7 @@
         <v>372</v>
       </c>
       <c r="D1379" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1380" spans="1:4">
@@ -20967,7 +20967,7 @@
         <v>399</v>
       </c>
       <c r="D1380" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1381" spans="1:4">
@@ -20981,7 +20981,7 @@
         <v>400</v>
       </c>
       <c r="D1381" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1382" spans="1:4">
@@ -20995,7 +20995,7 @@
         <v>401</v>
       </c>
       <c r="D1382" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1383" spans="1:4">
@@ -21009,7 +21009,7 @@
         <v>402</v>
       </c>
       <c r="D1383" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1384" spans="1:4">
@@ -21023,7 +21023,7 @@
         <v>403</v>
       </c>
       <c r="D1384" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1385" spans="1:4">
@@ -21037,7 +21037,7 @@
         <v>285</v>
       </c>
       <c r="D1385" s="2">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1386" spans="1:4">
@@ -21051,7 +21051,7 @@
         <v>404</v>
       </c>
       <c r="D1386" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1387" spans="1:4">
@@ -24957,7 +24957,7 @@
         <v>182</v>
       </c>
       <c r="D1665" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1666" spans="1:4">
@@ -25391,7 +25391,7 @@
         <v>295</v>
       </c>
       <c r="D1696" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1697" spans="1:4">
@@ -25797,7 +25797,7 @@
         <v>334</v>
       </c>
       <c r="D1725" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1726" spans="1:4">
@@ -25909,7 +25909,7 @@
         <v>343</v>
       </c>
       <c r="D1733" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1734" spans="1:4">
@@ -26161,7 +26161,7 @@
         <v>375</v>
       </c>
       <c r="D1751" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1752" spans="1:4">
@@ -26231,7 +26231,7 @@
         <v>378</v>
       </c>
       <c r="D1756" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1757" spans="1:4">
@@ -26609,7 +26609,7 @@
         <v>401</v>
       </c>
       <c r="D1783" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1784" spans="1:4">
@@ -41205,13 +41205,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C37DFDD8-2EA9-45DA-BAFF-83FBBFF683A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{708F3462-9CDD-4807-8447-8CB9B84862B8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BB45FFE-F82A-4341-A137-DCBF4A237188}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D9AD92D-585C-4A89-8603-F80F44D7AE20}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D611122-E865-4955-BCB2-52DBFAE2DE1A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95B6543B-51B4-441A-A475-188F140C4F61}"/>
 </file>
--- a/ramco_count_working_days.xlsx
+++ b/ramco_count_working_days.xlsx
@@ -18797,7 +18797,7 @@
         <v>6</v>
       </c>
       <c r="D1225" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1226" spans="1:4">
@@ -18811,7 +18811,7 @@
         <v>7</v>
       </c>
       <c r="D1226" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1227" spans="1:4">
@@ -18825,7 +18825,7 @@
         <v>19</v>
       </c>
       <c r="D1227" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1228" spans="1:4">
@@ -18839,7 +18839,7 @@
         <v>22</v>
       </c>
       <c r="D1228" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1229" spans="1:4">
@@ -18853,7 +18853,7 @@
         <v>25</v>
       </c>
       <c r="D1229" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1230" spans="1:4">
@@ -18867,7 +18867,7 @@
         <v>28</v>
       </c>
       <c r="D1230" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1231" spans="1:4">
@@ -18881,7 +18881,7 @@
         <v>283</v>
       </c>
       <c r="D1231" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1232" spans="1:4">
@@ -18895,7 +18895,7 @@
         <v>48</v>
       </c>
       <c r="D1232" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1233" spans="1:4">
@@ -18909,7 +18909,7 @@
         <v>49</v>
       </c>
       <c r="D1233" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1234" spans="1:4">
@@ -18923,7 +18923,7 @@
         <v>50</v>
       </c>
       <c r="D1234" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1235" spans="1:4">
@@ -18937,7 +18937,7 @@
         <v>51</v>
       </c>
       <c r="D1235" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1236" spans="1:4">
@@ -18951,7 +18951,7 @@
         <v>54</v>
       </c>
       <c r="D1236" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1237" spans="1:4">
@@ -18965,7 +18965,7 @@
         <v>55</v>
       </c>
       <c r="D1237" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1238" spans="1:4">
@@ -18979,7 +18979,7 @@
         <v>56</v>
       </c>
       <c r="D1238" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1239" spans="1:4">
@@ -18993,7 +18993,7 @@
         <v>72</v>
       </c>
       <c r="D1239" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1240" spans="1:4">
@@ -19007,7 +19007,7 @@
         <v>77</v>
       </c>
       <c r="D1240" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1241" spans="1:4">
@@ -19021,7 +19021,7 @@
         <v>85</v>
       </c>
       <c r="D1241" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1242" spans="1:4">
@@ -19035,7 +19035,7 @@
         <v>88</v>
       </c>
       <c r="D1242" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1243" spans="1:4">
@@ -19049,7 +19049,7 @@
         <v>92</v>
       </c>
       <c r="D1243" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1244" spans="1:4">
@@ -19077,7 +19077,7 @@
         <v>102</v>
       </c>
       <c r="D1245" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1246" spans="1:4">
@@ -19091,7 +19091,7 @@
         <v>103</v>
       </c>
       <c r="D1246" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1247" spans="1:4">
@@ -19119,7 +19119,7 @@
         <v>107</v>
       </c>
       <c r="D1248" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1249" spans="1:4">
@@ -19161,7 +19161,7 @@
         <v>122</v>
       </c>
       <c r="D1251" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1252" spans="1:4">
@@ -19175,7 +19175,7 @@
         <v>123</v>
       </c>
       <c r="D1252" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1253" spans="1:4">
@@ -19189,7 +19189,7 @@
         <v>125</v>
       </c>
       <c r="D1253" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1254" spans="1:4">
@@ -19203,7 +19203,7 @@
         <v>126</v>
       </c>
       <c r="D1254" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1255" spans="1:4">
@@ -19217,7 +19217,7 @@
         <v>128</v>
       </c>
       <c r="D1255" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1256" spans="1:4">
@@ -19231,7 +19231,7 @@
         <v>129</v>
       </c>
       <c r="D1256" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1257" spans="1:4">
@@ -19245,7 +19245,7 @@
         <v>135</v>
       </c>
       <c r="D1257" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1258" spans="1:4">
@@ -19259,7 +19259,7 @@
         <v>139</v>
       </c>
       <c r="D1258" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1259" spans="1:4">
@@ -19273,7 +19273,7 @@
         <v>145</v>
       </c>
       <c r="D1259" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1260" spans="1:4">
@@ -19287,7 +19287,7 @@
         <v>148</v>
       </c>
       <c r="D1260" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1261" spans="1:4">
@@ -19301,7 +19301,7 @@
         <v>151</v>
       </c>
       <c r="D1261" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1262" spans="1:4">
@@ -19329,7 +19329,7 @@
         <v>159</v>
       </c>
       <c r="D1263" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1264" spans="1:4">
@@ -19343,7 +19343,7 @@
         <v>160</v>
       </c>
       <c r="D1264" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1265" spans="1:4">
@@ -19357,7 +19357,7 @@
         <v>162</v>
       </c>
       <c r="D1265" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1266" spans="1:4">
@@ -19371,7 +19371,7 @@
         <v>166</v>
       </c>
       <c r="D1266" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1267" spans="1:4">
@@ -19385,7 +19385,7 @@
         <v>170</v>
       </c>
       <c r="D1267" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1268" spans="1:4">
@@ -19399,7 +19399,7 @@
         <v>171</v>
       </c>
       <c r="D1268" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1269" spans="1:4">
@@ -19413,7 +19413,7 @@
         <v>172</v>
       </c>
       <c r="D1269" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1270" spans="1:4">
@@ -19427,7 +19427,7 @@
         <v>173</v>
       </c>
       <c r="D1270" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1271" spans="1:4">
@@ -19441,7 +19441,7 @@
         <v>174</v>
       </c>
       <c r="D1271" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1272" spans="1:4">
@@ -19455,7 +19455,7 @@
         <v>175</v>
       </c>
       <c r="D1272" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1273" spans="1:4">
@@ -19469,7 +19469,7 @@
         <v>177</v>
       </c>
       <c r="D1273" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1274" spans="1:4">
@@ -19483,7 +19483,7 @@
         <v>182</v>
       </c>
       <c r="D1274" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1275" spans="1:4">
@@ -19497,7 +19497,7 @@
         <v>183</v>
       </c>
       <c r="D1275" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1276" spans="1:4">
@@ -19511,7 +19511,7 @@
         <v>186</v>
       </c>
       <c r="D1276" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1277" spans="1:4">
@@ -19525,7 +19525,7 @@
         <v>189</v>
       </c>
       <c r="D1277" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1278" spans="1:4">
@@ -19539,7 +19539,7 @@
         <v>194</v>
       </c>
       <c r="D1278" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1279" spans="1:4">
@@ -19553,7 +19553,7 @@
         <v>206</v>
       </c>
       <c r="D1279" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1280" spans="1:4">
@@ -19567,7 +19567,7 @@
         <v>208</v>
       </c>
       <c r="D1280" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1281" spans="1:4">
@@ -19581,7 +19581,7 @@
         <v>209</v>
       </c>
       <c r="D1281" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1282" spans="1:4">
@@ -19595,7 +19595,7 @@
         <v>226</v>
       </c>
       <c r="D1282" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1283" spans="1:4">
@@ -19609,7 +19609,7 @@
         <v>229</v>
       </c>
       <c r="D1283" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1284" spans="1:4">
@@ -19623,7 +19623,7 @@
         <v>230</v>
       </c>
       <c r="D1284" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1285" spans="1:4">
@@ -19637,7 +19637,7 @@
         <v>235</v>
       </c>
       <c r="D1285" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1286" spans="1:4">
@@ -19651,7 +19651,7 @@
         <v>246</v>
       </c>
       <c r="D1286" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1287" spans="1:4">
@@ -19665,7 +19665,7 @@
         <v>259</v>
       </c>
       <c r="D1287" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1288" spans="1:4">
@@ -19693,7 +19693,7 @@
         <v>262</v>
       </c>
       <c r="D1289" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1290" spans="1:4">
@@ -19721,7 +19721,7 @@
         <v>273</v>
       </c>
       <c r="D1291" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1292" spans="1:4">
@@ -19735,7 +19735,7 @@
         <v>276</v>
       </c>
       <c r="D1292" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1293" spans="1:4">
@@ -19749,7 +19749,7 @@
         <v>277</v>
       </c>
       <c r="D1293" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1294" spans="1:4">
@@ -19763,7 +19763,7 @@
         <v>285</v>
       </c>
       <c r="D1294" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1295" spans="1:4">
@@ -19791,7 +19791,7 @@
         <v>288</v>
       </c>
       <c r="D1296" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1297" spans="1:4">
@@ -19805,7 +19805,7 @@
         <v>289</v>
       </c>
       <c r="D1297" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1298" spans="1:4">
@@ -19819,7 +19819,7 @@
         <v>290</v>
       </c>
       <c r="D1298" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1299" spans="1:4">
@@ -19833,7 +19833,7 @@
         <v>291</v>
       </c>
       <c r="D1299" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1300" spans="1:4">
@@ -19847,7 +19847,7 @@
         <v>150</v>
       </c>
       <c r="D1300" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1301" spans="1:4">
@@ -19861,7 +19861,7 @@
         <v>292</v>
       </c>
       <c r="D1301" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1302" spans="1:4">
@@ -19889,7 +19889,7 @@
         <v>294</v>
       </c>
       <c r="D1303" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1304" spans="1:4">
@@ -19903,7 +19903,7 @@
         <v>130</v>
       </c>
       <c r="D1304" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1305" spans="1:4">
@@ -19945,7 +19945,7 @@
         <v>301</v>
       </c>
       <c r="D1307" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1308" spans="1:4">
@@ -19959,7 +19959,7 @@
         <v>302</v>
       </c>
       <c r="D1308" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1309" spans="1:4">
@@ -19973,7 +19973,7 @@
         <v>303</v>
       </c>
       <c r="D1309" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1310" spans="1:4">
@@ -19987,7 +19987,7 @@
         <v>304</v>
       </c>
       <c r="D1310" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1311" spans="1:4">
@@ -20001,7 +20001,7 @@
         <v>305</v>
       </c>
       <c r="D1311" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1312" spans="1:4">
@@ -20015,7 +20015,7 @@
         <v>306</v>
       </c>
       <c r="D1312" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1313" spans="1:4">
@@ -20029,7 +20029,7 @@
         <v>307</v>
       </c>
       <c r="D1313" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1314" spans="1:4">
@@ -20043,7 +20043,7 @@
         <v>308</v>
       </c>
       <c r="D1314" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1315" spans="1:4">
@@ -20057,7 +20057,7 @@
         <v>309</v>
       </c>
       <c r="D1315" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1316" spans="1:4">
@@ -20071,7 +20071,7 @@
         <v>310</v>
       </c>
       <c r="D1316" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1317" spans="1:4">
@@ -20085,7 +20085,7 @@
         <v>312</v>
       </c>
       <c r="D1317" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1318" spans="1:4">
@@ -20099,7 +20099,7 @@
         <v>313</v>
       </c>
       <c r="D1318" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1319" spans="1:4">
@@ -20113,7 +20113,7 @@
         <v>314</v>
       </c>
       <c r="D1319" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1320" spans="1:4">
@@ -20127,7 +20127,7 @@
         <v>315</v>
       </c>
       <c r="D1320" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1321" spans="1:4">
@@ -20155,7 +20155,7 @@
         <v>317</v>
       </c>
       <c r="D1322" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1323" spans="1:4">
@@ -20183,7 +20183,7 @@
         <v>319</v>
       </c>
       <c r="D1324" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1325" spans="1:4">
@@ -20225,7 +20225,7 @@
         <v>323</v>
       </c>
       <c r="D1327" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1328" spans="1:4">
@@ -20239,7 +20239,7 @@
         <v>324</v>
       </c>
       <c r="D1328" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1329" spans="1:4">
@@ -20253,7 +20253,7 @@
         <v>325</v>
       </c>
       <c r="D1329" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1330" spans="1:4">
@@ -20267,7 +20267,7 @@
         <v>326</v>
       </c>
       <c r="D1330" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1331" spans="1:4">
@@ -20281,7 +20281,7 @@
         <v>328</v>
       </c>
       <c r="D1331" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1332" spans="1:4">
@@ -20295,7 +20295,7 @@
         <v>330</v>
       </c>
       <c r="D1332" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1333" spans="1:4">
@@ -20323,7 +20323,7 @@
         <v>334</v>
       </c>
       <c r="D1334" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1335" spans="1:4">
@@ -20365,7 +20365,7 @@
         <v>339</v>
       </c>
       <c r="D1337" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1338" spans="1:4">
@@ -20379,7 +20379,7 @@
         <v>340</v>
       </c>
       <c r="D1338" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1339" spans="1:4">
@@ -20393,7 +20393,7 @@
         <v>341</v>
       </c>
       <c r="D1339" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1340" spans="1:4">
@@ -20407,7 +20407,7 @@
         <v>342</v>
       </c>
       <c r="D1340" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1341" spans="1:4">
@@ -20449,7 +20449,7 @@
         <v>346</v>
       </c>
       <c r="D1343" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1344" spans="1:4">
@@ -20491,7 +20491,7 @@
         <v>349</v>
       </c>
       <c r="D1346" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1347" spans="1:4">
@@ -20505,7 +20505,7 @@
         <v>350</v>
       </c>
       <c r="D1347" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1348" spans="1:4">
@@ -20519,7 +20519,7 @@
         <v>368</v>
       </c>
       <c r="D1348" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1349" spans="1:4">
@@ -20533,7 +20533,7 @@
         <v>369</v>
       </c>
       <c r="D1349" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1350" spans="1:4">
@@ -20561,7 +20561,7 @@
         <v>371</v>
       </c>
       <c r="D1351" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1352" spans="1:4">
@@ -20575,7 +20575,7 @@
         <v>372</v>
       </c>
       <c r="D1352" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1353" spans="1:4">
@@ -20589,7 +20589,7 @@
         <v>373</v>
       </c>
       <c r="D1353" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1354" spans="1:4">
@@ -20603,7 +20603,7 @@
         <v>374</v>
       </c>
       <c r="D1354" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1355" spans="1:4">
@@ -20617,7 +20617,7 @@
         <v>375</v>
       </c>
       <c r="D1355" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1356" spans="1:4">
@@ -20631,7 +20631,7 @@
         <v>376</v>
       </c>
       <c r="D1356" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1357" spans="1:4">
@@ -20645,7 +20645,7 @@
         <v>377</v>
       </c>
       <c r="D1357" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1358" spans="1:4">
@@ -20659,7 +20659,7 @@
         <v>378</v>
       </c>
       <c r="D1358" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1359" spans="1:4">
@@ -20673,7 +20673,7 @@
         <v>379</v>
       </c>
       <c r="D1359" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1360" spans="1:4">
@@ -20701,7 +20701,7 @@
         <v>381</v>
       </c>
       <c r="D1361" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1362" spans="1:4">
@@ -20757,7 +20757,7 @@
         <v>385</v>
       </c>
       <c r="D1365" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1366" spans="1:4">
@@ -20771,7 +20771,7 @@
         <v>386</v>
       </c>
       <c r="D1366" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1367" spans="1:4">
@@ -20785,7 +20785,7 @@
         <v>387</v>
       </c>
       <c r="D1367" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1368" spans="1:4">
@@ -20813,7 +20813,7 @@
         <v>389</v>
       </c>
       <c r="D1369" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1370" spans="1:4">
@@ -20827,7 +20827,7 @@
         <v>390</v>
       </c>
       <c r="D1370" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1371" spans="1:4">
@@ -20841,7 +20841,7 @@
         <v>391</v>
       </c>
       <c r="D1371" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1372" spans="1:4">
@@ -20855,7 +20855,7 @@
         <v>392</v>
       </c>
       <c r="D1372" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1373" spans="1:4">
@@ -20869,7 +20869,7 @@
         <v>393</v>
       </c>
       <c r="D1373" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1374" spans="1:4">
@@ -20883,7 +20883,7 @@
         <v>394</v>
       </c>
       <c r="D1374" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1375" spans="1:4">
@@ -20897,7 +20897,7 @@
         <v>395</v>
       </c>
       <c r="D1375" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1376" spans="1:4">
@@ -20925,7 +20925,7 @@
         <v>397</v>
       </c>
       <c r="D1377" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1378" spans="1:4">
@@ -20939,7 +20939,7 @@
         <v>398</v>
       </c>
       <c r="D1378" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1379" spans="1:4">
@@ -20953,7 +20953,7 @@
         <v>372</v>
       </c>
       <c r="D1379" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1380" spans="1:4">
@@ -20967,7 +20967,7 @@
         <v>399</v>
       </c>
       <c r="D1380" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1381" spans="1:4">
@@ -20995,7 +20995,7 @@
         <v>401</v>
       </c>
       <c r="D1382" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1383" spans="1:4">
@@ -21009,7 +21009,7 @@
         <v>402</v>
       </c>
       <c r="D1383" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1384" spans="1:4">
@@ -21023,7 +21023,7 @@
         <v>403</v>
       </c>
       <c r="D1384" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1385" spans="1:4">
@@ -21051,7 +21051,7 @@
         <v>404</v>
       </c>
       <c r="D1386" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1387" spans="1:4">
@@ -41205,13 +41205,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{708F3462-9CDD-4807-8447-8CB9B84862B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F60D653D-CF03-46A8-BC7D-354339F2EE6A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D9AD92D-585C-4A89-8603-F80F44D7AE20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1ADD114-1F4E-430D-BE0F-54345871F42B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95B6543B-51B4-441A-A475-188F140C4F61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7725B95-64CC-43A5-8EC6-699DC13341E7}"/>
 </file>